--- a/Data/TeamTracker.xlsx
+++ b/Data/TeamTracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\HROnboardingApp\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290A2C58-7E48-4AB1-B0EB-949A51E4EB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2DB88E-8BC7-43B1-9BFA-034378D0886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{30C4A489-88FD-4F42-90A7-1AA7E270F543}"/>
   </bookViews>
@@ -173,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="801">
   <si>
     <t>SrNo</t>
   </si>
@@ -1503,6 +1503,9 @@
     <t>Senior Consultant</t>
   </si>
   <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
     <t>AWS</t>
   </si>
   <si>
@@ -1515,6 +1518,36 @@
     <t>7937937830</t>
   </si>
   <si>
+    <t>Rahul Patki</t>
+  </si>
+  <si>
+    <t>rpatki@deloitte.com</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>Firewire Rsik</t>
+  </si>
+  <si>
+    <t>Working on VDI setup</t>
+  </si>
+  <si>
+    <t>97987698076</t>
+  </si>
+  <si>
+    <t>Ramesh Saharan</t>
+  </si>
+  <si>
+    <t>rasaharan@deloitte.com</t>
+  </si>
+  <si>
+    <t>Will start working next week</t>
+  </si>
+  <si>
+    <t>8746848938</t>
+  </si>
+  <si>
     <t>UserID</t>
   </si>
   <si>
@@ -1533,39 +1566,39 @@
     <t>Admin@123</t>
   </si>
   <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>User@123</t>
+  </si>
+  <si>
     <t>User</t>
   </si>
   <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>User@123</t>
-  </si>
-  <si>
     <t>kmullangi1@deloitte.com</t>
   </si>
   <si>
     <t>Admin2@456</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>ropatil@deloitte.com</t>
-  </si>
-  <si>
-    <t>Ropat@97</t>
+    <t>Plks@2000</t>
+  </si>
+  <si>
+    <t>Admin@789</t>
+  </si>
+  <si>
+    <t>pefernandes2@deloitte.com</t>
+  </si>
+  <si>
+    <t>Pearlfer@96</t>
   </si>
   <si>
     <t>FALSE</t>
   </si>
   <si>
-    <t>Plks@2000</t>
-  </si>
-  <si>
-    <t>Admin@789</t>
-  </si>
-  <si>
     <t>StepID</t>
   </si>
   <si>
@@ -1650,79 +1683,79 @@
     <t>CompletedDate</t>
   </si>
   <si>
+    <t>NotStarted</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>InProgress</t>
+  </si>
+  <si>
+    <t>CandidateId</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>.Net Dev</t>
+  </si>
+  <si>
+    <t>Client Escalation</t>
+  </si>
+  <si>
+    <t>Late to setup VDI</t>
+  </si>
+  <si>
+    <t>Contract Ended</t>
+  </si>
+  <si>
+    <t>Did not Joined</t>
+  </si>
+  <si>
+    <t>TrainingID</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>DueDate</t>
+  </si>
+  <si>
+    <t>DataDog</t>
+  </si>
+  <si>
+    <t>AKS</t>
+  </si>
+  <si>
+    <t>ROVO</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
     <t>2026-09-01</t>
   </si>
   <si>
-    <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
-    <t>2026-09-07</t>
-  </si>
-  <si>
-    <t>NotStarted</t>
-  </si>
-  <si>
-    <t>InProgress</t>
-  </si>
-  <si>
-    <t>CandidateId</t>
-  </si>
-  <si>
-    <t>Reason</t>
-  </si>
-  <si>
-    <t>.Net Dev</t>
-  </si>
-  <si>
-    <t>Client Escalation</t>
-  </si>
-  <si>
-    <t>Ganesh Mundhe</t>
-  </si>
-  <si>
-    <t>Cloud Admin</t>
-  </si>
-  <si>
-    <t>Contract End</t>
-  </si>
-  <si>
-    <t>Hari Gokhale</t>
-  </si>
-  <si>
-    <t>harryG@deloitte.com</t>
-  </si>
-  <si>
-    <t>Not Joined</t>
-  </si>
-  <si>
-    <t>TrainingID</t>
-  </si>
-  <si>
-    <t>Domain</t>
-  </si>
-  <si>
-    <t>DueDate</t>
-  </si>
-  <si>
-    <t>DataDog</t>
-  </si>
-  <si>
-    <t>AKS</t>
-  </si>
-  <si>
-    <t>ROVO</t>
-  </si>
-  <si>
-    <t>2026-10-30</t>
-  </si>
-  <si>
     <t>Github Copilot</t>
   </si>
   <si>
     <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Project name</t>
@@ -3742,7 +3775,7 @@
     <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
     <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1"/>
@@ -4404,9 +4437,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -7407,7 +7437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{358897FF-3897-4B6D-8A0F-DEA84C78DC28}">
-  <dimension ref="A1:AI101"/>
+  <dimension ref="A1:AI103"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -16877,11 +16907,17 @@
       <c r="I101" s="0" t="s">
         <v>439</v>
       </c>
+      <c r="K101" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="L101" s="0" t="s">
+        <v>127</v>
+      </c>
       <c r="M101" s="0" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N101" s="0" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O101" s="0" t="s">
         <v>42</v>
@@ -16893,22 +16929,140 @@
         <v>126</v>
       </c>
       <c r="U101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="V101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="W101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE101" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="AG101" s="0" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0">
+        <v>101</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="C102" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="D102" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E102" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="I102" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L102" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M102" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="N102" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="O102" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="P102" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q102" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="U102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="V101" s="0" t="s">
+      <c r="V102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="W101" s="0" t="s">
+      <c r="W102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="AB101" s="0" t="s">
+      <c r="AB102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="AE101" s="0" t="s">
+      <c r="AE102" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="AG102" s="0" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>102</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="D103" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E103" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="I103" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="M103" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="N103" s="0" t="s">
         <v>442</v>
       </c>
-      <c r="AG101" s="0" t="s">
-        <v>443</v>
+      <c r="O103" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="P103" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q103" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="U103" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="V103" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="W103" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="AB103" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE103" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="AG103" s="0" t="s">
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -17085,21 +17239,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>50</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3">
@@ -17192,7 +17346,7 @@
     </row>
     <row r="11">
       <c r="A11" s="80" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B11" s="78">
         <v>84</v>
@@ -17220,22 +17374,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="78" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
     <row r="3">
       <c r="A3" s="78" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>127</v>
@@ -17244,7 +17398,7 @@
         <v>45</v>
       </c>
       <c r="D3" s="78" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4">
@@ -17407,7 +17561,7 @@
     </row>
     <row r="17">
       <c r="A17" s="78" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B17" s="78">
         <v>6</v>
@@ -17426,20 +17580,20 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="77" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="78" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B23" s="78" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="C23" s="78"/>
       <c r="D23" s="78"/>
@@ -17447,7 +17601,7 @@
     </row>
     <row r="24">
       <c r="A24" s="78" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B24" s="78" t="s">
         <v>83</v>
@@ -17459,7 +17613,7 @@
         <v>61</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
     </row>
     <row r="25">
@@ -17643,7 +17797,7 @@
     </row>
     <row r="38">
       <c r="A38" s="78" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B38" s="78">
         <v>24</v>
@@ -17660,63 +17814,63 @@
     </row>
     <row r="41">
       <c r="A41" s="78" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="79" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>36</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="80" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="B52" s="0">
         <v>5</v>
@@ -17733,7 +17887,7 @@
     </row>
     <row r="53">
       <c r="A53" s="80" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="C53" s="0">
         <v>8</v>
@@ -17744,7 +17898,7 @@
     </row>
     <row r="54">
       <c r="A54" s="80" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="B54" s="0">
         <v>1</v>
@@ -17761,12 +17915,12 @@
     </row>
     <row r="55">
       <c r="A55" s="80" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="80" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B56" s="0">
         <v>6</v>
@@ -17783,7 +17937,7 @@
     </row>
     <row r="59">
       <c r="A59" s="70" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="B59" s="71"/>
       <c r="C59" s="71"/>
@@ -17792,19 +17946,19 @@
     </row>
     <row r="60">
       <c r="A60" s="70" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="B60" s="70" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="C60" s="70" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D60" s="70" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E60" s="70" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="F60" s="77"/>
     </row>
@@ -17813,7 +17967,7 @@
         <v>38</v>
       </c>
       <c r="B61" s="71" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C61" s="71">
         <v>12</v>
@@ -17828,7 +17982,7 @@
     <row r="62">
       <c r="A62" s="325"/>
       <c r="B62" s="71" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C62" s="71">
         <v>9</v>
@@ -17843,7 +17997,7 @@
     <row r="63">
       <c r="A63" s="326"/>
       <c r="B63" s="71" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C63" s="71">
         <v>27</v>
@@ -17896,15 +18050,15 @@
         <v>4</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
     </row>
     <row r="4">
@@ -18005,7 +18159,7 @@
     </row>
     <row r="16">
       <c r="A16" s="80" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B16" s="0">
         <v>104</v>
@@ -18031,10 +18185,10 @@
         <v>12</v>
       </c>
       <c r="B1" s="291" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="C1" s="291" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2" ht="29">
@@ -18042,10 +18196,10 @@
         <v>198</v>
       </c>
       <c r="B2" s="293" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C2" s="294" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
     </row>
     <row r="3">
@@ -18053,10 +18207,10 @@
         <v>110</v>
       </c>
       <c r="B3" s="295" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="C3" s="294" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" ht="29">
@@ -18064,32 +18218,32 @@
         <v>141</v>
       </c>
       <c r="B4" s="293" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C4" s="294" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
     </row>
     <row r="5" ht="58">
       <c r="A5" s="292" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="B5" s="293" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" ht="29">
       <c r="A6" s="293" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="B6" s="293" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="C6" s="294" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7">
@@ -18097,10 +18251,10 @@
         <v>58</v>
       </c>
       <c r="B7" s="293" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C7" s="294" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8">
@@ -18108,7 +18262,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="297" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C8" s="296" t="s">
         <v>172</v>
@@ -18119,10 +18273,10 @@
         <v>113</v>
       </c>
       <c r="B9" s="297" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="C9" s="296" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -18142,18 +18296,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="288" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B1" s="288" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="289" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="B2" s="290" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
     </row>
   </sheetData>
@@ -18179,19 +18333,19 @@
   <sheetData>
     <row r="1" ht="39">
       <c r="A1" s="298" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="B1" s="299" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="C1" s="299" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="D1" s="299" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="E1" s="300" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" ht="247" customHeight="1">
@@ -18199,16 +18353,16 @@
         <v>198</v>
       </c>
       <c r="B2" s="329" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="C2" s="329">
         <v>2</v>
       </c>
       <c r="D2" s="331" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="E2" s="301" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" ht="26.5">
@@ -18217,22 +18371,22 @@
       <c r="C3" s="330"/>
       <c r="D3" s="332"/>
       <c r="E3" s="302" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
     </row>
     <row r="4" ht="156.5">
       <c r="A4" s="328"/>
       <c r="B4" s="303" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="C4" s="303">
         <v>2</v>
       </c>
       <c r="D4" s="304" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="E4" s="302" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
     </row>
     <row r="5" ht="39.5">
@@ -18246,10 +18400,10 @@
         <v>3</v>
       </c>
       <c r="D5" s="305" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="E5" s="302" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6" ht="65.5">
@@ -18257,15 +18411,15 @@
       <c r="B6" s="330"/>
       <c r="C6" s="330"/>
       <c r="D6" s="306" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="E6" s="307" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
     </row>
     <row r="7" ht="52.5">
       <c r="A7" s="327" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="B7" s="329" t="s">
         <v>96</v>
@@ -18274,10 +18428,10 @@
         <v>3</v>
       </c>
       <c r="D7" s="305" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="E7" s="301" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8" ht="65.5">
@@ -18285,10 +18439,10 @@
       <c r="B8" s="336"/>
       <c r="C8" s="336"/>
       <c r="D8" s="308" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="E8" s="309" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" ht="39.5">
@@ -18296,13 +18450,13 @@
       <c r="B9" s="330"/>
       <c r="C9" s="330"/>
       <c r="D9" s="306" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="E9" s="310"/>
     </row>
     <row r="10" ht="273" customHeight="1">
       <c r="A10" s="327" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="B10" s="329" t="s">
         <v>87</v>
@@ -18311,10 +18465,10 @@
         <v>4</v>
       </c>
       <c r="D10" s="334" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="E10" s="301" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" ht="26.5">
@@ -18323,7 +18477,7 @@
       <c r="C11" s="330"/>
       <c r="D11" s="335"/>
       <c r="E11" s="307" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" ht="65.5">
@@ -18337,10 +18491,10 @@
         <v>2</v>
       </c>
       <c r="D12" s="304" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="E12" s="312" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -18376,26 +18530,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="275" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="B1" s="276" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="71" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="71" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -18420,104 +18574,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
     </row>
   </sheetData>
@@ -18547,53 +18701,53 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" ht="101.5">
       <c r="A2" s="0" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="C2" s="277" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
     </row>
   </sheetData>
@@ -18613,62 +18767,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="C2" s="278" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C3" s="278" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="C4" s="278" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="C5" s="278" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="C6" s="278" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
     </row>
   </sheetData>
@@ -18695,19 +18849,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2">
@@ -18718,13 +18872,13 @@
         <v>161</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3">
@@ -18735,13 +18889,13 @@
         <v>351</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="4">
@@ -18749,67 +18903,67 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>456</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>457</v>
+        <v>435</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>467</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>435</v>
+        <v>91</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>91</v>
+        <v>469</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -18820,7 +18974,6 @@
     <hyperlink ref="C3" r:id="rId4"/>
     <hyperlink ref="B4" r:id="rId5"/>
     <hyperlink ref="C4" r:id="rId6"/>
-    <hyperlink ref="C5" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -18839,68 +18992,68 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="2" ht="43.5">
       <c r="A2" s="337" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B2" s="173" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="C2" s="277" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3" ht="29">
       <c r="A3" s="337"/>
       <c r="B3" s="173" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
     <row r="6">
@@ -18908,19 +19061,19 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -18949,98 +19102,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="275" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="279" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="B2" s="280" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" ht="43.5">
       <c r="A3" s="281" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="B3" s="282" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
     </row>
     <row r="4" ht="43.5">
       <c r="A4" s="281" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="B4" s="282" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
     </row>
     <row r="5" ht="101.5">
       <c r="A5" s="281" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B5" s="283" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
     </row>
     <row r="6" ht="29">
       <c r="A6" s="281" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="B6" s="282" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="279" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="B7" s="280" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="279" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="B8" s="280" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
     </row>
     <row r="9" ht="72.5">
       <c r="A9" s="281" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="B9" s="282" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="279" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="B10" s="280" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="284" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="B11" s="280" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" ht="58">
       <c r="A12" s="285" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="B12" s="282" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -19073,26 +19226,26 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="67" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="B1" s="67" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
     </row>
     <row r="2" ht="43.5">
       <c r="A2" s="286" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" ht="43.5">
       <c r="A3" s="286" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
     </row>
   </sheetData>
@@ -19116,50 +19269,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="77" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
     </row>
   </sheetData>
@@ -19186,34 +19339,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="287" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="B1" s="276" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="114" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="71" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="71" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
     </row>
   </sheetData>
@@ -19240,19 +19393,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2">
@@ -19263,13 +19416,13 @@
         <v>169</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D2" s="0">
         <v>1</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3">
@@ -19280,13 +19433,13 @@
         <v>169</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D3" s="0">
         <v>2</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4">
@@ -19297,13 +19450,13 @@
         <v>169</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D4" s="0">
         <v>3</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5">
@@ -19314,13 +19467,13 @@
         <v>169</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D5" s="0">
         <v>4</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6">
@@ -19328,16 +19481,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="D6" s="0">
         <v>1</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7">
@@ -19345,16 +19498,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D7" s="0">
         <v>2</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -19362,16 +19515,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D8" s="0">
         <v>3</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -19379,16 +19532,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>477</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>466</v>
       </c>
       <c r="D9" s="0">
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10">
@@ -19396,16 +19549,16 @@
         <v>10</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D10" s="0">
         <v>2</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11">
@@ -19413,16 +19566,16 @@
         <v>11</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D11" s="0">
         <v>3</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12">
@@ -19430,16 +19583,16 @@
         <v>12</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D12" s="0">
         <v>4</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13">
@@ -19447,16 +19600,16 @@
         <v>13</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D13" s="0">
         <v>1</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14">
@@ -19464,16 +19617,16 @@
         <v>14</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D14" s="0">
         <v>2</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15">
@@ -19481,16 +19634,16 @@
         <v>15</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D15" s="0">
         <v>3</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16">
@@ -19498,16 +19651,16 @@
         <v>16</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D16" s="0">
         <v>4</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="17">
@@ -19515,16 +19668,16 @@
         <v>17</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="D17" s="0">
         <v>1</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="18">
@@ -19532,16 +19685,16 @@
         <v>18</v>
       </c>
       <c r="B18" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>479</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>468</v>
       </c>
       <c r="D18" s="0">
         <v>2</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19">
@@ -19549,16 +19702,16 @@
         <v>19</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="D19" s="0">
         <v>3</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="20">
@@ -19566,16 +19719,16 @@
         <v>20</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="D20" s="0">
         <v>4</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21">
@@ -19583,16 +19736,16 @@
         <v>21</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="D21" s="0">
         <v>4</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22">
@@ -19600,16 +19753,16 @@
         <v>22</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D22" s="0">
         <v>5</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23">
@@ -19620,13 +19773,13 @@
         <v>206</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="D23" s="0">
         <v>1</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -19637,7 +19790,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F9B618-8BC8-49DD-B7A7-74400FF462D0}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -19648,106 +19801,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="0">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C2" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>489</v>
+        <v>500</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="0">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C3" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>320</v>
+        <v>500</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="0">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C4" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>320</v>
+        <v>61</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="0">
-        <v>22</v>
+        <v>80</v>
       </c>
       <c r="C5" s="0">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="338">
-        <v>46239</v>
+      <c r="E5" s="0" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="0">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="C6" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="0">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="C7" s="0">
         <v>5</v>
@@ -19756,108 +19915,74 @@
         <v>61</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="0">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C8" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>491</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="0">
         <v>25</v>
       </c>
       <c r="C9" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D9" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>492</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="0">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C10" s="0">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D10" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="0">
         <v>25</v>
       </c>
       <c r="C11" s="0">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>61</v>
+        <v>504</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0">
-        <v>25</v>
-      </c>
-      <c r="C12" s="0">
-        <v>21</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>493</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0">
-        <v>25</v>
-      </c>
-      <c r="C13" s="0">
-        <v>22</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>494</v>
-      </c>
-      <c r="E13" s="0" t="s">
         <v>46</v>
       </c>
     </row>
@@ -19869,7 +19994,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5417B356-7CA8-4073-B5EA-2ED7E0869648}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -19881,7 +20006,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -19890,10 +20015,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2">
@@ -19907,50 +20032,66 @@
         <v>347</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>499</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>218</v>
+        <v>192</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>193</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>500</v>
+        <v>52</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>131</v>
+        <v>41</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>502</v>
+        <v>217</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>503</v>
+        <v>218</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>119</v>
+        <v>439</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>504</v>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>60</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>511</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -19959,7 +20100,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14947C1-2082-4307-8EB3-961E6465F131}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -19972,22 +20113,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2">
@@ -19998,7 +20139,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>61</v>
@@ -20018,7 +20159,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>320</v>
@@ -20035,7 +20176,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>61</v>
@@ -20055,7 +20196,7 @@
         <v>78</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="D5" s="0" t="s">
         <v>61</v>
@@ -20075,7 +20216,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="D6" s="0" t="s">
         <v>320</v>
@@ -20098,10 +20239,10 @@
         <v>61</v>
       </c>
       <c r="E7" s="314" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F7" s="314" t="s">
-        <v>489</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -20112,13 +20253,73 @@
         <v>78</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>513</v>
+        <v>521</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0">
+        <v>94</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>55</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>97</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>522</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -20150,34 +20351,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" ht="126" customHeight="1">
@@ -20205,10 +20406,10 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
     </row>
     <row r="3">
@@ -20225,7 +20426,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>127</v>
@@ -20236,7 +20437,7 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="K3" s="8"/>
     </row>
@@ -20254,7 +20455,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>127</v>
@@ -20263,10 +20464,10 @@
         <v>127</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="8"/>
@@ -20294,10 +20495,10 @@
         <v>127</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="8"/>
@@ -20307,7 +20508,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="5"/>
@@ -20345,7 +20546,7 @@
         <v>190</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
@@ -20393,7 +20594,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="11" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10">
@@ -20420,7 +20621,7 @@
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="8"/>
@@ -20439,7 +20640,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>45</v>
@@ -20448,12 +20649,12 @@
         <v>45</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="11" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
     </row>
     <row r="12" ht="58.5" customHeight="1">
@@ -20480,13 +20681,13 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13">
@@ -20539,10 +20740,10 @@
         <v>127</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
@@ -20568,10 +20769,10 @@
         <v>127</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
@@ -20592,7 +20793,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>45</v>
@@ -20601,14 +20802,14 @@
         <v>127</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17" ht="134" customHeight="1">
@@ -20634,16 +20835,16 @@
         <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18">
@@ -20651,7 +20852,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>50</v>
@@ -20660,7 +20861,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>127</v>
@@ -20669,10 +20870,10 @@
         <v>127</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="15"/>
@@ -20682,7 +20883,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>50</v>
@@ -20691,7 +20892,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>127</v>
@@ -20709,7 +20910,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>50</v>
@@ -20736,7 +20937,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>50</v>
@@ -20781,10 +20982,10 @@
         <v>127</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
@@ -20828,7 +21029,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>127</v>
@@ -20840,7 +21041,7 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="8" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
     </row>
     <row r="25">
@@ -20848,7 +21049,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>50</v>
@@ -20875,7 +21076,7 @@
         <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>50</v>
@@ -20911,7 +21112,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>127</v>
@@ -20931,7 +21132,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>50</v>
@@ -20952,7 +21153,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="8" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
     </row>
     <row r="29" ht="68.5" customHeight="1">
@@ -20960,7 +21161,7 @@
         <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>50</v>
@@ -20981,7 +21182,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="8" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -21016,7 +21217,7 @@
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="315" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="D1" s="316"/>
       <c r="E1" s="316"/>
@@ -21027,7 +21228,7 @@
       <c r="J1" s="316"/>
       <c r="K1" s="317"/>
       <c r="L1" s="318" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="M1" s="319"/>
       <c r="N1" s="319"/>
@@ -21037,7 +21238,7 @@
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
       <c r="D2" s="320" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="E2" s="320"/>
       <c r="F2" s="320"/>
@@ -21045,7 +21246,7 @@
       <c r="H2" s="320"/>
       <c r="I2" s="320"/>
       <c r="J2" s="26" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="K2" s="27"/>
       <c r="L2" s="25"/>
@@ -21054,66 +21255,66 @@
     </row>
     <row r="3" ht="43.5">
       <c r="A3" s="28" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="N3" s="29" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="24" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="G4" s="25">
         <v>0</v>
@@ -21122,7 +21323,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>63</v>
@@ -21134,7 +21335,7 @@
         <v>45</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N4" s="25">
         <v>10</v>
@@ -21142,16 +21343,16 @@
     </row>
     <row r="5">
       <c r="A5" s="35" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="C5" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E5" s="38" t="s">
         <v>63</v>
@@ -21176,7 +21377,7 @@
         <v>45</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N5" s="37">
         <v>4</v>
@@ -21184,7 +21385,7 @@
     </row>
     <row r="6">
       <c r="A6" s="35" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>269</v>
@@ -21228,43 +21429,43 @@
     </row>
     <row r="7">
       <c r="A7" s="35" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="L7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N7" s="37">
         <v>6</v>
@@ -21272,16 +21473,16 @@
     </row>
     <row r="8">
       <c r="A8" s="35" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E8" s="41">
         <v>0.5</v>
@@ -21300,13 +21501,13 @@
         <v>48</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="L8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N8" s="37">
         <v>8</v>
@@ -21317,13 +21518,13 @@
         <v>59</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="C9" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>63</v>
@@ -21350,7 +21551,7 @@
         <v>45</v>
       </c>
       <c r="M9" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N9" s="43">
         <v>1</v>
@@ -21367,7 +21568,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E10" s="41">
         <v>1</v>
@@ -21385,16 +21586,16 @@
         <v>63</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="L10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N10" s="43">
         <v>3</v>
@@ -21405,13 +21606,13 @@
         <v>59</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E11" s="41">
         <v>1</v>
@@ -21429,16 +21630,16 @@
         <v>63</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="L11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N11" s="43">
         <v>3</v>
@@ -21455,7 +21656,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E12" s="49">
         <v>0.8</v>
@@ -21476,13 +21677,13 @@
         <v>253</v>
       </c>
       <c r="K12" s="52" t="s">
+        <v>605</v>
+      </c>
+      <c r="L12" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="43" t="s">
         <v>594</v>
-      </c>
-      <c r="L12" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" s="43" t="s">
-        <v>583</v>
       </c>
       <c r="N12" s="43">
         <v>12</v>
@@ -21493,13 +21694,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="C13" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E13" s="41">
         <v>0.5</v>
@@ -21517,7 +21718,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="K13" s="54">
         <v>9618241586</v>
@@ -21526,7 +21727,7 @@
         <v>45</v>
       </c>
       <c r="M13" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N13" s="43">
         <v>0</v>
@@ -21537,7 +21738,7 @@
         <v>59</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>127</v>
@@ -21614,7 +21815,7 @@
         <v>45</v>
       </c>
       <c r="M15" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N15" s="43">
         <v>3</v>
@@ -21646,13 +21847,13 @@
         <v>210</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>127</v>
@@ -21669,13 +21870,13 @@
         <v>59</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>63</v>
@@ -21713,13 +21914,13 @@
         <v>59</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E18" s="41">
         <v>0.5</v>
@@ -21737,16 +21938,16 @@
         <v>46049</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="L18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M18" s="43" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="N18" s="43">
         <v>9</v>
@@ -21763,22 +21964,22 @@
         <v>45</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -21805,19 +22006,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="C1" s="76" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D1" s="76" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E1" s="76" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2">
@@ -21826,7 +22027,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="C2" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!U1:U679, "Y")</f>
@@ -21844,7 +22045,7 @@
     <row r="3">
       <c r="A3" s="321"/>
       <c r="B3" s="6" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C3" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!V1:V679, "Y")</f>
@@ -21862,7 +22063,7 @@
     <row r="4">
       <c r="A4" s="321"/>
       <c r="B4" s="6" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="C4" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!AB1:AB679, "Y")</f>
@@ -21879,20 +22080,20 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7">
       <c r="B7" s="6" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="C7" s="68">
         <v>36</v>
@@ -21904,12 +22105,12 @@
     </row>
     <row r="9">
       <c r="A9" s="322" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="B9" s="322"/>
       <c r="C9" s="322"/>
       <c r="D9" s="0" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
     </row>
     <row r="10">
@@ -21918,12 +22119,12 @@
         <v>36</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="70" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="B11" s="323">
         <v>74</v>
@@ -21932,7 +22133,7 @@
     </row>
     <row r="12">
       <c r="A12" s="71" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="B12" s="72">
         <v>61</v>
@@ -21943,7 +22144,7 @@
     </row>
     <row r="13">
       <c r="A13" s="71" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="B13" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
@@ -21955,7 +22156,7 @@
     </row>
     <row r="14">
       <c r="A14" s="71" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="B14" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "N")</f>
@@ -21965,7 +22166,7 @@
     </row>
     <row r="15">
       <c r="A15" s="74" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="B15" s="75">
         <v>26</v>
@@ -21976,14 +22177,14 @@
     </row>
     <row r="16">
       <c r="A16" s="71" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="B16" s="72">
         <f>B12-B15</f>
         <v>35</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
     </row>
   </sheetData>

--- a/Data/TeamTracker.xlsx
+++ b/Data/TeamTracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\HROnboardingApp\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2DB88E-8BC7-43B1-9BFA-034378D0886F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78AC528C-3A23-4B49-8177-526F3A6D1B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{30C4A489-88FD-4F42-90A7-1AA7E270F543}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{30C4A489-88FD-4F42-90A7-1AA7E270F543}"/>
   </bookViews>
   <sheets>
     <sheet name="TeamMember" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
   <externalReferences>
     <externalReference r:id="rId25"/>
   </externalReferences>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId26"/>
     <pivotCache cacheId="1" r:id="rId27"/>
@@ -80,35 +80,26 @@
   <commentList>
     <comment ref="Y39" authorId="0" shapeId="0" xr:uid="{A76EB6EC-838A-4804-B11A-4B53BE1844C8}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Completed AI anthropic training</t>
       </text>
     </comment>
     <comment ref="Y40" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Completed AI anthropic training</t>
       </text>
     </comment>
     <comment ref="Y41" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Completed AI anthropic training</t>
       </text>
     </comment>
   </commentList>
@@ -126,46 +117,34 @@
   <commentList>
     <comment ref="K15" authorId="0" shapeId="0" xr:uid="{E8742F7E-8B8E-40B8-88FA-1BF58FA61E56}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Connect with GD onshore team_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Connect with GD onshore team</t>
       </text>
     </comment>
     <comment ref="K16" authorId="1" shapeId="0" xr:uid="{2B8B1264-9F08-40E1-9040-B79527887B45}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri</t>
       </text>
     </comment>
     <comment ref="K17" authorId="2" shapeId="0" xr:uid="{B23C388E-2E4B-496D-A7D5-EFA61D303073}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel</t>
       </text>
     </comment>
     <comment ref="K22" authorId="3" shapeId="0" xr:uid="{6A7DE910-52BF-4905-9039-3376F875BE51}">
       <text>
-        <r>
-          <rPr>
-            <rFont val="Aptos Narrow"/>
-            <sz val="11"/>
-          </rPr>
-          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Tech Sync calls are there with onshore GD teams_x000A_</t>
-        </r>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Tech Sync calls are there with onshore GD teams</t>
       </text>
     </comment>
   </commentList>
@@ -173,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3556" uniqueCount="797">
   <si>
     <t>SrNo</t>
   </si>
@@ -391,7 +370,7 @@
     <t>Firewire Modernization 2.0</t>
   </si>
   <si>
-    <t xml:space="preserve">We are going through KT videos.
+    <t>We are going through KT videos.
 Delivery not started yet.</t>
   </si>
   <si>
@@ -629,7 +608,7 @@
     <t>In progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Client compliance Training Completed ,  Started working on Project Task</t>
+    <t>Client compliance Training Completed ,  Started working on Project Task</t>
   </si>
   <si>
     <t>Anand Maurya</t>
@@ -1006,7 +985,7 @@
     <t>Alex</t>
   </si>
   <si>
-    <t xml:space="preserve">VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
+    <t>VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
   </si>
   <si>
     <t>Abinesh C</t>
@@ -1121,7 +1100,7 @@
     <t>JIRA</t>
   </si>
   <si>
-    <t xml:space="preserve">VDI  received</t>
+    <t>VDI  received</t>
   </si>
   <si>
     <t>Kammeta, Prathap</t>
@@ -1142,7 +1121,7 @@
     <t>Inprogress</t>
   </si>
   <si>
-    <t xml:space="preserve">VDI Setup Done, Required tools setup completed (Ready API, JMeter)
+    <t>VDI Setup Done, Required tools setup completed (Ready API, JMeter)
 Client compliance email not received</t>
   </si>
   <si>
@@ -1179,7 +1158,7 @@
     <t>Mathew Romstadt</t>
   </si>
   <si>
-    <t xml:space="preserve">DUO setup done. VDI is accessible.
+    <t>DUO setup done. VDI is accessible.
 Received Compliance training email. Completed compliance training.
 Raised AG tickets for Confluence, Github and ReadyAPI.
 VDI setup done</t>
@@ -1536,16 +1515,19 @@
     <t>97987698076</t>
   </si>
   <si>
-    <t>Ramesh Saharan</t>
-  </si>
-  <si>
-    <t>rasaharan@deloitte.com</t>
-  </si>
-  <si>
-    <t>Will start working next week</t>
-  </si>
-  <si>
-    <t>8746848938</t>
+    <t>Ravi Kishan</t>
+  </si>
+  <si>
+    <t>rkishan@deloitte.com</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>Completing Onboarded Formalities.</t>
+  </si>
+  <si>
+    <t>7648786737</t>
   </si>
   <si>
     <t>UserID</t>
@@ -1590,10 +1572,7 @@
     <t>Admin@789</t>
   </si>
   <si>
-    <t>pefernandes2@deloitte.com</t>
-  </si>
-  <si>
-    <t>Pearlfer@96</t>
+    <t>Jarla@123</t>
   </si>
   <si>
     <t>FALSE</t>
@@ -1689,9 +1668,6 @@
     <t>2026-09-05</t>
   </si>
   <si>
-    <t>2026-09-04</t>
-  </si>
-  <si>
     <t>2026-09-08</t>
   </si>
   <si>
@@ -1716,7 +1692,7 @@
     <t>Contract Ended</t>
   </si>
   <si>
-    <t>Did not Joined</t>
+    <t>Not part of the team.</t>
   </si>
   <si>
     <t>TrainingID</t>
@@ -1737,12 +1713,6 @@
     <t>ROVO</t>
   </si>
   <si>
-    <t>2026-10-30</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
     <t>Github Copilot</t>
   </si>
   <si>
@@ -1755,9 +1725,6 @@
     <t>2026-09-03</t>
   </si>
   <si>
-    <t>2026-09-02</t>
-  </si>
-  <si>
     <t>Project name</t>
   </si>
   <si>
@@ -1776,26 +1743,26 @@
     <t>Has Team Member(s) in ADMX? (Y/N)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scrum Master
+    <t>Scrum Master
 (Offshore)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scrum Master
+    <t>Scrum Master
 (Onshore / GD)</t>
   </si>
   <si>
-    <t xml:space="preserve">Scrum Master
+    <t>Scrum Master
 (Release)</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal Meeting Cadence 
+    <t>Internal Meeting Cadence 
 (If has Team in USA / ADMX)</t>
   </si>
   <si>
     <t>Rekha/Meenakshi</t>
   </si>
   <si>
-    <t xml:space="preserve">M,T,TH,F - 10:30 - 11:00 PM IST 
+    <t>M,T,TH,F - 10:30 - 11:00 PM IST 
 USA : Daily Connect with Michael Griffin  
 Mexico : Daily Connect with Jesus Enrique Rivera Hernandez</t>
   </si>
@@ -1927,29 +1894,30 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
       </rPr>
-      <t>Team Member Available for _x000A_W/E 21st</t>
+      <t>Team Member Available for 
+W/E 21st</t>
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> June</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> Support</t>
     </r>
@@ -1961,7 +1929,7 @@
     <t>Track Name</t>
   </si>
   <si>
-    <t xml:space="preserve">PROD Support Applicable 
+    <t>PROD Support Applicable 
 (Y/N)</t>
   </si>
   <si>
@@ -2268,7 +2236,7 @@
     <t>Total No. of Resources</t>
   </si>
   <si>
-    <t xml:space="preserve">Additional Tools  Access requested specific to skillset</t>
+    <t>Additional Tools  Access requested specific to skillset</t>
   </si>
   <si>
     <t>Key Highlights</t>
@@ -2282,10 +2250,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Firewire: Github, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2296,10 +2264,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Both resources are going through KT recordings.</t>
     </r>
@@ -2310,10 +2278,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Access to Github, Sciforma are pending for one resource</t>
     </r>
@@ -2327,10 +2295,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>ArcPlatform: Confluence, VS2022 (.Net Framework &amp; .Net Core), GitHub, GitHub Copilot, DB Access - Non/ Prod, DataDog, Team City, Octopus, Azure DevOps, Prod VDI, ActiveBatch, CosmosDB, RedShift, SSMS</t>
     </r>
@@ -2341,10 +2309,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">One resource pending with Dev environment setup in progress and started with the KT confluence page &amp; recordings. </t>
     </r>
@@ -2355,10 +2323,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Github, Informatica, AWS Redshift</t>
     </r>
@@ -2369,10 +2337,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Currently progressing on project deliverables for OnePay Wallet</t>
     </r>
@@ -2383,10 +2351,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>DC1 (prod server), Informatica POC (Shared path for code), Azure SQL DB, Microsoft SQL Server</t>
     </r>
@@ -2397,10 +2365,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>2 of 3 resources are working on prod support</t>
     </r>
@@ -2414,20 +2382,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>IDE</t>
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>: Android Studio for Android, and XCode for iOS</t>
     </r>
@@ -2438,10 +2406,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Received macOS VDI details, but unable to access due to IP address issue (GD team is working on the resolution).</t>
     </r>
@@ -2452,20 +2420,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">Github: </t>
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Copilot access if being used by client</t>
     </r>
@@ -2476,10 +2444,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Going through KT and Onboarding contents. Project delivery is yet to start. Further info on Project Delivery after today's client connect</t>
     </r>
@@ -2490,20 +2458,20 @@
     </r>
     <r>
       <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Git GUI tool:</t>
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve"> Sourcetree or Github Desktop</t>
     </r>
@@ -2517,10 +2485,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>Git Hub, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2531,10 +2499,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>2 resources are Working on the Legacy Non-Prod &amp; PRD Deployments.</t>
     </r>
@@ -2545,10 +2513,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>2 resources are awaiting VDI access.</t>
     </r>
@@ -2559,10 +2527,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>VS code and JIRA</t>
     </r>
@@ -2573,10 +2541,10 @@
     </r>
     <r>
       <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="10.5"/>
       </rPr>
       <t>One resource is going through KT videos and started on JIRA story TAX-72949 from Sprint 141 and other resource is yet to start.</t>
     </r>
@@ -2745,14 +2713,15 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)_x000A_</t>
+      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
       <t>Only Section 1 - 4</t>
     </r>
@@ -2762,14 +2731,15 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code_x000A_</t>
+      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
       <t>Only Section Introducing Thread Locking</t>
     </r>
@@ -2779,16 +2749,22 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Learn Parallel Programming with C# and .NET_x000A_</t>
+      <t xml:space="preserve">Learn Parallel Programming with C# and .NET
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
-      <t>Only Sections:_x000A_- Task Programing_x000A_- Concurrent Collection_x000A_- [Optional] Task Coordination_x000A_- Async Programming_x000A_+ Task.WhenAll(), Task.WhenAny()</t>
+      <t>Only Sections:
+- Task Programing
+- Concurrent Collection
+- [Optional] Task Coordination
+- Async Programming
++ Task.WhenAll(), Task.WhenAny()</t>
     </r>
   </si>
   <si>
@@ -2796,14 +2772,15 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide_x000A_</t>
+      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
       <t>Only Section 4 Middleware</t>
     </r>
@@ -2826,21 +2803,23 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">RabbitMQ and Messaging Concepts_x000A_</t>
+      <t xml:space="preserve">RabbitMQ and Messaging Concepts
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
-      <t>Only Section:_x000A_[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
+      <t>Only Section:
+[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
     </r>
   </si>
   <si>
@@ -2860,16 +2839,18 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Modern dotnet testing_x000A_</t>
+      <t xml:space="preserve">Modern dotnet testing
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
-        <color rgb="FFFF0000"/>
-        <sz val="11"/>
       </rPr>
-      <t>Only Section:_x000A_Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
+      <t>Only Section:
+Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
     </r>
   </si>
   <si>
@@ -2940,8 +2921,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="35">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3167,6 +3147,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -3177,13 +3170,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.3999755851924192"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3225,7 +3218,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3237,13 +3230,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3772,667 +3765,664 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="337">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="17" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="18" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="18" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0"/>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="18" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="18" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="1" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="16" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="23" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="21" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="8" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="26" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="14" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="21" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="22" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="15" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
-    <xf numFmtId="16" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="11" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="30" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" applyFont="1" fillId="15" applyFill="1" borderId="4" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="16" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="1"/>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="15" fontId="20" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="27" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" applyFont="1" fillId="16" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="39" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="36" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="37" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4652,8 +4642,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Mandatory Trainings"/>
       <sheetName val="List of Projects"/>
@@ -4677,7 +4670,6 @@
       <sheetName val="ETL"/>
       <sheetName val="Sheet2"/>
     </sheetNames>
-    <definedNames/>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
@@ -6622,14 +6614,14 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5952C43C-8246-4EC2-A258-48BB4CDE7E1C}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:C11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
+    <pivotField axis="axisCol" showAll="0">
       <items count="6">
         <item x="1"/>
         <item h="1" x="0"/>
@@ -6639,8 +6631,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="11">
         <item m="1" x="9"/>
         <item x="2"/>
@@ -6655,7 +6647,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
+    <pivotField dataField="1" showAll="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -6668,7 +6660,7 @@
     <dataField name="Count of Level - Original" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="16">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6688,11 +6680,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94E0152F-0BF3-438D-8873-7B4459136091}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:D17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -6700,7 +6692,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField axis="axisRow" showAll="0">
       <items count="18">
         <item x="0"/>
         <item x="2"/>
@@ -6722,18 +6714,18 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
@@ -6745,35 +6737,35 @@
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="16">
+    <format dxfId="25">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="23">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="22">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="21">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="20">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
@@ -6800,11 +6792,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2BDA4149-0E05-4180-8484-88A33678FB6E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A23:E38" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -6812,7 +6804,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField axis="axisRow" showAll="0">
       <items count="18">
         <item x="0"/>
         <item x="2"/>
@@ -6834,9 +6826,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
       <items count="5">
         <item x="0"/>
         <item x="1"/>
@@ -6845,15 +6837,15 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
@@ -6865,35 +6857,35 @@
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="16">
+    <format dxfId="34">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="33">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="32">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="31">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="30">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="29">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6913,10 +6905,10 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EDF3A7DE-9201-4E1B-B165-09BBC2FC53FB}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A50:F56" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="30">
-    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
       <items count="5">
         <item x="2"/>
         <item x="0"/>
@@ -6925,8 +6917,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
       <items count="19">
         <item m="1" x="17"/>
         <item x="2"/>
@@ -6949,9 +6941,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="2"/>
         <item x="1"/>
@@ -6960,27 +6952,27 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="8"/>
@@ -7007,11 +6999,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{489EF034-6C39-4528-AA56-4CC8CE7F55D5}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="37">
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisPage" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
       <items count="4">
         <item x="1"/>
         <item x="2"/>
@@ -7019,10 +7011,10 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="13">
         <item x="2"/>
         <item x="1"/>
@@ -7039,34 +7031,34 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
-    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="8"/>
@@ -7444,7 +7436,7 @@
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
     <col min="3" max="3" width="29.1796875" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="10.08984375" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
     <col min="9" max="9" width="13.54296875" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
@@ -7466,7 +7458,7 @@
     <col min="35" max="35" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
@@ -7573,7 +7565,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" s="87">
         <v>1</v>
       </c>
@@ -7648,7 +7640,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" s="71">
         <v>2</v>
       </c>
@@ -7720,7 +7712,7 @@
       </c>
       <c r="AH3" s="71"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" s="71">
         <v>3</v>
       </c>
@@ -7818,7 +7810,7 @@
       </c>
       <c r="AH4" s="71"/>
     </row>
-    <row r="5" ht="43.5">
+    <row r="5" spans="1:35" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="71">
         <v>4</v>
       </c>
@@ -7918,7 +7910,7 @@
       </c>
       <c r="AH5" s="71"/>
     </row>
-    <row r="6" ht="101.5">
+    <row r="6" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A6" s="71">
         <v>5</v>
       </c>
@@ -8018,7 +8010,7 @@
       </c>
       <c r="AH6" s="71"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" s="71">
         <v>6</v>
       </c>
@@ -8031,16 +8023,16 @@
       <c r="D7" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>82</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" t="s">
         <v>39</v>
       </c>
       <c r="I7" s="94" t="s">
@@ -8116,7 +8108,7 @@
       </c>
       <c r="AH7" s="71"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A8" s="71">
         <v>7</v>
       </c>
@@ -8208,7 +8200,7 @@
       </c>
       <c r="AH8" s="71"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" s="71">
         <v>8</v>
       </c>
@@ -8300,7 +8292,7 @@
       </c>
       <c r="AH9" s="71"/>
     </row>
-    <row r="10" ht="87">
+    <row r="10" spans="1:35" ht="87" x14ac:dyDescent="0.35">
       <c r="A10" s="87">
         <v>9</v>
       </c>
@@ -8372,7 +8364,7 @@
       </c>
       <c r="AH10" s="108"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" s="71">
         <v>10</v>
       </c>
@@ -8391,10 +8383,10 @@
       <c r="F11" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="G11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="0" t="s">
+      <c r="H11" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="94" t="s">
@@ -8470,7 +8462,7 @@
       </c>
       <c r="AH11" s="94"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" s="71">
         <v>11</v>
       </c>
@@ -8570,7 +8562,7 @@
       </c>
       <c r="AH12" s="94"/>
     </row>
-    <row r="13" ht="101.5">
+    <row r="13" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A13" s="71">
         <v>12</v>
       </c>
@@ -8668,7 +8660,7 @@
       </c>
       <c r="AH13" s="94"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" s="87">
         <v>13</v>
       </c>
@@ -8754,7 +8746,7 @@
       </c>
       <c r="AH14" s="89"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" s="71">
         <v>14</v>
       </c>
@@ -8846,7 +8838,7 @@
       </c>
       <c r="AH15" s="94"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" s="71">
         <v>15</v>
       </c>
@@ -8940,7 +8932,7 @@
       </c>
       <c r="AH16" s="94"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A17" s="71">
         <v>16</v>
       </c>
@@ -8959,7 +8951,7 @@
       <c r="F17" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="G17" t="s">
         <v>101</v>
       </c>
       <c r="H17" s="114" t="s">
@@ -8983,7 +8975,7 @@
       <c r="N17" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O17" s="0" t="s">
+      <c r="O17" t="s">
         <v>125</v>
       </c>
       <c r="P17" s="71" t="s">
@@ -9040,7 +9032,7 @@
       </c>
       <c r="AH17" s="94"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A18" s="71">
         <v>17</v>
       </c>
@@ -9059,7 +9051,7 @@
       <c r="F18" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="G18" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="71" t="s">
@@ -9134,7 +9126,7 @@
       </c>
       <c r="AH18" s="94"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A19" s="71">
         <v>18</v>
       </c>
@@ -9230,7 +9222,7 @@
       </c>
       <c r="AH19" s="94"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A20" s="71">
         <v>19</v>
       </c>
@@ -9324,7 +9316,7 @@
       </c>
       <c r="AH20" s="94"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A21" s="87">
         <v>20</v>
       </c>
@@ -9416,7 +9408,7 @@
       </c>
       <c r="AH21" s="89"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A22" s="71">
         <v>21</v>
       </c>
@@ -9512,7 +9504,7 @@
       </c>
       <c r="AH22" s="94"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A23" s="71">
         <v>22</v>
       </c>
@@ -9534,7 +9526,7 @@
       <c r="G23" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="H23" t="s">
         <v>149</v>
       </c>
       <c r="I23" s="115" t="s">
@@ -9610,7 +9602,7 @@
       </c>
       <c r="AH23" s="94"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A24" s="71">
         <v>23</v>
       </c>
@@ -9629,7 +9621,7 @@
       <c r="F24" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="G24" t="s">
         <v>101</v>
       </c>
       <c r="H24" s="71" t="s">
@@ -9700,7 +9692,7 @@
       </c>
       <c r="AH24" s="94"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A25" s="71">
         <v>24</v>
       </c>
@@ -9743,7 +9735,7 @@
       <c r="N25" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O25" s="0" t="s">
+      <c r="O25" t="s">
         <v>125</v>
       </c>
       <c r="P25" s="71" t="s">
@@ -9798,7 +9790,7 @@
       </c>
       <c r="AH25" s="94"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A26" s="71">
         <v>25</v>
       </c>
@@ -9811,13 +9803,13 @@
       <c r="D26" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="E26" t="s">
         <v>50</v>
       </c>
       <c r="F26" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="G26" t="s">
         <v>101</v>
       </c>
       <c r="H26" s="71" t="s">
@@ -9889,7 +9881,7 @@
         <v>9619484828</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27" s="71">
         <v>26</v>
       </c>
@@ -9987,7 +9979,7 @@
       </c>
       <c r="AH27" s="94"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28" s="71">
         <v>27</v>
       </c>
@@ -10087,7 +10079,7 @@
       </c>
       <c r="AH28" s="94"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29" s="87">
         <v>28</v>
       </c>
@@ -10185,7 +10177,7 @@
       </c>
       <c r="AH29" s="127"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A30" s="71">
         <v>29</v>
       </c>
@@ -10275,7 +10267,7 @@
       </c>
       <c r="AH30" s="94"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A31" s="71">
         <v>30</v>
       </c>
@@ -10372,7 +10364,7 @@
         <v>7353336812</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A32" s="71">
         <v>31</v>
       </c>
@@ -10468,7 +10460,7 @@
       </c>
       <c r="AH32" s="136"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A33" s="71">
         <v>32</v>
       </c>
@@ -10564,7 +10556,7 @@
       </c>
       <c r="AH33" s="113"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A34" s="71">
         <v>33</v>
       </c>
@@ -10660,7 +10652,7 @@
       </c>
       <c r="AH34" s="94"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A35" s="71">
         <v>34</v>
       </c>
@@ -10703,7 +10695,7 @@
       <c r="N35" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O35" s="0" t="s">
+      <c r="O35" t="s">
         <v>125</v>
       </c>
       <c r="P35" s="71" t="s">
@@ -10754,7 +10746,7 @@
       </c>
       <c r="AH35" s="94"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A36" s="87">
         <v>35</v>
       </c>
@@ -10846,7 +10838,7 @@
       </c>
       <c r="AH36" s="89"/>
     </row>
-    <row r="37" ht="87">
+    <row r="37" spans="1:34" ht="87" x14ac:dyDescent="0.35">
       <c r="A37" s="71">
         <v>36</v>
       </c>
@@ -10943,7 +10935,7 @@
         <v>7023147061</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A38" s="71">
         <v>37</v>
       </c>
@@ -11039,7 +11031,7 @@
       </c>
       <c r="AH38" s="94"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A39" s="71">
         <v>38</v>
       </c>
@@ -11082,7 +11074,7 @@
       <c r="N39" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O39" s="0" t="s">
+      <c r="O39" t="s">
         <v>125</v>
       </c>
       <c r="P39" s="71" t="s">
@@ -11131,7 +11123,7 @@
       </c>
       <c r="AH39" s="71"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A40" s="71">
         <v>39</v>
       </c>
@@ -11227,7 +11219,7 @@
       </c>
       <c r="AH40" s="71"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A41" s="87">
         <v>40</v>
       </c>
@@ -11311,7 +11303,7 @@
       </c>
       <c r="AH41" s="87"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A42" s="71">
         <v>41</v>
       </c>
@@ -11409,7 +11401,7 @@
       </c>
       <c r="AH42" s="71"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A43" s="119">
         <v>42</v>
       </c>
@@ -11505,7 +11497,7 @@
       </c>
       <c r="AH43" s="119"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A44" s="87">
         <v>43</v>
       </c>
@@ -11599,7 +11591,7 @@
       </c>
       <c r="AH44" s="87"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A45" s="119">
         <v>44</v>
       </c>
@@ -11695,7 +11687,7 @@
       </c>
       <c r="AH45" s="119"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A46" s="71">
         <v>45</v>
       </c>
@@ -11793,7 +11785,7 @@
       </c>
       <c r="AH46" s="71"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A47" s="87">
         <v>46</v>
       </c>
@@ -11881,7 +11873,7 @@
       </c>
       <c r="AH47" s="87"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A48" s="87">
         <v>47</v>
       </c>
@@ -11967,7 +11959,7 @@
       </c>
       <c r="AH48" s="87"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A49" s="71">
         <v>48</v>
       </c>
@@ -12063,7 +12055,7 @@
       </c>
       <c r="AH49" s="71"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A50" s="71">
         <v>49</v>
       </c>
@@ -12161,7 +12153,7 @@
       </c>
       <c r="AH50" s="71"/>
     </row>
-    <row r="51" ht="29">
+    <row r="51" spans="1:34" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="100">
         <v>50</v>
       </c>
@@ -12257,7 +12249,7 @@
       </c>
       <c r="AH51" s="100"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A52" s="71">
         <v>51</v>
       </c>
@@ -12353,7 +12345,7 @@
       </c>
       <c r="AH52" s="71"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A53" s="71">
         <v>52</v>
       </c>
@@ -12449,7 +12441,7 @@
       </c>
       <c r="AH53" s="71"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A54" s="87">
         <v>53</v>
       </c>
@@ -12543,7 +12535,7 @@
       </c>
       <c r="AH54" s="87"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A55" s="87">
         <v>54</v>
       </c>
@@ -12627,7 +12619,7 @@
       </c>
       <c r="AH55" s="87"/>
     </row>
-    <row r="56" ht="58">
+    <row r="56" spans="1:34" ht="58" x14ac:dyDescent="0.35">
       <c r="A56" s="71">
         <v>55</v>
       </c>
@@ -12721,7 +12713,7 @@
       </c>
       <c r="AH56" s="71"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A57" s="71">
         <v>56</v>
       </c>
@@ -12815,7 +12807,7 @@
       </c>
       <c r="AH57" s="71"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A58" s="87">
         <v>57</v>
       </c>
@@ -12909,7 +12901,7 @@
       </c>
       <c r="AH58" s="87"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A59" s="71">
         <v>58</v>
       </c>
@@ -13001,7 +12993,7 @@
       </c>
       <c r="AH59" s="71"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A60" s="71">
         <v>59</v>
       </c>
@@ -13044,7 +13036,7 @@
       <c r="N60" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O60" s="0" t="s">
+      <c r="O60" t="s">
         <v>125</v>
       </c>
       <c r="P60" s="71" t="s">
@@ -13097,7 +13089,7 @@
       </c>
       <c r="AH60" s="71"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A61" s="87">
         <v>60</v>
       </c>
@@ -13169,7 +13161,7 @@
       </c>
       <c r="AH61" s="87"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A62" s="71">
         <v>61</v>
       </c>
@@ -13265,7 +13257,7 @@
       </c>
       <c r="AH62" s="71"/>
     </row>
-    <row r="63" ht="29">
+    <row r="63" spans="1:34" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="71">
         <v>62</v>
       </c>
@@ -13363,7 +13355,7 @@
       </c>
       <c r="AH63" s="71"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A64" s="71">
         <v>63</v>
       </c>
@@ -13461,7 +13453,7 @@
       </c>
       <c r="AH64" s="71"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A65" s="87">
         <v>64</v>
       </c>
@@ -13545,7 +13537,7 @@
       </c>
       <c r="AH65" s="87"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A66" s="119">
         <v>65</v>
       </c>
@@ -13594,7 +13586,7 @@
       <c r="P66" s="157" t="s">
         <v>306</v>
       </c>
-      <c r="Q66" s="0" t="s">
+      <c r="Q66" t="s">
         <v>307</v>
       </c>
       <c r="R66" s="119" t="s">
@@ -13641,7 +13633,7 @@
       </c>
       <c r="AH66" s="119"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A67" s="87">
         <v>66</v>
       </c>
@@ -13721,7 +13713,7 @@
       </c>
       <c r="AH67" s="87"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A68" s="71">
         <v>67</v>
       </c>
@@ -13817,7 +13809,7 @@
       </c>
       <c r="AH68" s="71"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A69" s="71">
         <v>68</v>
       </c>
@@ -13909,7 +13901,7 @@
       </c>
       <c r="AH69" s="71"/>
     </row>
-    <row r="70" ht="87">
+    <row r="70" spans="1:34" ht="87" x14ac:dyDescent="0.35">
       <c r="A70" s="71">
         <v>69</v>
       </c>
@@ -14009,7 +14001,7 @@
       </c>
       <c r="AH70" s="71"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A71" s="71">
         <v>70</v>
       </c>
@@ -14105,7 +14097,7 @@
       </c>
       <c r="AH71" s="71"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A72" s="119">
         <v>71</v>
       </c>
@@ -14205,7 +14197,7 @@
       </c>
       <c r="AH72" s="119"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A73" s="71">
         <v>72</v>
       </c>
@@ -14224,7 +14216,7 @@
       <c r="F73" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="G73" t="s">
         <v>101</v>
       </c>
       <c r="H73" s="71" t="s">
@@ -14305,7 +14297,7 @@
       </c>
       <c r="AH73" s="71"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A74" s="71">
         <v>73</v>
       </c>
@@ -14327,7 +14319,7 @@
       <c r="G74" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="H74" s="0" t="s">
+      <c r="H74" t="s">
         <v>52</v>
       </c>
       <c r="I74" s="94" t="s">
@@ -14405,7 +14397,7 @@
       </c>
       <c r="AH74" s="71"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A75" s="71">
         <v>74</v>
       </c>
@@ -14496,12 +14488,12 @@
       </c>
       <c r="AE75" s="71"/>
       <c r="AF75" s="71"/>
-      <c r="AG75" s="0">
+      <c r="AG75">
         <v>9746540951</v>
       </c>
       <c r="AH75" s="71"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A76" s="71">
         <v>75</v>
       </c>
@@ -14597,7 +14589,7 @@
       </c>
       <c r="AH76" s="71"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A77" s="71">
         <v>76</v>
       </c>
@@ -14685,7 +14677,7 @@
       </c>
       <c r="AH77" s="71"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A78" s="87">
         <v>77</v>
       </c>
@@ -14763,7 +14755,7 @@
       </c>
       <c r="AH78" s="87"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A79" s="87">
         <v>78</v>
       </c>
@@ -14863,7 +14855,7 @@
       </c>
       <c r="AH79" s="87"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A80" s="71">
         <v>79</v>
       </c>
@@ -14959,7 +14951,7 @@
       </c>
       <c r="AH80" s="71"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A81" s="71">
         <v>80</v>
       </c>
@@ -15057,7 +15049,7 @@
       </c>
       <c r="AH81" s="71"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A82" s="71">
         <v>81</v>
       </c>
@@ -15153,7 +15145,7 @@
       </c>
       <c r="AH82" s="71"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A83" s="71">
         <v>82</v>
       </c>
@@ -15181,7 +15173,7 @@
       <c r="I83" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="J83" s="0" t="s">
+      <c r="J83" t="s">
         <v>68</v>
       </c>
       <c r="K83" s="218">
@@ -15249,7 +15241,7 @@
       </c>
       <c r="AH83" s="71"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A84" s="222">
         <v>83</v>
       </c>
@@ -15347,7 +15339,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A85" s="230">
         <v>84</v>
       </c>
@@ -15449,7 +15441,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A86" s="230">
         <v>85</v>
       </c>
@@ -15553,7 +15545,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A87" s="230">
         <v>86</v>
       </c>
@@ -15653,7 +15645,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A88" s="230">
         <v>87</v>
       </c>
@@ -15745,7 +15737,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A89" s="128">
         <v>88</v>
       </c>
@@ -15845,7 +15837,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A90" s="252">
         <v>89</v>
       </c>
@@ -15947,7 +15939,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A91" s="252">
         <v>90</v>
       </c>
@@ -16049,7 +16041,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A92" s="252">
         <v>91</v>
       </c>
@@ -16137,7 +16129,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A93" s="252">
         <v>92</v>
       </c>
@@ -16223,7 +16215,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A94" s="252">
         <v>93</v>
       </c>
@@ -16317,7 +16309,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A95" s="252">
         <v>94</v>
       </c>
@@ -16409,7 +16401,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A96" s="261">
         <v>95</v>
       </c>
@@ -16509,7 +16501,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A97" s="268">
         <v>96</v>
       </c>
@@ -16607,7 +16599,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A98" s="71">
         <v>97</v>
       </c>
@@ -16705,7 +16697,7 @@
       </c>
       <c r="AH98" s="71"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A99" s="71">
         <v>98</v>
       </c>
@@ -16801,7 +16793,7 @@
       </c>
       <c r="AH99" s="71"/>
     </row>
-    <row r="100" ht="15">
+    <row r="100" spans="1:34" ht="15" x14ac:dyDescent="0.4">
       <c r="A100" s="71">
         <v>99</v>
       </c>
@@ -16885,235 +16877,241 @@
         <v>436</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A101" s="71">
         <v>100</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" t="s">
         <v>437</v>
       </c>
-      <c r="C101" s="0" t="s">
+      <c r="C101" t="s">
         <v>438</v>
       </c>
-      <c r="D101" s="0" t="s">
+      <c r="D101" t="s">
         <v>36</v>
       </c>
-      <c r="E101" s="0" t="s">
+      <c r="E101" t="s">
         <v>37</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="G101" t="s">
         <v>197</v>
       </c>
-      <c r="I101" s="0" t="s">
+      <c r="I101" t="s">
         <v>439</v>
       </c>
-      <c r="K101" s="0" t="s">
+      <c r="K101" t="s">
         <v>440</v>
       </c>
-      <c r="L101" s="0" t="s">
+      <c r="L101" t="s">
         <v>127</v>
       </c>
-      <c r="M101" s="0" t="s">
+      <c r="M101" t="s">
         <v>441</v>
       </c>
-      <c r="N101" s="0" t="s">
+      <c r="N101" t="s">
         <v>442</v>
       </c>
-      <c r="O101" s="0" t="s">
+      <c r="O101" t="s">
         <v>42</v>
       </c>
-      <c r="P101" s="0" t="s">
+      <c r="P101" t="s">
         <v>43</v>
       </c>
-      <c r="Q101" s="0" t="s">
+      <c r="Q101" t="s">
         <v>126</v>
       </c>
-      <c r="U101" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="V101" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="W101" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB101" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE101" s="0" t="s">
+      <c r="U101" t="s">
+        <v>45</v>
+      </c>
+      <c r="V101" t="s">
+        <v>45</v>
+      </c>
+      <c r="W101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE101" t="s">
         <v>443</v>
       </c>
-      <c r="AG101" s="0" t="s">
+      <c r="AG101" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="0">
+    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A102">
         <v>101</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" t="s">
         <v>445</v>
       </c>
-      <c r="C102" s="0" t="s">
+      <c r="C102" t="s">
         <v>446</v>
       </c>
-      <c r="D102" s="0" t="s">
+      <c r="D102" t="s">
         <v>36</v>
       </c>
-      <c r="E102" s="0" t="s">
+      <c r="E102" t="s">
         <v>50</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="G102" t="s">
         <v>197</v>
       </c>
-      <c r="I102" s="0" t="s">
+      <c r="I102" t="s">
         <v>439</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="L102" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="M102" s="0" t="s">
+      <c r="L102" t="s">
+        <v>45</v>
+      </c>
+      <c r="M102" t="s">
         <v>441</v>
       </c>
-      <c r="N102" s="0" t="s">
+      <c r="N102" t="s">
         <v>442</v>
       </c>
-      <c r="O102" s="0" t="s">
+      <c r="O102" t="s">
         <v>42</v>
       </c>
-      <c r="P102" s="0" t="s">
+      <c r="P102" t="s">
         <v>43</v>
       </c>
-      <c r="Q102" s="0" t="s">
+      <c r="Q102" t="s">
         <v>448</v>
       </c>
-      <c r="U102" s="0" t="s">
+      <c r="U102" t="s">
         <v>127</v>
       </c>
-      <c r="V102" s="0" t="s">
+      <c r="V102" t="s">
         <v>127</v>
       </c>
-      <c r="W102" s="0" t="s">
+      <c r="W102" t="s">
         <v>127</v>
       </c>
-      <c r="AB102" s="0" t="s">
+      <c r="AB102" t="s">
         <v>127</v>
       </c>
-      <c r="AE102" s="0" t="s">
+      <c r="AE102" t="s">
         <v>449</v>
       </c>
-      <c r="AG102" s="0" t="s">
+      <c r="AG102" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="0">
+    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
+      <c r="A103">
         <v>102</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" t="s">
         <v>451</v>
       </c>
-      <c r="C103" s="0" t="s">
+      <c r="C103" t="s">
         <v>452</v>
       </c>
-      <c r="D103" s="0" t="s">
+      <c r="D103" t="s">
         <v>36</v>
       </c>
-      <c r="E103" s="0" t="s">
+      <c r="E103" t="s">
         <v>50</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="G103" t="s">
         <v>197</v>
       </c>
-      <c r="I103" s="0" t="s">
+      <c r="I103" t="s">
         <v>52</v>
       </c>
-      <c r="M103" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="N103" s="0" t="s">
+      <c r="K103" t="s">
+        <v>453</v>
+      </c>
+      <c r="L103" t="s">
+        <v>45</v>
+      </c>
+      <c r="M103" t="s">
+        <v>40</v>
+      </c>
+      <c r="N103" t="s">
         <v>442</v>
       </c>
-      <c r="O103" s="0" t="s">
+      <c r="O103" t="s">
         <v>46</v>
       </c>
-      <c r="P103" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q103" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="U103" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="V103" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="W103" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB103" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="AE103" s="0" t="s">
-        <v>453</v>
-      </c>
-      <c r="AG103" s="0" t="s">
+      <c r="P103" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>169</v>
+      </c>
+      <c r="U103" t="s">
+        <v>45</v>
+      </c>
+      <c r="V103" t="s">
+        <v>45</v>
+      </c>
+      <c r="W103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE103" t="s">
         <v>454</v>
+      </c>
+      <c r="AG103" t="s">
+        <v>455</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B99">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C92 C94:C98">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C100">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16 P16:Q16">
-    <cfRule type="expression" dxfId="2" priority="12">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>$AH16=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35 Q35 O40:Q40">
-    <cfRule type="expression" dxfId="2" priority="14">
+    <cfRule type="expression" dxfId="8" priority="14">
       <formula>$AF35=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N48:P48 N49 N51 Q51 N54:Q54 N56:Q56 N65:Q65 O71 O75:Q75">
-    <cfRule type="expression" dxfId="2" priority="10">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>$AB48=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:Q14">
-    <cfRule type="expression" dxfId="2" priority="13">
+    <cfRule type="expression" dxfId="6" priority="13">
       <formula>$AG14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O57">
-    <cfRule type="expression" dxfId="2" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>$AB57=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O59:Q59">
-    <cfRule type="expression" dxfId="2" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>$AB59=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42 N42:N43 Q42:Q43">
-    <cfRule type="expression" dxfId="2" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>$AE42=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17123,106 +17121,105 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH84:AH97">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId97"/>
-    <hyperlink ref="C3" r:id="rId98"/>
-    <hyperlink ref="D3" display="mailto:abirudugadda@deloitte.com" r:id="rId99"/>
-    <hyperlink ref="C4" r:id="rId100"/>
-    <hyperlink ref="C5" r:id="rId101"/>
-    <hyperlink ref="C6" r:id="rId102"/>
-    <hyperlink ref="C7" r:id="rId103"/>
-    <hyperlink ref="C8" r:id="rId104"/>
-    <hyperlink ref="C9" r:id="rId105"/>
-    <hyperlink ref="C10" r:id="rId106"/>
-    <hyperlink ref="C11" r:id="rId107"/>
-    <hyperlink ref="C12" r:id="rId108"/>
-    <hyperlink ref="C13" r:id="rId109"/>
-    <hyperlink ref="C14" r:id="rId110"/>
-    <hyperlink ref="C15" r:id="rId111"/>
-    <hyperlink ref="C16" r:id="rId112"/>
-    <hyperlink ref="C17" r:id="rId113"/>
-    <hyperlink ref="C18" r:id="rId114"/>
-    <hyperlink ref="C19" r:id="rId115"/>
-    <hyperlink ref="C20" r:id="rId116"/>
-    <hyperlink ref="C21" r:id="rId117"/>
-    <hyperlink ref="C22" r:id="rId118"/>
-    <hyperlink ref="C23" r:id="rId119"/>
-    <hyperlink ref="C24" r:id="rId120"/>
-    <hyperlink ref="C25" r:id="rId121"/>
-    <hyperlink ref="C26" r:id="rId122"/>
-    <hyperlink ref="C27" r:id="rId123"/>
-    <hyperlink ref="C28" r:id="rId124"/>
-    <hyperlink ref="C29" r:id="rId125"/>
-    <hyperlink ref="C30" r:id="rId126"/>
-    <hyperlink ref="C31" r:id="rId127"/>
-    <hyperlink ref="C32" r:id="rId128"/>
-    <hyperlink ref="C33" r:id="rId129"/>
-    <hyperlink ref="M33" display="akalkundre@deloitte.com" r:id="rId130"/>
-    <hyperlink ref="C34" r:id="rId131"/>
-    <hyperlink ref="C35" r:id="rId132"/>
-    <hyperlink ref="C36" r:id="rId133"/>
-    <hyperlink ref="C37" r:id="rId134"/>
-    <hyperlink ref="C38" r:id="rId135"/>
-    <hyperlink ref="P38" r:id="rId136"/>
-    <hyperlink ref="C39" r:id="rId137"/>
-    <hyperlink ref="C40" r:id="rId138"/>
-    <hyperlink ref="C41" r:id="rId139"/>
-    <hyperlink ref="C42" r:id="rId140"/>
-    <hyperlink ref="C43" r:id="rId141"/>
-    <hyperlink ref="C44" r:id="rId142"/>
-    <hyperlink ref="C45" r:id="rId143"/>
-    <hyperlink ref="C47" r:id="rId144"/>
-    <hyperlink ref="C48" r:id="rId145"/>
-    <hyperlink ref="C49" r:id="rId146"/>
-    <hyperlink ref="C50" r:id="rId147"/>
-    <hyperlink ref="C51" r:id="rId148"/>
-    <hyperlink ref="C52" r:id="rId149"/>
-    <hyperlink ref="C53" display="mailto:visviswanathan@deloitte.com" r:id="rId150"/>
-    <hyperlink ref="C54" r:id="rId151"/>
-    <hyperlink ref="C55" r:id="rId152"/>
-    <hyperlink ref="C56" r:id="rId153"/>
-    <hyperlink ref="C57" r:id="rId154"/>
-    <hyperlink ref="C58" r:id="rId155"/>
-    <hyperlink ref="C59" r:id="rId156"/>
-    <hyperlink ref="C61" r:id="rId157"/>
-    <hyperlink ref="C62" r:id="rId158"/>
-    <hyperlink ref="C63" r:id="rId159"/>
-    <hyperlink ref="C64" r:id="rId160"/>
-    <hyperlink ref="C66" r:id="rId161"/>
-    <hyperlink ref="C67" r:id="rId162"/>
-    <hyperlink ref="C68" r:id="rId163"/>
-    <hyperlink ref="C69" r:id="rId164"/>
-    <hyperlink ref="C71" r:id="rId165"/>
-    <hyperlink ref="C72" r:id="rId166"/>
-    <hyperlink ref="C73" r:id="rId167"/>
-    <hyperlink ref="C75" r:id="rId168"/>
-    <hyperlink ref="C76" r:id="rId169"/>
-    <hyperlink ref="C79" r:id="rId170"/>
-    <hyperlink ref="C80" r:id="rId171"/>
-    <hyperlink ref="C82" r:id="rId172"/>
-    <hyperlink ref="C83" r:id="rId173"/>
-    <hyperlink ref="C84" r:id="rId174"/>
-    <hyperlink ref="C85" r:id="rId175"/>
-    <hyperlink ref="C86" r:id="rId176"/>
-    <hyperlink ref="C87" r:id="rId177"/>
-    <hyperlink ref="C88" r:id="rId178"/>
-    <hyperlink ref="C89" r:id="rId179"/>
-    <hyperlink ref="C90" r:id="rId180"/>
-    <hyperlink ref="C91" r:id="rId181"/>
-    <hyperlink ref="C92" r:id="rId182"/>
-    <hyperlink ref="C93" r:id="rId183"/>
-    <hyperlink ref="C94" r:id="rId184"/>
-    <hyperlink ref="C95" r:id="rId185"/>
-    <hyperlink ref="C96" r:id="rId186"/>
-    <hyperlink ref="C97" r:id="rId187"/>
-    <hyperlink ref="C99" r:id="rId188"/>
-    <hyperlink ref="C100" r:id="rId189"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D3" r:id="rId3" display="mailto:abirudugadda@deloitte.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="M33" r:id="rId34" display="akalkundre@deloitte.com" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="P38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C39" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C40" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C41" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="C43" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="C44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="C45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="C51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="C52" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="C53" r:id="rId54" display="mailto:visviswanathan@deloitte.com" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="C54" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="C55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="C56" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="C57" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="C58" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="C59" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="C61" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="C62" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="C63" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="C64" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="C66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="C67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="C68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="C69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="C71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="C72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="C73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="C75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="C76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="C79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="C80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="C82" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="C83" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="C84" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="C85" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="C86" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="C87" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="C88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="C89" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="C90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="C91" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="C92" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="C93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="C94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="C95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="C96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="C97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="C99" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="C100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId94"/>
 </worksheet>
 </file>
@@ -17237,26 +17234,26 @@
     <col min="3" max="3" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>638</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="B2" s="0" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="80" t="s">
         <v>36</v>
       </c>
@@ -17267,7 +17264,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="82" t="s">
         <v>56</v>
       </c>
@@ -17278,7 +17275,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="82" t="s">
         <v>38</v>
       </c>
@@ -17289,7 +17286,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="82" t="s">
         <v>106</v>
       </c>
@@ -17300,7 +17297,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="82" t="s">
         <v>51</v>
       </c>
@@ -17311,7 +17308,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="82" t="s">
         <v>82</v>
       </c>
@@ -17322,7 +17319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="82" t="s">
         <v>101</v>
       </c>
@@ -17333,7 +17330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="82" t="s">
         <v>197</v>
       </c>
@@ -17344,9 +17341,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="80" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B11" s="78">
         <v>84</v>
@@ -17357,7 +17354,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -17372,24 +17368,24 @@
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="78" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="78" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>127</v>
@@ -17398,10 +17394,10 @@
         <v>45</v>
       </c>
       <c r="D3" s="78" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="78" t="s">
         <v>40</v>
       </c>
@@ -17415,7 +17411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="78" t="s">
         <v>75</v>
       </c>
@@ -17427,7 +17423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="78" t="s">
         <v>110</v>
       </c>
@@ -17439,7 +17435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="78" t="s">
         <v>58</v>
       </c>
@@ -17451,7 +17447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="78" t="s">
         <v>95</v>
       </c>
@@ -17463,7 +17459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="78" t="s">
         <v>113</v>
       </c>
@@ -17475,7 +17471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="78" t="s">
         <v>374</v>
       </c>
@@ -17487,7 +17483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="78" t="s">
         <v>123</v>
       </c>
@@ -17499,7 +17495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="78" t="s">
         <v>86</v>
       </c>
@@ -17511,7 +17507,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="78" t="s">
         <v>174</v>
       </c>
@@ -17523,7 +17519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="78" t="s">
         <v>211</v>
       </c>
@@ -17535,7 +17531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="78" t="s">
         <v>219</v>
       </c>
@@ -17547,7 +17543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="78" t="s">
         <v>228</v>
       </c>
@@ -17559,9 +17555,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="78" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B17" s="78">
         <v>6</v>
@@ -17573,35 +17569,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18">
-      <c r="D18" s="0" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D18" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="22">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="77" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="78" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B23" s="78" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C23" s="78"/>
       <c r="D23" s="78"/>
       <c r="E23" s="78"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="78" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B24" s="78" t="s">
         <v>83</v>
@@ -17613,10 +17609,10 @@
         <v>61</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="78" t="s">
         <v>40</v>
       </c>
@@ -17631,7 +17627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="78" t="s">
         <v>75</v>
       </c>
@@ -17644,7 +17640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="78" t="s">
         <v>110</v>
       </c>
@@ -17657,7 +17653,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="78" t="s">
         <v>58</v>
       </c>
@@ -17670,7 +17666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="78" t="s">
         <v>95</v>
       </c>
@@ -17683,7 +17679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="78" t="s">
         <v>113</v>
       </c>
@@ -17698,7 +17694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="78" t="s">
         <v>374</v>
       </c>
@@ -17713,7 +17709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="78" t="s">
         <v>123</v>
       </c>
@@ -17728,7 +17724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="78" t="s">
         <v>86</v>
       </c>
@@ -17743,7 +17739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="78" t="s">
         <v>174</v>
       </c>
@@ -17756,7 +17752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="78" t="s">
         <v>211</v>
       </c>
@@ -17769,7 +17765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="78" t="s">
         <v>219</v>
       </c>
@@ -17782,7 +17778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="78" t="s">
         <v>228</v>
       </c>
@@ -17795,9 +17791,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="78" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B38" s="78">
         <v>24</v>
@@ -17812,162 +17808,162 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="78" t="s">
+        <v>642</v>
+      </c>
+      <c r="B41" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B42" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B43" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B44" t="s">
         <v>646</v>
       </c>
-      <c r="B41" s="0" t="s">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="79" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="0" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>639</v>
+      </c>
+      <c r="B50" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>636</v>
+      </c>
+      <c r="B51" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="0" t="s">
+      <c r="C51" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" t="s">
         <v>649</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="0" t="s">
+      <c r="E51" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="79" t="s">
+      <c r="F51" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="80" t="s">
         <v>651</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>643</v>
-      </c>
-      <c r="B50" s="0" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="B51" s="0" t="s">
+      <c r="B52">
+        <v>5</v>
+      </c>
+      <c r="C52">
+        <v>14</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="80" t="s">
         <v>652</v>
       </c>
-      <c r="C51" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" s="0" t="s">
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="F53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="80" t="s">
         <v>653</v>
       </c>
-      <c r="E51" s="0" t="s">
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>29</v>
+      </c>
+      <c r="D54">
+        <v>5</v>
+      </c>
+      <c r="F54">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="80" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="80" t="s">
+        <v>637</v>
+      </c>
+      <c r="B56">
+        <v>6</v>
+      </c>
+      <c r="C56">
+        <v>51</v>
+      </c>
+      <c r="D56">
+        <v>6</v>
+      </c>
+      <c r="F56">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="70" t="s">
         <v>654</v>
-      </c>
-      <c r="F51" s="0" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="80" t="s">
-        <v>655</v>
-      </c>
-      <c r="B52" s="0">
-        <v>5</v>
-      </c>
-      <c r="C52" s="0">
-        <v>14</v>
-      </c>
-      <c r="D52" s="0">
-        <v>1</v>
-      </c>
-      <c r="F52" s="0">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="80" t="s">
-        <v>656</v>
-      </c>
-      <c r="C53" s="0">
-        <v>8</v>
-      </c>
-      <c r="F53" s="0">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="80" t="s">
-        <v>657</v>
-      </c>
-      <c r="B54" s="0">
-        <v>1</v>
-      </c>
-      <c r="C54" s="0">
-        <v>29</v>
-      </c>
-      <c r="D54" s="0">
-        <v>5</v>
-      </c>
-      <c r="F54" s="0">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="80" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="80" t="s">
-        <v>641</v>
-      </c>
-      <c r="B56" s="0">
-        <v>6</v>
-      </c>
-      <c r="C56" s="0">
-        <v>51</v>
-      </c>
-      <c r="D56" s="0">
-        <v>6</v>
-      </c>
-      <c r="F56" s="0">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="70" t="s">
-        <v>658</v>
       </c>
       <c r="B59" s="71"/>
       <c r="C59" s="71"/>
       <c r="D59" s="71"/>
       <c r="E59" s="71"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="70" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B60" s="70" t="s">
+        <v>617</v>
+      </c>
+      <c r="C60" s="70" t="s">
+        <v>618</v>
+      </c>
+      <c r="D60" s="70" t="s">
+        <v>619</v>
+      </c>
+      <c r="E60" s="70" t="s">
+        <v>620</v>
+      </c>
+      <c r="F60" s="77"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="323">
+        <v>38</v>
+      </c>
+      <c r="B61" s="71" t="s">
         <v>621</v>
-      </c>
-      <c r="C60" s="70" t="s">
-        <v>622</v>
-      </c>
-      <c r="D60" s="70" t="s">
-        <v>623</v>
-      </c>
-      <c r="E60" s="70" t="s">
-        <v>624</v>
-      </c>
-      <c r="F60" s="77"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="324">
-        <v>38</v>
-      </c>
-      <c r="B61" s="71" t="s">
-        <v>625</v>
       </c>
       <c r="C61" s="71">
         <v>12</v>
@@ -17979,10 +17975,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="325"/>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="324"/>
       <c r="B62" s="71" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C62" s="71">
         <v>9</v>
@@ -17994,10 +17990,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="326"/>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="325"/>
       <c r="B63" s="71" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C63" s="71">
         <v>27</v>
@@ -18009,30 +18005,29 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C64" s="81">
         <f>C63/(C63+D63)</f>
-        <v>0.7941176470588235</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>0.79411764705882348</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C65" s="81">
         <f>C62/(C62+D62)</f>
-        <v>0.391304347826087</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>0.39130434782608697</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C66" s="81">
         <f>C61/(C61+D61)</f>
         <v>0.34285714285714286</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A61:A63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18045,129 +18040,128 @@
     <col min="2" max="2" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>640</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B3" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>25</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B6">
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="0">
+      <c r="B7">
         <v>4</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="0">
+      <c r="B8">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="80" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="0">
+      <c r="B9">
         <v>4</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="80" t="s">
         <v>391</v>
       </c>
-      <c r="B10" s="0">
+      <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="80" t="s">
         <v>406</v>
       </c>
-      <c r="B11" s="0">
+      <c r="B11">
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="80" t="s">
         <v>357</v>
       </c>
-      <c r="B12" s="0">
+      <c r="B12">
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="80" t="s">
         <v>410</v>
       </c>
-      <c r="B13" s="0">
+      <c r="B13">
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="0">
+      <c r="B14">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="0">
+      <c r="B15">
         <v>27</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="80" t="s">
-        <v>641</v>
-      </c>
-      <c r="B16" s="0">
+        <v>637</v>
+      </c>
+      <c r="B16">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18180,108 +18174,107 @@
     <col min="2" max="3" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="291" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="291" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C1" s="291" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="2" ht="29">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="292" t="s">
         <v>198</v>
       </c>
       <c r="B2" s="293" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C2" s="294" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="292" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="295" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C3" s="294" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="4" ht="29">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="292" t="s">
         <v>141</v>
       </c>
       <c r="B4" s="293" t="s">
+        <v>660</v>
+      </c>
+      <c r="C4" s="294" t="s">
         <v>664</v>
       </c>
-      <c r="C4" s="294" t="s">
+    </row>
+    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A5" s="292" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" s="293" t="s">
+        <v>660</v>
+      </c>
+      <c r="C5" s="294" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="293" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" s="293" t="s">
+        <v>662</v>
+      </c>
+      <c r="C6" s="294" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="5" ht="58">
-      <c r="A5" s="292" t="s">
-        <v>669</v>
-      </c>
-      <c r="B5" s="293" t="s">
-        <v>664</v>
-      </c>
-      <c r="C5" s="294" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="6" ht="29">
-      <c r="A6" s="293" t="s">
-        <v>671</v>
-      </c>
-      <c r="B6" s="293" t="s">
-        <v>666</v>
-      </c>
-      <c r="C6" s="294" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="293" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="293" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C7" s="294" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="296" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="297" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C8" s="296" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="296" t="s">
         <v>113</v>
       </c>
       <c r="B9" s="297" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C9" s="296" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18294,28 +18287,27 @@
     <col min="2" max="2" width="93.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="288" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B1" s="288" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="289" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B2" s="290" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" r:id="rId1"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18331,156 +18323,156 @@
     <col min="5" max="5" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39">
+    <row r="1" spans="1:5" ht="39" x14ac:dyDescent="0.35">
       <c r="A1" s="298" t="s">
+        <v>675</v>
+      </c>
+      <c r="B1" s="299" t="s">
+        <v>676</v>
+      </c>
+      <c r="C1" s="299" t="s">
+        <v>677</v>
+      </c>
+      <c r="D1" s="299" t="s">
+        <v>678</v>
+      </c>
+      <c r="E1" s="300" t="s">
         <v>679</v>
       </c>
-      <c r="B1" s="299" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="247" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="328" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="331" t="s">
         <v>680</v>
       </c>
-      <c r="C1" s="299" t="s">
+      <c r="C2" s="331">
+        <v>2</v>
+      </c>
+      <c r="D2" s="334" t="s">
         <v>681</v>
       </c>
-      <c r="D1" s="299" t="s">
+      <c r="E2" s="301" t="s">
         <v>682</v>
       </c>
-      <c r="E1" s="300" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="329"/>
+      <c r="B3" s="333"/>
+      <c r="C3" s="333"/>
+      <c r="D3" s="335"/>
+      <c r="E3" s="302" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="2" ht="247" customHeight="1">
-      <c r="A2" s="327" t="s">
-        <v>198</v>
-      </c>
-      <c r="B2" s="329" t="s">
+    <row r="4" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="329"/>
+      <c r="B4" s="303" t="s">
         <v>684</v>
-      </c>
-      <c r="C2" s="329">
-        <v>2</v>
-      </c>
-      <c r="D2" s="331" t="s">
-        <v>685</v>
-      </c>
-      <c r="E2" s="301" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="3" ht="26.5">
-      <c r="A3" s="328"/>
-      <c r="B3" s="330"/>
-      <c r="C3" s="330"/>
-      <c r="D3" s="332"/>
-      <c r="E3" s="302" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="4" ht="156.5">
-      <c r="A4" s="328"/>
-      <c r="B4" s="303" t="s">
-        <v>688</v>
       </c>
       <c r="C4" s="303">
         <v>2</v>
       </c>
       <c r="D4" s="304" t="s">
+        <v>685</v>
+      </c>
+      <c r="E4" s="302" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="329" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="331" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="331">
+        <v>3</v>
+      </c>
+      <c r="D5" s="305" t="s">
+        <v>687</v>
+      </c>
+      <c r="E5" s="302" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="330"/>
+      <c r="B6" s="333"/>
+      <c r="C6" s="333"/>
+      <c r="D6" s="306" t="s">
         <v>689</v>
       </c>
-      <c r="E4" s="302" t="s">
+      <c r="E6" s="307" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="5" ht="39.5">
-      <c r="A5" s="328" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="329" t="s">
-        <v>261</v>
-      </c>
-      <c r="C5" s="329">
+    <row r="7" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="328" t="s">
+        <v>691</v>
+      </c>
+      <c r="B7" s="331" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="331">
         <v>3</v>
       </c>
-      <c r="D5" s="305" t="s">
-        <v>691</v>
-      </c>
-      <c r="E5" s="302" t="s">
+      <c r="D7" s="305" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="6" ht="65.5">
-      <c r="A6" s="333"/>
-      <c r="B6" s="330"/>
-      <c r="C6" s="330"/>
-      <c r="D6" s="306" t="s">
+      <c r="E7" s="301" t="s">
         <v>693</v>
       </c>
-      <c r="E6" s="307" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="329"/>
+      <c r="B8" s="332"/>
+      <c r="C8" s="332"/>
+      <c r="D8" s="308" t="s">
         <v>694</v>
       </c>
-    </row>
-    <row r="7" ht="52.5">
-      <c r="A7" s="327" t="s">
+      <c r="E8" s="309" t="s">
         <v>695</v>
       </c>
-      <c r="B7" s="329" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="329">
-        <v>3</v>
-      </c>
-      <c r="D7" s="305" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="330"/>
+      <c r="B9" s="333"/>
+      <c r="C9" s="333"/>
+      <c r="D9" s="306" t="s">
         <v>696</v>
       </c>
-      <c r="E7" s="301" t="s">
+      <c r="E9" s="310"/>
+    </row>
+    <row r="10" spans="1:5" ht="273" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="328" t="s">
         <v>697</v>
       </c>
-    </row>
-    <row r="8" ht="65.5">
-      <c r="A8" s="328"/>
-      <c r="B8" s="336"/>
-      <c r="C8" s="336"/>
-      <c r="D8" s="308" t="s">
+      <c r="B10" s="331" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="331">
+        <v>4</v>
+      </c>
+      <c r="D10" s="326" t="s">
         <v>698</v>
       </c>
-      <c r="E8" s="309" t="s">
+      <c r="E10" s="301" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="9" ht="39.5">
-      <c r="A9" s="333"/>
-      <c r="B9" s="330"/>
-      <c r="C9" s="330"/>
-      <c r="D9" s="306" t="s">
+    <row r="11" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="330"/>
+      <c r="B11" s="333"/>
+      <c r="C11" s="333"/>
+      <c r="D11" s="327"/>
+      <c r="E11" s="307" t="s">
         <v>700</v>
       </c>
-      <c r="E9" s="310"/>
-    </row>
-    <row r="10" ht="273" customHeight="1">
-      <c r="A10" s="327" t="s">
-        <v>701</v>
-      </c>
-      <c r="B10" s="329" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="329">
-        <v>4</v>
-      </c>
-      <c r="D10" s="334" t="s">
-        <v>702</v>
-      </c>
-      <c r="E10" s="301" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="11" ht="26.5">
-      <c r="A11" s="333"/>
-      <c r="B11" s="330"/>
-      <c r="C11" s="330"/>
-      <c r="D11" s="335"/>
-      <c r="E11" s="307" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="12" ht="65.5">
+    </row>
+    <row r="12" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A12" s="311" t="s">
         <v>110</v>
       </c>
@@ -18491,14 +18483,21 @@
         <v>2</v>
       </c>
       <c r="D12" s="304" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E12" s="312" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="14">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:B9"/>
@@ -18506,16 +18505,8 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:C11"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18528,37 +18519,36 @@
     <col min="2" max="2" width="62.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="275" t="s">
+        <v>703</v>
+      </c>
+      <c r="B1" s="276" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="71" t="s">
+        <v>704</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="s">
+        <v>706</v>
+      </c>
+      <c r="B3" s="101" t="s">
         <v>707</v>
-      </c>
-      <c r="B1" s="276" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="71" t="s">
-        <v>708</v>
-      </c>
-      <c r="B2" s="101" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="71" t="s">
-        <v>710</v>
-      </c>
-      <c r="B3" s="101" t="s">
-        <v>711</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18572,118 +18562,117 @@
     <col min="3" max="3" width="53.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>710</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>711</v>
+      </c>
+      <c r="E1" s="77" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="77" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>713</v>
       </c>
-      <c r="C1" s="77" t="s">
+      <c r="B2" t="s">
         <v>714</v>
       </c>
-      <c r="D1" s="77" t="s">
+      <c r="C2" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="E1" s="77" t="s">
+      <c r="D2" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+      <c r="E2" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="0" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B3" t="s">
         <v>718</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D3" t="s">
         <v>720</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E3" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>722</v>
+      </c>
+      <c r="B4" t="s">
+        <v>723</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D4" t="s">
+        <v>716</v>
+      </c>
+      <c r="E4" t="s">
         <v>717</v>
       </c>
-      <c r="B3" s="0" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>722</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="E3" s="0" t="s">
+      <c r="B5" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+      <c r="C5" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="D5" t="s">
         <v>727</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B6" t="s">
         <v>728</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>720</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="C6" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D6" t="s">
+        <v>730</v>
+      </c>
+      <c r="E6" t="s">
         <v>721</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>729</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>726</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>732</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>734</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>725</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="C4" r:id="rId3"/>
-    <hyperlink ref="C5" r:id="rId4"/>
-    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-1000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-1000-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-1000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18699,64 +18688,63 @@
     <col min="5" max="5" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>710</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>711</v>
+      </c>
+      <c r="E1" s="77" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="77" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>713</v>
       </c>
-      <c r="C1" s="77" t="s">
-        <v>714</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>715</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="2" ht="101.5">
-      <c r="A2" s="0" t="s">
-        <v>717</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C2" s="277" t="s">
+        <v>732</v>
+      </c>
+      <c r="D2" t="s">
+        <v>733</v>
+      </c>
+      <c r="E2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>735</v>
       </c>
-      <c r="C2" s="277" t="s">
+      <c r="B3" t="s">
+        <v>515</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>731</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>738</v>
+      <c r="D3" t="s">
+        <v>727</v>
+      </c>
+      <c r="E3" t="s">
+        <v>734</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" location="overview" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C2" r:id="rId1" location="overview" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18765,76 +18753,75 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>710</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>711</v>
+      </c>
+      <c r="E1" s="77" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="77" t="s">
-        <v>713</v>
-      </c>
-      <c r="C1" s="77" t="s">
-        <v>714</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>715</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C2" s="278" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C3" s="278" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" s="278" t="s">
         <v>739</v>
       </c>
-      <c r="C2" s="278" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>740</v>
+      </c>
+      <c r="C5" s="278" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="C3" s="278" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>740</v>
+      </c>
+      <c r="C6" s="278" t="s">
         <v>742</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>739</v>
-      </c>
-      <c r="C4" s="278" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>744</v>
-      </c>
-      <c r="C5" s="278" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>744</v>
-      </c>
-      <c r="C6" s="278" t="s">
-        <v>746</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" r:id="rId2"/>
-    <hyperlink ref="C4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" r:id="rId3"/>
-    <hyperlink ref="C5" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" r:id="rId4"/>
-    <hyperlink ref="C6" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" r:id="rId5"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1200-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" xr:uid="{00000000-0004-0000-1200-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" xr:uid="{00000000-0004-0000-1200-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" xr:uid="{00000000-0004-0000-1200-000003000000}"/>
+    <hyperlink ref="C6" r:id="rId5" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" xr:uid="{00000000-0004-0000-1200-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18847,136 +18834,135 @@
     <col min="3" max="3" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D2" s="0" t="s">
         <v>461</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
+      <c r="E2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>351</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E3" t="s">
         <v>463</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="E3" s="0" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D4" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" t="s">
+        <v>468</v>
+      </c>
+      <c r="D5" t="s">
         <v>465</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="E5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>469</v>
+      </c>
+      <c r="D6" t="s">
         <v>462</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
+      <c r="E6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>468</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>461</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>7</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="C7" s="0" t="s">
+      <c r="B7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" t="s">
         <v>470</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>464</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="D7" t="s">
+        <v>465</v>
+      </c>
+      <c r="E7" t="s">
         <v>471</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="C2" r:id="rId2"/>
-    <hyperlink ref="B3" r:id="rId3"/>
-    <hyperlink ref="C3" r:id="rId4"/>
-    <hyperlink ref="B4" r:id="rId5"/>
-    <hyperlink ref="C4" r:id="rId6"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="B4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="C4" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18990,104 +18976,103 @@
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
+        <v>708</v>
+      </c>
+      <c r="B1" s="77" t="s">
+        <v>709</v>
+      </c>
+      <c r="C1" s="77" t="s">
+        <v>710</v>
+      </c>
+      <c r="D1" s="77" t="s">
+        <v>711</v>
+      </c>
+      <c r="E1" s="77" t="s">
         <v>712</v>
       </c>
-      <c r="B1" s="77" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="336" t="s">
         <v>713</v>
       </c>
-      <c r="C1" s="77" t="s">
-        <v>714</v>
-      </c>
-      <c r="D1" s="77" t="s">
-        <v>715</v>
-      </c>
-      <c r="E1" s="77" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="2" ht="43.5">
-      <c r="A2" s="337" t="s">
+      <c r="B2" s="173" t="s">
+        <v>743</v>
+      </c>
+      <c r="C2" s="277" t="s">
+        <v>744</v>
+      </c>
+      <c r="D2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E2" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="173" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A3" s="336"/>
+      <c r="B3" s="173" t="s">
+        <v>745</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="D3" t="s">
         <v>747</v>
       </c>
-      <c r="C2" s="277" t="s">
+      <c r="E3" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>748</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>724</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="3" ht="29">
-      <c r="A3" s="337"/>
-      <c r="B3" s="173" t="s">
+      <c r="B5" t="s">
         <v>749</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D5" t="s">
+        <v>733</v>
+      </c>
+      <c r="E5" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>751</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+      <c r="B7" t="s">
         <v>752</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="C7" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D7" t="s">
         <v>754</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>737</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>755</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>756</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>758</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>721</v>
+      <c r="E7" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="1">
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-    <hyperlink ref="C5" r:id="rId3"/>
-    <hyperlink ref="C7" r:id="rId4"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1300-000001000000}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-1300-000002000000}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-1300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19100,118 +19085,117 @@
     <col min="2" max="2" width="77.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="275" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="279" t="s">
+        <v>755</v>
+      </c>
+      <c r="B2" s="280" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="281" t="s">
+        <v>757</v>
+      </c>
+      <c r="B3" s="282" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="281" t="s">
         <v>759</v>
       </c>
-      <c r="B2" s="280" t="s">
+      <c r="B4" s="282" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="3" ht="43.5">
-      <c r="A3" s="281" t="s">
+    <row r="5" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="281" t="s">
         <v>761</v>
       </c>
-      <c r="B3" s="282" t="s">
+      <c r="B5" s="283" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="4" ht="43.5">
-      <c r="A4" s="281" t="s">
+    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A6" s="281" t="s">
         <v>763</v>
       </c>
-      <c r="B4" s="282" t="s">
+      <c r="B6" s="282" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="5" ht="101.5">
-      <c r="A5" s="281" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="279" t="s">
         <v>765</v>
       </c>
-      <c r="B5" s="283" t="s">
+      <c r="B7" s="280" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="6" ht="29">
-      <c r="A6" s="281" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="279" t="s">
         <v>767</v>
       </c>
-      <c r="B6" s="282" t="s">
+      <c r="B8" s="280" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="279" t="s">
+    <row r="9" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="281" t="s">
         <v>769</v>
       </c>
-      <c r="B7" s="280" t="s">
+      <c r="B9" s="282" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="279" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="279" t="s">
         <v>771</v>
       </c>
-      <c r="B8" s="280" t="s">
+      <c r="B10" s="280" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="9" ht="72.5">
-      <c r="A9" s="281" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="284" t="s">
         <v>773</v>
       </c>
-      <c r="B9" s="282" t="s">
+      <c r="B11" s="280" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="279" t="s">
+    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A12" s="285" t="s">
         <v>775</v>
       </c>
-      <c r="B10" s="280" t="s">
+      <c r="B12" s="282" t="s">
         <v>776</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="284" t="s">
-        <v>777</v>
-      </c>
-      <c r="B11" s="280" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="12" ht="58">
-      <c r="A12" s="285" t="s">
-        <v>779</v>
-      </c>
-      <c r="B12" s="282" t="s">
-        <v>780</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" r:id="rId2"/>
-    <hyperlink ref="B4" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" r:id="rId5"/>
-    <hyperlink ref="B7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" r:id="rId6"/>
-    <hyperlink ref="B8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" r:id="rId7"/>
-    <hyperlink ref="B9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" r:id="rId8"/>
-    <hyperlink ref="B10" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" r:id="rId9"/>
-    <hyperlink ref="B11" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" r:id="rId10"/>
-    <hyperlink ref="B12" r:id="rId11"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-1400-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" xr:uid="{00000000-0004-0000-1400-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" xr:uid="{00000000-0004-0000-1400-000002000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-1400-000003000000}"/>
+    <hyperlink ref="B6" r:id="rId5" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" xr:uid="{00000000-0004-0000-1400-000004000000}"/>
+    <hyperlink ref="B7" r:id="rId6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" xr:uid="{00000000-0004-0000-1400-000005000000}"/>
+    <hyperlink ref="B8" r:id="rId7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" xr:uid="{00000000-0004-0000-1400-000006000000}"/>
+    <hyperlink ref="B9" r:id="rId8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" xr:uid="{00000000-0004-0000-1400-000007000000}"/>
+    <hyperlink ref="B10" r:id="rId9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" xr:uid="{00000000-0004-0000-1400-000008000000}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" xr:uid="{00000000-0004-0000-1400-000009000000}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-1400-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19224,37 +19208,36 @@
     <col min="2" max="2" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="67" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B1" s="67" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="2" ht="43.5">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="286" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="3" ht="43.5">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="286" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1"/>
-    <hyperlink ref="A3" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-1500-000000000000}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-1500-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19267,64 +19250,63 @@
     <col min="2" max="2" width="48.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
-        <v>676</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>672</v>
+      </c>
+      <c r="B1" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B5" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B7" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B8" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B9" t="s">
         <v>790</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>794</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1"/>
-    <hyperlink ref="A5" r:id="rId2"/>
-    <hyperlink ref="A7" r:id="rId3"/>
-    <hyperlink ref="A8" r:id="rId4"/>
-    <hyperlink ref="A9" r:id="rId5"/>
+    <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-1600-000000000000}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{00000000-0004-0000-1600-000001000000}"/>
+    <hyperlink ref="A7" r:id="rId3" xr:uid="{00000000-0004-0000-1600-000002000000}"/>
+    <hyperlink ref="A8" r:id="rId4" xr:uid="{00000000-0004-0000-1600-000003000000}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{00000000-0004-0000-1600-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19337,46 +19319,45 @@
     <col min="2" max="2" width="42.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="287" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B1" s="276" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="114" t="s">
+        <v>791</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="71" t="s">
+        <v>793</v>
+      </c>
+      <c r="B3" s="101" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="71" t="s">
         <v>795</v>
       </c>
-      <c r="B2" s="101" t="s">
+      <c r="B4" s="101" t="s">
         <v>796</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="71" t="s">
-        <v>797</v>
-      </c>
-      <c r="B3" s="101" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="71" t="s">
-        <v>799</v>
-      </c>
-      <c r="B4" s="101" t="s">
-        <v>800</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" r:id="rId1"/>
-    <hyperlink ref="B3" display="https://becurious.edcast.eu/pathways/azure-sql-this" r:id="rId2"/>
-    <hyperlink ref="B4" location="overview" display="IICS Complated Guide" r:id="rId3"/>
+    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" xr:uid="{00000000-0004-0000-1700-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://becurious.edcast.eu/pathways/azure-sql-this" xr:uid="{00000000-0004-0000-1700-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" location="overview" display="IICS Complated Guide" xr:uid="{00000000-0004-0000-1700-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19391,7 +19372,7 @@
     <col min="5" max="5" width="57.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>472</v>
       </c>
@@ -19408,383 +19389,382 @@
         <v>476</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="0">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>169</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>479</v>
       </c>
-      <c r="D3" s="0">
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>481</v>
       </c>
-      <c r="D4" s="0">
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>483</v>
       </c>
-      <c r="D5" s="0">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>485</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>486</v>
       </c>
-      <c r="D6" s="0">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>485</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>479</v>
       </c>
-      <c r="D7" s="0">
+      <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>485</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>481</v>
       </c>
-      <c r="D8" s="0">
+      <c r="D8">
         <v>3</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>9</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>488</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>477</v>
       </c>
-      <c r="D9" s="0">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>10</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>488</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>479</v>
       </c>
-      <c r="D10" s="0">
+      <c r="D10">
         <v>2</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
         <v>11</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>488</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" t="s">
         <v>481</v>
       </c>
-      <c r="D11" s="0">
+      <c r="D11">
         <v>3</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
         <v>12</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>488</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>483</v>
       </c>
-      <c r="D12" s="0">
+      <c r="D12">
         <v>4</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
         <v>13</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>489</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" t="s">
         <v>477</v>
       </c>
-      <c r="D13" s="0">
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
         <v>14</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>489</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" t="s">
         <v>479</v>
       </c>
-      <c r="D14" s="0">
+      <c r="D14">
         <v>2</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
         <v>15</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>489</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" t="s">
         <v>481</v>
       </c>
-      <c r="D15" s="0">
+      <c r="D15">
         <v>3</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
         <v>16</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>489</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>483</v>
       </c>
-      <c r="D16" s="0">
+      <c r="D16">
         <v>4</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17">
         <v>17</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>490</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" t="s">
         <v>477</v>
       </c>
-      <c r="D17" s="0">
+      <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
         <v>18</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>490</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" t="s">
         <v>479</v>
       </c>
-      <c r="D18" s="0">
+      <c r="D18">
         <v>2</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
         <v>19</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>490</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" t="s">
         <v>481</v>
       </c>
-      <c r="D19" s="0">
+      <c r="D19">
         <v>3</v>
       </c>
-      <c r="E19" s="0" t="s">
+      <c r="E19" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
         <v>20</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>490</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" t="s">
         <v>483</v>
       </c>
-      <c r="D20" s="0">
+      <c r="D20">
         <v>4</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
         <v>21</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>485</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" t="s">
         <v>491</v>
       </c>
-      <c r="D21" s="0">
+      <c r="D21">
         <v>4</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
         <v>22</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>485</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" t="s">
         <v>493</v>
       </c>
-      <c r="D22" s="0">
+      <c r="D22">
         <v>5</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
         <v>23</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>206</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>486</v>
       </c>
-      <c r="D23" s="0">
+      <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" t="s">
         <v>495</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19799,7 +19779,7 @@
     <col min="5" max="5" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>496</v>
       </c>
@@ -19816,179 +19796,178 @@
         <v>499</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>38</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>500</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>24</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>500</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>5</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>34</v>
       </c>
-      <c r="C4" s="0">
+      <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>6</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>80</v>
       </c>
-      <c r="C5" s="0">
+      <c r="C5">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>21</v>
+      </c>
+      <c r="D10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>7</v>
-      </c>
-      <c r="B6" s="0">
-        <v>80</v>
-      </c>
-      <c r="C6" s="0">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>8</v>
-      </c>
-      <c r="B7" s="0">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11">
         <v>25</v>
       </c>
-      <c r="C7" s="0">
-        <v>5</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>9</v>
-      </c>
-      <c r="B8" s="0">
-        <v>1</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>10</v>
-      </c>
-      <c r="B9" s="0">
-        <v>25</v>
-      </c>
-      <c r="C9" s="0">
-        <v>7</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>11</v>
-      </c>
-      <c r="B10" s="0">
-        <v>25</v>
-      </c>
-      <c r="C10" s="0">
-        <v>21</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="C11">
+        <v>22</v>
+      </c>
+      <c r="D11" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>12</v>
-      </c>
-      <c r="B11" s="0">
-        <v>25</v>
-      </c>
-      <c r="C11" s="0">
-        <v>22</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -20004,9 +19983,9 @@
     <col min="5" max="5" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -20015,92 +19994,91 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>80</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>346</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E2" t="s">
         <v>507</v>
       </c>
-      <c r="E2" s="0" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>35</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>193</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="0" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E4" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>41</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="0" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="s">
         <v>439</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E5" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>60</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>288</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>289</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>511</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14947C1-2082-4307-8EB3-961E6465F131}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -20111,37 +20089,37 @@
     <col min="6" max="6" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>498</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="0">
+      <c r="B2">
         <v>22</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D2" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="3">
@@ -20151,34 +20129,34 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="0">
+      <c r="B3">
         <v>22</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" t="s">
         <v>320</v>
       </c>
       <c r="E3" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="0">
+      <c r="B4">
         <v>22</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" t="s">
+        <v>516</v>
+      </c>
+      <c r="D4" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="3">
@@ -20188,17 +20166,17 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="0">
+      <c r="B5">
         <v>78</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>515</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D5" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="3">
@@ -20208,123 +20186,76 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="0">
+      <c r="B6">
         <v>87</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>516</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D6" t="s">
         <v>320</v>
       </c>
       <c r="E6" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>78</v>
+      </c>
+      <c r="C7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D7" t="s">
+        <v>503</v>
+      </c>
+      <c r="E7" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>94</v>
+      </c>
+      <c r="C8" t="s">
+        <v>514</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B7" s="0">
-        <v>78</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="B9">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="314" t="s">
-        <v>518</v>
-      </c>
-      <c r="F7" s="314" t="s">
+      <c r="E9" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0">
-        <v>78</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="F9" t="s">
         <v>520</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0">
-        <v>94</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>517</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>500</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0">
-        <v>55</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0">
-        <v>97</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>522</v>
-      </c>
-      <c r="F11" s="0" t="s">
-        <v>524</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -20346,42 +20277,42 @@
     <col min="11" max="11" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58">
+    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>525</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="G1" s="23" t="s">
         <v>526</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="H1" s="23" t="s">
         <v>527</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="I1" s="23" t="s">
         <v>528</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="J1" s="23" t="s">
         <v>529</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="K1" s="23" t="s">
         <v>530</v>
       </c>
-      <c r="H1" s="23" t="s">
-        <v>531</v>
-      </c>
-      <c r="I1" s="23" t="s">
-        <v>532</v>
-      </c>
-      <c r="J1" s="23" t="s">
-        <v>533</v>
-      </c>
-      <c r="K1" s="23" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="2" ht="126" customHeight="1">
+    </row>
+    <row r="2" spans="1:11" ht="126" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -20406,13 +20337,13 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -20426,7 +20357,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>127</v>
@@ -20437,11 +20368,11 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -20455,7 +20386,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>127</v>
@@ -20464,15 +20395,15 @@
         <v>127</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -20495,20 +20426,20 @@
         <v>127</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="5"/>
@@ -20520,7 +20451,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -20546,12 +20477,12 @@
         <v>190</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -20568,7 +20499,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" ht="82" customHeight="1">
+    <row r="9" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>9</v>
       </c>
@@ -20594,10 +20525,10 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="11" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -20621,12 +20552,12 @@
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" ht="246" customHeight="1">
+    <row r="11" spans="1:11" ht="246" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>11</v>
       </c>
@@ -20640,7 +20571,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>45</v>
@@ -20649,15 +20580,15 @@
         <v>45</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="11" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="12" ht="58.5" customHeight="1">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>12</v>
       </c>
@@ -20681,16 +20612,16 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>13</v>
       </c>
@@ -20717,7 +20648,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>14</v>
       </c>
@@ -20740,15 +20671,15 @@
         <v>127</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>15</v>
       </c>
@@ -20769,17 +20700,17 @@
         <v>127</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" ht="71" customHeight="1">
+    <row r="16" spans="1:11" ht="71" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>16</v>
       </c>
@@ -20792,8 +20723,8 @@
       <c r="D16" s="5">
         <v>3</v>
       </c>
-      <c r="E16" s="0" t="s">
-        <v>552</v>
+      <c r="E16" t="s">
+        <v>548</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>45</v>
@@ -20802,17 +20733,17 @@
         <v>127</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="17" ht="134" customHeight="1">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="134" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>17</v>
       </c>
@@ -20835,24 +20766,24 @@
         <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>553</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>556</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="18">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <v>18</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>50</v>
@@ -20861,7 +20792,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>127</v>
@@ -20870,20 +20801,20 @@
         <v>127</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>50</v>
@@ -20892,7 +20823,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>127</v>
@@ -20905,12 +20836,12 @@
       <c r="J19" s="6"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>50</v>
@@ -20932,12 +20863,12 @@
       <c r="J20" s="6"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>21</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>50</v>
@@ -20959,7 +20890,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -20982,17 +20913,17 @@
         <v>127</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -21015,7 +20946,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" ht="60.5" customHeight="1">
+    <row r="24" spans="1:11" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -21029,7 +20960,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>127</v>
@@ -21041,15 +20972,15 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="8" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>50</v>
@@ -21071,12 +21002,12 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>50</v>
@@ -21098,7 +21029,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>28</v>
       </c>
@@ -21112,7 +21043,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>127</v>
@@ -21127,12 +21058,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" ht="55.5" customHeight="1">
+    <row r="28" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>50</v>
@@ -21153,15 +21084,15 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="8" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="29" ht="68.5" customHeight="1">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>50</v>
@@ -21182,12 +21113,11 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="8" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -21213,108 +21143,108 @@
     <col min="14" max="14" width="18.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
-      <c r="C1" s="315" t="s">
-        <v>574</v>
-      </c>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="317"/>
-      <c r="L1" s="318" t="s">
-        <v>575</v>
-      </c>
-      <c r="M1" s="319"/>
-      <c r="N1" s="319"/>
-    </row>
-    <row r="2" ht="58">
+      <c r="C1" s="314" t="s">
+        <v>570</v>
+      </c>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="315"/>
+      <c r="G1" s="315"/>
+      <c r="H1" s="315"/>
+      <c r="I1" s="315"/>
+      <c r="J1" s="315"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="317" t="s">
+        <v>571</v>
+      </c>
+      <c r="M1" s="318"/>
+      <c r="N1" s="318"/>
+    </row>
+    <row r="2" spans="1:14" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
-      <c r="D2" s="320" t="s">
-        <v>576</v>
-      </c>
-      <c r="E2" s="320"/>
-      <c r="F2" s="320"/>
-      <c r="G2" s="320"/>
-      <c r="H2" s="320"/>
-      <c r="I2" s="320"/>
+      <c r="D2" s="319" t="s">
+        <v>572</v>
+      </c>
+      <c r="E2" s="319"/>
+      <c r="F2" s="319"/>
+      <c r="G2" s="319"/>
+      <c r="H2" s="319"/>
+      <c r="I2" s="319"/>
       <c r="J2" s="26" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="K2" s="27"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" ht="43.5">
+    <row r="3" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
+        <v>574</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>576</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>577</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="F3" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="G3" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="H3" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="I3" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="J3" s="29" t="s">
         <v>583</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="K3" s="30" t="s">
         <v>584</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="L3" s="29" t="s">
         <v>585</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="M3" s="29" t="s">
         <v>586</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="N3" s="29" t="s">
         <v>587</v>
       </c>
-      <c r="K3" s="30" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="B4" s="31" t="s">
         <v>589</v>
-      </c>
-      <c r="M3" s="29" t="s">
-        <v>590</v>
-      </c>
-      <c r="N3" s="29" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="s">
-        <v>592</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>593</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="G4" s="25">
         <v>0</v>
@@ -21323,7 +21253,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>63</v>
@@ -21335,24 +21265,24 @@
         <v>45</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N4" s="25">
         <v>10</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="35" t="s">
+        <v>588</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>592</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>596</v>
-      </c>
       <c r="C5" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E5" s="38" t="s">
         <v>63</v>
@@ -21377,15 +21307,15 @@
         <v>45</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N5" s="37">
         <v>4</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="35" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>269</v>
@@ -21427,62 +21357,62 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="35" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="L7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N7" s="37">
         <v>6</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="35" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E8" s="41">
         <v>0.5</v>
@@ -21501,30 +21431,30 @@
         <v>48</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="L8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N8" s="37">
         <v>8</v>
       </c>
     </row>
-    <row r="9" ht="29">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C9" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>63</v>
@@ -21551,13 +21481,13 @@
         <v>45</v>
       </c>
       <c r="M9" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N9" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="24" t="s">
         <v>59</v>
       </c>
@@ -21568,7 +21498,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E10" s="41">
         <v>1</v>
@@ -21586,33 +21516,33 @@
         <v>63</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="L10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N10" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="11" ht="29">
+    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E11" s="41">
         <v>1</v>
@@ -21630,22 +21560,22 @@
         <v>63</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="L11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N11" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="24" t="s">
         <v>59</v>
       </c>
@@ -21656,7 +21586,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E12" s="49">
         <v>0.8</v>
@@ -21677,30 +21607,30 @@
         <v>253</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="L12" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N12" s="43">
         <v>12</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C13" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E13" s="41">
         <v>0.5</v>
@@ -21718,7 +21648,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="K13" s="54">
         <v>9618241586</v>
@@ -21727,18 +21657,18 @@
         <v>45</v>
       </c>
       <c r="M13" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N13" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>127</v>
@@ -21777,7 +21707,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
         <v>59</v>
       </c>
@@ -21815,13 +21745,13 @@
         <v>45</v>
       </c>
       <c r="M15" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N15" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="24" t="s">
         <v>59</v>
       </c>
@@ -21847,13 +21777,13 @@
         <v>210</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>127</v>
@@ -21865,18 +21795,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>63</v>
@@ -21909,18 +21839,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="64" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="E18" s="41">
         <v>0.5</v>
@@ -21938,58 +21868,57 @@
         <v>46049</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="L18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M18" s="43" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="N18" s="43">
         <v>9</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>597</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>616</v>
-      </c>
-      <c r="F19" s="0" t="s">
-        <v>521</v>
-      </c>
-      <c r="G19" s="0" t="s">
-        <v>617</v>
-      </c>
-      <c r="J19" s="0" t="s">
-        <v>618</v>
-      </c>
-      <c r="K19" s="0" t="s">
-        <v>619</v>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>593</v>
+      </c>
+      <c r="E19" t="s">
+        <v>612</v>
+      </c>
+      <c r="F19" t="s">
+        <v>518</v>
+      </c>
+      <c r="G19" t="s">
+        <v>613</v>
+      </c>
+      <c r="J19" t="s">
+        <v>614</v>
+      </c>
+      <c r="K19" t="s">
+        <v>615</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="D2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
@@ -22004,30 +21933,30 @@
     <col min="5" max="5" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="76" t="s">
+        <v>616</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>617</v>
+      </c>
+      <c r="C1" s="76" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1" s="76" t="s">
+        <v>619</v>
+      </c>
+      <c r="E1" s="76" t="s">
         <v>620</v>
       </c>
-      <c r="B1" s="76" t="s">
-        <v>621</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>622</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>623</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="321" t="e">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="320" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C2" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!U1:U679, "Y")</f>
@@ -22042,10 +21971,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="321"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="320"/>
       <c r="B3" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C3" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!V1:V679, "Y")</f>
@@ -22060,10 +21989,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="321"/>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="320"/>
       <c r="B4" s="6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C4" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!AB1:AB679, "Y")</f>
@@ -22078,22 +22007,22 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>626</v>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>622</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="D6" s="67" t="s">
+        <v>619</v>
+      </c>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="6" t="s">
         <v>623</v>
-      </c>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="s">
-        <v>627</v>
       </c>
       <c r="C7" s="68">
         <v>36</v>
@@ -22103,37 +22032,37 @@
       </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="9">
-      <c r="A9" s="322" t="s">
-        <v>628</v>
-      </c>
-      <c r="B9" s="322"/>
-      <c r="C9" s="322"/>
-      <c r="D9" s="0" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="10">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="321" t="s">
+        <v>624</v>
+      </c>
+      <c r="B9" s="321"/>
+      <c r="C9" s="321"/>
+      <c r="D9" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="69"/>
       <c r="B10" s="69" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="70" t="s">
-        <v>631</v>
-      </c>
-      <c r="B11" s="323">
+        <v>627</v>
+      </c>
+      <c r="B11" s="322">
         <v>74</v>
       </c>
-      <c r="C11" s="323"/>
-    </row>
-    <row r="12">
+      <c r="C11" s="322"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="71" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B12" s="72">
         <v>61</v>
@@ -22142,9 +22071,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="71" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B13" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
@@ -22154,9 +22083,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="71" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B14" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "N")</f>
@@ -22164,9 +22093,9 @@
       </c>
       <c r="C14" s="71"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="74" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B15" s="75">
         <v>26</v>
@@ -22175,32 +22104,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="71" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B16" s="72">
         <f>B12-B15</f>
         <v>35</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="3">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to TeamTracker under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/TeamTracker.xlsx
+++ b/Data/TeamTracker.xlsx
@@ -41,7 +41,7 @@
   <externalReferences>
     <externalReference r:id="rId25"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId26"/>
     <pivotCache cacheId="1" r:id="rId27"/>
@@ -80,26 +80,35 @@
   <commentList>
     <comment ref="Y39" authorId="0" shapeId="0" xr:uid="{A76EB6EC-838A-4804-B11A-4B53BE1844C8}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y40" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y41" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -117,34 +126,46 @@
   <commentList>
     <comment ref="K15" authorId="0" shapeId="0" xr:uid="{E8742F7E-8B8E-40B8-88FA-1BF58FA61E56}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Connect with GD onshore team</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Connect with GD onshore team_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K16" authorId="1" shapeId="0" xr:uid="{2B8B1264-9F08-40E1-9040-B79527887B45}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K17" authorId="2" shapeId="0" xr:uid="{B23C388E-2E4B-496D-A7D5-EFA61D303073}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K22" authorId="3" shapeId="0" xr:uid="{6A7DE910-52BF-4905-9039-3376F875BE51}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Tech Sync calls are there with onshore GD teams</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Tech Sync calls are there with onshore GD teams_x000A_</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -152,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3556" uniqueCount="797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="800">
   <si>
     <t>SrNo</t>
   </si>
@@ -370,7 +391,7 @@
     <t>Firewire Modernization 2.0</t>
   </si>
   <si>
-    <t>We are going through KT videos.
+    <t xml:space="preserve">We are going through KT videos.
 Delivery not started yet.</t>
   </si>
   <si>
@@ -608,7 +629,7 @@
     <t>In progress</t>
   </si>
   <si>
-    <t>Client compliance Training Completed ,  Started working on Project Task</t>
+    <t xml:space="preserve">Client compliance Training Completed ,  Started working on Project Task</t>
   </si>
   <si>
     <t>Anand Maurya</t>
@@ -985,7 +1006,7 @@
     <t>Alex</t>
   </si>
   <si>
-    <t>VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
+    <t xml:space="preserve">VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
   </si>
   <si>
     <t>Abinesh C</t>
@@ -1100,7 +1121,7 @@
     <t>JIRA</t>
   </si>
   <si>
-    <t>VDI  received</t>
+    <t xml:space="preserve">VDI  received</t>
   </si>
   <si>
     <t>Kammeta, Prathap</t>
@@ -1121,7 +1142,7 @@
     <t>Inprogress</t>
   </si>
   <si>
-    <t>VDI Setup Done, Required tools setup completed (Ready API, JMeter)
+    <t xml:space="preserve">VDI Setup Done, Required tools setup completed (Ready API, JMeter)
 Client compliance email not received</t>
   </si>
   <si>
@@ -1158,7 +1179,7 @@
     <t>Mathew Romstadt</t>
   </si>
   <si>
-    <t>DUO setup done. VDI is accessible.
+    <t xml:space="preserve">DUO setup done. VDI is accessible.
 Received Compliance training email. Completed compliance training.
 Raised AG tickets for Confluence, Github and ReadyAPI.
 VDI setup done</t>
@@ -1515,19 +1536,19 @@
     <t>97987698076</t>
   </si>
   <si>
-    <t>Ravi Kishan</t>
-  </si>
-  <si>
-    <t>rkishan@deloitte.com</t>
+    <t>Suyash Dandekar</t>
+  </si>
+  <si>
+    <t>sudande@deloitte.com</t>
   </si>
   <si>
     <t>2026-09-04</t>
   </si>
   <si>
-    <t>Completing Onboarded Formalities.</t>
-  </si>
-  <si>
-    <t>7648786737</t>
+    <t>Just joined</t>
+  </si>
+  <si>
+    <t>8848993785</t>
   </si>
   <si>
     <t>UserID</t>
@@ -1578,6 +1599,9 @@
     <t>FALSE</t>
   </si>
   <si>
+    <t>psharma@deloitte.com</t>
+  </si>
+  <si>
     <t>StepID</t>
   </si>
   <si>
@@ -1668,9 +1692,6 @@
     <t>2026-09-05</t>
   </si>
   <si>
-    <t>2026-09-08</t>
-  </si>
-  <si>
     <t>InProgress</t>
   </si>
   <si>
@@ -1695,6 +1716,9 @@
     <t>Not part of the team.</t>
   </si>
   <si>
+    <t>Working in another project.</t>
+  </si>
+  <si>
     <t>TrainingID</t>
   </si>
   <si>
@@ -1713,7 +1737,7 @@
     <t>ROVO</t>
   </si>
   <si>
-    <t>Github Copilot</t>
+    <t>Copilot</t>
   </si>
   <si>
     <t>2026-09-30</t>
@@ -1725,6 +1749,9 @@
     <t>2026-09-03</t>
   </si>
   <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
     <t>Project name</t>
   </si>
   <si>
@@ -1743,26 +1770,26 @@
     <t>Has Team Member(s) in ADMX? (Y/N)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Offshore)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Onshore / GD)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Release)</t>
   </si>
   <si>
-    <t>Internal Meeting Cadence 
+    <t xml:space="preserve">Internal Meeting Cadence 
 (If has Team in USA / ADMX)</t>
   </si>
   <si>
     <t>Rekha/Meenakshi</t>
   </si>
   <si>
-    <t>M,T,TH,F - 10:30 - 11:00 PM IST 
+    <t xml:space="preserve">M,T,TH,F - 10:30 - 11:00 PM IST 
 USA : Daily Connect with Michael Griffin  
 Mexico : Daily Connect with Jesus Enrique Rivera Hernandez</t>
   </si>
@@ -1894,30 +1921,29 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Team Member Available for 
-W/E 21st</t>
+      <t>Team Member Available for _x000A_W/E 21st</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> June</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> Support</t>
     </r>
@@ -1929,7 +1955,7 @@
     <t>Track Name</t>
   </si>
   <si>
-    <t>PROD Support Applicable 
+    <t xml:space="preserve">PROD Support Applicable 
 (Y/N)</t>
   </si>
   <si>
@@ -2068,6 +2094,9 @@
     <t>Datadog</t>
   </si>
   <si>
+    <t>Github Copilot</t>
+  </si>
+  <si>
     <t>16 are yet to join</t>
   </si>
   <si>
@@ -2236,7 +2265,7 @@
     <t>Total No. of Resources</t>
   </si>
   <si>
-    <t>Additional Tools  Access requested specific to skillset</t>
+    <t xml:space="preserve">Additional Tools  Access requested specific to skillset</t>
   </si>
   <si>
     <t>Key Highlights</t>
@@ -2250,10 +2279,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Firewire: Github, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2264,10 +2293,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Both resources are going through KT recordings.</t>
     </r>
@@ -2278,10 +2307,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Access to Github, Sciforma are pending for one resource</t>
     </r>
@@ -2295,10 +2324,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>ArcPlatform: Confluence, VS2022 (.Net Framework &amp; .Net Core), GitHub, GitHub Copilot, DB Access - Non/ Prod, DataDog, Team City, Octopus, Azure DevOps, Prod VDI, ActiveBatch, CosmosDB, RedShift, SSMS</t>
     </r>
@@ -2309,10 +2338,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">One resource pending with Dev environment setup in progress and started with the KT confluence page &amp; recordings. </t>
     </r>
@@ -2323,10 +2352,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Github, Informatica, AWS Redshift</t>
     </r>
@@ -2337,10 +2366,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Currently progressing on project deliverables for OnePay Wallet</t>
     </r>
@@ -2351,10 +2380,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>DC1 (prod server), Informatica POC (Shared path for code), Azure SQL DB, Microsoft SQL Server</t>
     </r>
@@ -2365,10 +2394,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 of 3 resources are working on prod support</t>
     </r>
@@ -2382,20 +2411,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>IDE</t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>: Android Studio for Android, and XCode for iOS</t>
     </r>
@@ -2406,10 +2435,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Received macOS VDI details, but unable to access due to IP address issue (GD team is working on the resolution).</t>
     </r>
@@ -2420,20 +2449,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">Github: </t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Copilot access if being used by client</t>
     </r>
@@ -2444,10 +2473,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Going through KT and Onboarding contents. Project delivery is yet to start. Further info on Project Delivery after today's client connect</t>
     </r>
@@ -2458,20 +2487,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Git GUI tool:</t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve"> Sourcetree or Github Desktop</t>
     </r>
@@ -2485,10 +2514,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Git Hub, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2499,10 +2528,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 resources are Working on the Legacy Non-Prod &amp; PRD Deployments.</t>
     </r>
@@ -2513,10 +2542,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 resources are awaiting VDI access.</t>
     </r>
@@ -2527,10 +2556,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>VS code and JIRA</t>
     </r>
@@ -2541,10 +2570,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>One resource is going through KT videos and started on JIRA story TAX-72949 from Sprint 141 and other resource is yet to start.</t>
     </r>
@@ -2713,15 +2742,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)
-</t>
+      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section 1 - 4</t>
     </r>
@@ -2731,15 +2759,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code
-</t>
+      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section Introducing Thread Locking</t>
     </r>
@@ -2749,22 +2776,16 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Learn Parallel Programming with C# and .NET
-</t>
+      <t xml:space="preserve">Learn Parallel Programming with C# and .NET_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Sections:
-- Task Programing
-- Concurrent Collection
-- [Optional] Task Coordination
-- Async Programming
-+ Task.WhenAll(), Task.WhenAny()</t>
+      <t>Only Sections:_x000A_- Task Programing_x000A_- Concurrent Collection_x000A_- [Optional] Task Coordination_x000A_- Async Programming_x000A_+ Task.WhenAll(), Task.WhenAny()</t>
     </r>
   </si>
   <si>
@@ -2772,15 +2793,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide
-</t>
+      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section 4 Middleware</t>
     </r>
@@ -2803,23 +2823,21 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">RabbitMQ and Messaging Concepts
-</t>
+      <t xml:space="preserve">RabbitMQ and Messaging Concepts_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Section:
-[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
+      <t>Only Section:_x000A_[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
     </r>
   </si>
   <si>
@@ -2839,18 +2857,16 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Modern dotnet testing
-</t>
+      <t xml:space="preserve">Modern dotnet testing_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Section:
-Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
+      <t>Only Section:_x000A_Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
     </r>
   </si>
   <si>
@@ -2921,7 +2937,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3147,19 +3164,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -3170,13 +3174,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3218,7 +3222,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3230,13 +3234,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3765,664 +3769,664 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="337">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="18" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="18" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="1" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="8" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="14" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="22" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="15" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="30" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" applyFont="1" fillId="15" applyFill="1" borderId="4" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="16" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="1"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="20" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="27" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" applyFont="1" fillId="16" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="39" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="36" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="37" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4642,11 +4646,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Mandatory Trainings"/>
       <sheetName val="List of Projects"/>
@@ -4670,6 +4671,7 @@
       <sheetName val="ETL"/>
       <sheetName val="Sheet2"/>
     </sheetNames>
+    <definedNames/>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
@@ -6614,14 +6616,14 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5952C43C-8246-4EC2-A258-48BB4CDE7E1C}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:C11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="5">
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
       <items count="6">
         <item x="1"/>
         <item h="1" x="0"/>
@@ -6631,8 +6633,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="11">
         <item m="1" x="9"/>
         <item x="2"/>
@@ -6647,7 +6649,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -6660,7 +6662,7 @@
     <dataField name="Count of Level - Original" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="35">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -6680,11 +6682,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94E0152F-0BF3-438D-8873-7B4459136091}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:D17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -6692,7 +6694,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="18">
         <item x="0"/>
         <item x="2"/>
@@ -6714,18 +6716,18 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
@@ -6737,35 +6739,35 @@
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="10">
-    <format dxfId="25">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="16">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="16">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="16">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="16">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="4" count="0"/>
@@ -6792,11 +6794,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2BDA4149-0E05-4180-8484-88A33678FB6E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A23:E38" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1">
       <items count="4">
         <item x="1"/>
         <item x="0"/>
@@ -6804,7 +6806,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="18">
         <item x="0"/>
         <item x="2"/>
@@ -6826,9 +6828,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
       <items count="5">
         <item x="0"/>
         <item x="1"/>
@@ -6837,15 +6839,15 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="5"/>
@@ -6857,35 +6859,35 @@
     <dataField name="Count of Name" fld="1" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="34">
+    <format dxfId="16">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="16">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="16">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="16">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="16">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="5" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -6905,10 +6907,10 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EDF3A7DE-9201-4E1B-B165-09BBC2FC53FB}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A50:F56" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="30">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisCol" showAll="0" defaultSubtotal="1">
       <items count="5">
         <item x="2"/>
         <item x="0"/>
@@ -6917,8 +6919,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1">
       <items count="19">
         <item m="1" x="17"/>
         <item x="2"/>
@@ -6941,9 +6943,9 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="5">
         <item x="2"/>
         <item x="1"/>
@@ -6952,27 +6954,27 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="8"/>
@@ -6999,11 +7001,11 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{489EF034-6C39-4528-AA56-4CC8CE7F55D5}" name="PivotTable5" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="37">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisPage" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisPage" showAll="0" defaultSubtotal="1">
       <items count="4">
         <item x="1"/>
         <item x="2"/>
@@ -7011,10 +7013,10 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField axis="axisRow" showAll="0" defaultSubtotal="1">
       <items count="13">
         <item x="2"/>
         <item x="1"/>
@@ -7031,34 +7033,34 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
+    <pivotField showAll="0" defaultSubtotal="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="8"/>
@@ -7436,7 +7438,7 @@
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
     <col min="3" max="3" width="29.1796875" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="10.08984375" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
     <col min="9" max="9" width="13.54296875" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
@@ -7458,7 +7460,7 @@
     <col min="35" max="35" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
@@ -7565,7 +7567,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="87">
         <v>1</v>
       </c>
@@ -7640,7 +7642,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="71">
         <v>2</v>
       </c>
@@ -7712,7 +7714,7 @@
       </c>
       <c r="AH3" s="71"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="71">
         <v>3</v>
       </c>
@@ -7810,7 +7812,7 @@
       </c>
       <c r="AH4" s="71"/>
     </row>
-    <row r="5" spans="1:35" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="43.5">
       <c r="A5" s="71">
         <v>4</v>
       </c>
@@ -7910,7 +7912,7 @@
       </c>
       <c r="AH5" s="71"/>
     </row>
-    <row r="6" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="6" ht="101.5">
       <c r="A6" s="71">
         <v>5</v>
       </c>
@@ -8010,7 +8012,7 @@
       </c>
       <c r="AH6" s="71"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="71">
         <v>6</v>
       </c>
@@ -8023,16 +8025,16 @@
       <c r="D7" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="0" t="s">
         <v>39</v>
       </c>
       <c r="I7" s="94" t="s">
@@ -8108,7 +8110,7 @@
       </c>
       <c r="AH7" s="71"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="71">
         <v>7</v>
       </c>
@@ -8200,7 +8202,7 @@
       </c>
       <c r="AH8" s="71"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="71">
         <v>8</v>
       </c>
@@ -8292,7 +8294,7 @@
       </c>
       <c r="AH9" s="71"/>
     </row>
-    <row r="10" spans="1:35" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" ht="87">
       <c r="A10" s="87">
         <v>9</v>
       </c>
@@ -8364,7 +8366,7 @@
       </c>
       <c r="AH10" s="108"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="71">
         <v>10</v>
       </c>
@@ -8383,10 +8385,10 @@
       <c r="F11" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>101</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="0" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="94" t="s">
@@ -8462,7 +8464,7 @@
       </c>
       <c r="AH11" s="94"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="71">
         <v>11</v>
       </c>
@@ -8562,7 +8564,7 @@
       </c>
       <c r="AH12" s="94"/>
     </row>
-    <row r="13" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" ht="101.5">
       <c r="A13" s="71">
         <v>12</v>
       </c>
@@ -8660,7 +8662,7 @@
       </c>
       <c r="AH13" s="94"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="87">
         <v>13</v>
       </c>
@@ -8746,7 +8748,7 @@
       </c>
       <c r="AH14" s="89"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="71">
         <v>14</v>
       </c>
@@ -8838,7 +8840,7 @@
       </c>
       <c r="AH15" s="94"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="71">
         <v>15</v>
       </c>
@@ -8932,7 +8934,7 @@
       </c>
       <c r="AH16" s="94"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="71">
         <v>16</v>
       </c>
@@ -8951,7 +8953,7 @@
       <c r="F17" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H17" s="114" t="s">
@@ -8975,7 +8977,7 @@
       <c r="N17" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="0" t="s">
         <v>125</v>
       </c>
       <c r="P17" s="71" t="s">
@@ -9032,7 +9034,7 @@
       </c>
       <c r="AH17" s="94"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="71">
         <v>17</v>
       </c>
@@ -9051,7 +9053,7 @@
       <c r="F18" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="71" t="s">
@@ -9126,7 +9128,7 @@
       </c>
       <c r="AH18" s="94"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="71">
         <v>18</v>
       </c>
@@ -9222,7 +9224,7 @@
       </c>
       <c r="AH19" s="94"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="71">
         <v>19</v>
       </c>
@@ -9316,7 +9318,7 @@
       </c>
       <c r="AH20" s="94"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="87">
         <v>20</v>
       </c>
@@ -9408,7 +9410,7 @@
       </c>
       <c r="AH21" s="89"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="71">
         <v>21</v>
       </c>
@@ -9504,7 +9506,7 @@
       </c>
       <c r="AH22" s="94"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="71">
         <v>22</v>
       </c>
@@ -9526,7 +9528,7 @@
       <c r="G23" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="0" t="s">
         <v>149</v>
       </c>
       <c r="I23" s="115" t="s">
@@ -9602,7 +9604,7 @@
       </c>
       <c r="AH23" s="94"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="71">
         <v>23</v>
       </c>
@@ -9621,7 +9623,7 @@
       <c r="F24" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H24" s="71" t="s">
@@ -9692,7 +9694,7 @@
       </c>
       <c r="AH24" s="94"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="71">
         <v>24</v>
       </c>
@@ -9735,7 +9737,7 @@
       <c r="N25" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="0" t="s">
         <v>125</v>
       </c>
       <c r="P25" s="71" t="s">
@@ -9790,7 +9792,7 @@
       </c>
       <c r="AH25" s="94"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="71">
         <v>25</v>
       </c>
@@ -9803,13 +9805,13 @@
       <c r="D26" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="0" t="s">
         <v>50</v>
       </c>
       <c r="F26" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H26" s="71" t="s">
@@ -9881,7 +9883,7 @@
         <v>9619484828</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="71">
         <v>26</v>
       </c>
@@ -9979,7 +9981,7 @@
       </c>
       <c r="AH27" s="94"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="71">
         <v>27</v>
       </c>
@@ -10079,7 +10081,7 @@
       </c>
       <c r="AH28" s="94"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="87">
         <v>28</v>
       </c>
@@ -10177,7 +10179,7 @@
       </c>
       <c r="AH29" s="127"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="71">
         <v>29</v>
       </c>
@@ -10267,7 +10269,7 @@
       </c>
       <c r="AH30" s="94"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="71">
         <v>30</v>
       </c>
@@ -10364,7 +10366,7 @@
         <v>7353336812</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="71">
         <v>31</v>
       </c>
@@ -10460,7 +10462,7 @@
       </c>
       <c r="AH32" s="136"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="71">
         <v>32</v>
       </c>
@@ -10556,7 +10558,7 @@
       </c>
       <c r="AH33" s="113"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="71">
         <v>33</v>
       </c>
@@ -10652,7 +10654,7 @@
       </c>
       <c r="AH34" s="94"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="71">
         <v>34</v>
       </c>
@@ -10695,7 +10697,7 @@
       <c r="N35" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O35" t="s">
+      <c r="O35" s="0" t="s">
         <v>125</v>
       </c>
       <c r="P35" s="71" t="s">
@@ -10746,7 +10748,7 @@
       </c>
       <c r="AH35" s="94"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="87">
         <v>35</v>
       </c>
@@ -10838,7 +10840,7 @@
       </c>
       <c r="AH36" s="89"/>
     </row>
-    <row r="37" spans="1:34" ht="87" x14ac:dyDescent="0.35">
+    <row r="37" ht="87">
       <c r="A37" s="71">
         <v>36</v>
       </c>
@@ -10935,7 +10937,7 @@
         <v>7023147061</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="71">
         <v>37</v>
       </c>
@@ -11031,7 +11033,7 @@
       </c>
       <c r="AH38" s="94"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="71">
         <v>38</v>
       </c>
@@ -11074,7 +11076,7 @@
       <c r="N39" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O39" s="0" t="s">
         <v>125</v>
       </c>
       <c r="P39" s="71" t="s">
@@ -11123,7 +11125,7 @@
       </c>
       <c r="AH39" s="71"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="71">
         <v>39</v>
       </c>
@@ -11219,7 +11221,7 @@
       </c>
       <c r="AH40" s="71"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="87">
         <v>40</v>
       </c>
@@ -11303,7 +11305,7 @@
       </c>
       <c r="AH41" s="87"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="71">
         <v>41</v>
       </c>
@@ -11401,7 +11403,7 @@
       </c>
       <c r="AH42" s="71"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="119">
         <v>42</v>
       </c>
@@ -11497,7 +11499,7 @@
       </c>
       <c r="AH43" s="119"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="87">
         <v>43</v>
       </c>
@@ -11591,7 +11593,7 @@
       </c>
       <c r="AH44" s="87"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="119">
         <v>44</v>
       </c>
@@ -11687,7 +11689,7 @@
       </c>
       <c r="AH45" s="119"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="71">
         <v>45</v>
       </c>
@@ -11785,7 +11787,7 @@
       </c>
       <c r="AH46" s="71"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="87">
         <v>46</v>
       </c>
@@ -11873,7 +11875,7 @@
       </c>
       <c r="AH47" s="87"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="87">
         <v>47</v>
       </c>
@@ -11959,7 +11961,7 @@
       </c>
       <c r="AH48" s="87"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="71">
         <v>48</v>
       </c>
@@ -12055,7 +12057,7 @@
       </c>
       <c r="AH49" s="71"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="71">
         <v>49</v>
       </c>
@@ -12153,7 +12155,7 @@
       </c>
       <c r="AH50" s="71"/>
     </row>
-    <row r="51" spans="1:34" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" ht="29">
       <c r="A51" s="100">
         <v>50</v>
       </c>
@@ -12249,7 +12251,7 @@
       </c>
       <c r="AH51" s="100"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="71">
         <v>51</v>
       </c>
@@ -12345,7 +12347,7 @@
       </c>
       <c r="AH52" s="71"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="71">
         <v>52</v>
       </c>
@@ -12441,7 +12443,7 @@
       </c>
       <c r="AH53" s="71"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="87">
         <v>53</v>
       </c>
@@ -12535,7 +12537,7 @@
       </c>
       <c r="AH54" s="87"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="87">
         <v>54</v>
       </c>
@@ -12619,7 +12621,7 @@
       </c>
       <c r="AH55" s="87"/>
     </row>
-    <row r="56" spans="1:34" ht="58" x14ac:dyDescent="0.35">
+    <row r="56" ht="58">
       <c r="A56" s="71">
         <v>55</v>
       </c>
@@ -12713,7 +12715,7 @@
       </c>
       <c r="AH56" s="71"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="71">
         <v>56</v>
       </c>
@@ -12807,7 +12809,7 @@
       </c>
       <c r="AH57" s="71"/>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="87">
         <v>57</v>
       </c>
@@ -12901,7 +12903,7 @@
       </c>
       <c r="AH58" s="87"/>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="71">
         <v>58</v>
       </c>
@@ -12993,7 +12995,7 @@
       </c>
       <c r="AH59" s="71"/>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="71">
         <v>59</v>
       </c>
@@ -13036,7 +13038,7 @@
       <c r="N60" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="O60" t="s">
+      <c r="O60" s="0" t="s">
         <v>125</v>
       </c>
       <c r="P60" s="71" t="s">
@@ -13089,7 +13091,7 @@
       </c>
       <c r="AH60" s="71"/>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="87">
         <v>60</v>
       </c>
@@ -13161,7 +13163,7 @@
       </c>
       <c r="AH61" s="87"/>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="71">
         <v>61</v>
       </c>
@@ -13257,7 +13259,7 @@
       </c>
       <c r="AH62" s="71"/>
     </row>
-    <row r="63" spans="1:34" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" ht="29">
       <c r="A63" s="71">
         <v>62</v>
       </c>
@@ -13355,7 +13357,7 @@
       </c>
       <c r="AH63" s="71"/>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="71">
         <v>63</v>
       </c>
@@ -13453,7 +13455,7 @@
       </c>
       <c r="AH64" s="71"/>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="87">
         <v>64</v>
       </c>
@@ -13537,7 +13539,7 @@
       </c>
       <c r="AH65" s="87"/>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="119">
         <v>65</v>
       </c>
@@ -13586,7 +13588,7 @@
       <c r="P66" s="157" t="s">
         <v>306</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="Q66" s="0" t="s">
         <v>307</v>
       </c>
       <c r="R66" s="119" t="s">
@@ -13633,7 +13635,7 @@
       </c>
       <c r="AH66" s="119"/>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="87">
         <v>66</v>
       </c>
@@ -13713,7 +13715,7 @@
       </c>
       <c r="AH67" s="87"/>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="71">
         <v>67</v>
       </c>
@@ -13809,7 +13811,7 @@
       </c>
       <c r="AH68" s="71"/>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="71">
         <v>68</v>
       </c>
@@ -13901,7 +13903,7 @@
       </c>
       <c r="AH69" s="71"/>
     </row>
-    <row r="70" spans="1:34" ht="87" x14ac:dyDescent="0.35">
+    <row r="70" ht="87">
       <c r="A70" s="71">
         <v>69</v>
       </c>
@@ -14001,7 +14003,7 @@
       </c>
       <c r="AH70" s="71"/>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="71">
         <v>70</v>
       </c>
@@ -14097,7 +14099,7 @@
       </c>
       <c r="AH71" s="71"/>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="119">
         <v>71</v>
       </c>
@@ -14197,7 +14199,7 @@
       </c>
       <c r="AH72" s="119"/>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="71">
         <v>72</v>
       </c>
@@ -14216,7 +14218,7 @@
       <c r="F73" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="0" t="s">
         <v>101</v>
       </c>
       <c r="H73" s="71" t="s">
@@ -14297,7 +14299,7 @@
       </c>
       <c r="AH73" s="71"/>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="71">
         <v>73</v>
       </c>
@@ -14319,7 +14321,7 @@
       <c r="G74" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="0" t="s">
         <v>52</v>
       </c>
       <c r="I74" s="94" t="s">
@@ -14397,7 +14399,7 @@
       </c>
       <c r="AH74" s="71"/>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="71">
         <v>74</v>
       </c>
@@ -14488,12 +14490,12 @@
       </c>
       <c r="AE75" s="71"/>
       <c r="AF75" s="71"/>
-      <c r="AG75">
+      <c r="AG75" s="0">
         <v>9746540951</v>
       </c>
       <c r="AH75" s="71"/>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="71">
         <v>75</v>
       </c>
@@ -14589,7 +14591,7 @@
       </c>
       <c r="AH76" s="71"/>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="71">
         <v>76</v>
       </c>
@@ -14677,7 +14679,7 @@
       </c>
       <c r="AH77" s="71"/>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="87">
         <v>77</v>
       </c>
@@ -14755,7 +14757,7 @@
       </c>
       <c r="AH78" s="87"/>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="87">
         <v>78</v>
       </c>
@@ -14855,7 +14857,7 @@
       </c>
       <c r="AH79" s="87"/>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="71">
         <v>79</v>
       </c>
@@ -14951,7 +14953,7 @@
       </c>
       <c r="AH80" s="71"/>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="71">
         <v>80</v>
       </c>
@@ -15049,7 +15051,7 @@
       </c>
       <c r="AH81" s="71"/>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="71">
         <v>81</v>
       </c>
@@ -15145,7 +15147,7 @@
       </c>
       <c r="AH82" s="71"/>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83" s="71">
         <v>82</v>
       </c>
@@ -15173,7 +15175,7 @@
       <c r="I83" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="0" t="s">
         <v>68</v>
       </c>
       <c r="K83" s="218">
@@ -15241,7 +15243,7 @@
       </c>
       <c r="AH83" s="71"/>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84" s="222">
         <v>83</v>
       </c>
@@ -15339,7 +15341,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85" s="230">
         <v>84</v>
       </c>
@@ -15441,7 +15443,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86" s="230">
         <v>85</v>
       </c>
@@ -15545,7 +15547,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87" s="230">
         <v>86</v>
       </c>
@@ -15645,7 +15647,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88" s="230">
         <v>87</v>
       </c>
@@ -15737,7 +15739,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89" s="128">
         <v>88</v>
       </c>
@@ -15837,7 +15839,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90" s="252">
         <v>89</v>
       </c>
@@ -15939,7 +15941,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91" s="252">
         <v>90</v>
       </c>
@@ -16041,7 +16043,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92" s="252">
         <v>91</v>
       </c>
@@ -16129,7 +16131,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93" s="252">
         <v>92</v>
       </c>
@@ -16215,7 +16217,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94" s="252">
         <v>93</v>
       </c>
@@ -16309,7 +16311,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95" s="252">
         <v>94</v>
       </c>
@@ -16401,7 +16403,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96" s="261">
         <v>95</v>
       </c>
@@ -16501,7 +16503,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97" s="268">
         <v>96</v>
       </c>
@@ -16599,7 +16601,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98" s="71">
         <v>97</v>
       </c>
@@ -16697,7 +16699,7 @@
       </c>
       <c r="AH98" s="71"/>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99" s="71">
         <v>98</v>
       </c>
@@ -16793,7 +16795,7 @@
       </c>
       <c r="AH99" s="71"/>
     </row>
-    <row r="100" spans="1:34" ht="15" x14ac:dyDescent="0.4">
+    <row r="100" ht="15">
       <c r="A100" s="71">
         <v>99</v>
       </c>
@@ -16877,241 +16879,255 @@
         <v>436</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101" s="71">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="0" t="s">
         <v>437</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="0" t="s">
         <v>438</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K101" s="0" t="s">
         <v>440</v>
       </c>
-      <c r="L101" t="s">
+      <c r="L101" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="M101" t="s">
+      <c r="M101" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="N101" t="s">
+      <c r="N101" s="0" t="s">
         <v>442</v>
       </c>
-      <c r="O101" t="s">
+      <c r="O101" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="P101" t="s">
+      <c r="P101" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="Q101" t="s">
+      <c r="Q101" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="U101" t="s">
-        <v>45</v>
-      </c>
-      <c r="V101" t="s">
-        <v>45</v>
-      </c>
-      <c r="W101" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB101" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE101" t="s">
+      <c r="U101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="V101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="W101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE101" s="0" t="s">
         <v>443</v>
       </c>
-      <c r="AG101" t="s">
+      <c r="AG101" s="0" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" s="0">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="0" t="s">
         <v>445</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="0" t="s">
         <v>446</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G102" t="s">
+      <c r="G102" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I102" s="0" t="s">
         <v>439</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="L102" t="s">
-        <v>45</v>
-      </c>
-      <c r="M102" t="s">
+      <c r="L102" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M102" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N102" s="0" t="s">
         <v>442</v>
       </c>
-      <c r="O102" t="s">
+      <c r="O102" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="P102" t="s">
+      <c r="P102" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="Q102" s="0" t="s">
         <v>448</v>
       </c>
-      <c r="U102" t="s">
+      <c r="U102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="V102" t="s">
+      <c r="V102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="W102" t="s">
+      <c r="W102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="AB102" t="s">
+      <c r="AB102" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="AE102" t="s">
+      <c r="AE102" s="0" t="s">
         <v>449</v>
       </c>
-      <c r="AG102" t="s">
+      <c r="AG102" s="0" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>102</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="103">
+      <c r="A103" s="0">
+        <v>103</v>
+      </c>
+      <c r="B103" s="0" t="s">
         <v>451</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G103" t="s">
+      <c r="F103"/>
+      <c r="G103" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="I103" t="s">
+      <c r="H103"/>
+      <c r="I103" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="K103" t="s">
+      <c r="J103"/>
+      <c r="K103" s="0" t="s">
         <v>453</v>
       </c>
-      <c r="L103" t="s">
-        <v>45</v>
-      </c>
-      <c r="M103" t="s">
-        <v>40</v>
-      </c>
-      <c r="N103" t="s">
+      <c r="L103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M103" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="N103" s="0" t="s">
         <v>442</v>
       </c>
-      <c r="O103" t="s">
+      <c r="O103" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="P103" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>169</v>
-      </c>
-      <c r="U103" t="s">
-        <v>45</v>
-      </c>
-      <c r="V103" t="s">
-        <v>45</v>
-      </c>
-      <c r="W103" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB103" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE103" t="s">
+      <c r="P103" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q103" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="R103"/>
+      <c r="S103"/>
+      <c r="T103"/>
+      <c r="U103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="V103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="W103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="X103"/>
+      <c r="Y103"/>
+      <c r="Z103"/>
+      <c r="AA103"/>
+      <c r="AB103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC103"/>
+      <c r="AD103"/>
+      <c r="AE103" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="AG103" t="s">
+      <c r="AF103"/>
+      <c r="AG103" s="0" t="s">
         <v>455</v>
       </c>
+      <c r="AH103"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B99">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C92 C94:C98">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C100">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16 P16:Q16">
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>$AH16=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35 Q35 O40:Q40">
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>$AF35=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N48:P48 N49 N51 Q51 N54:Q54 N56:Q56 N65:Q65 O71 O75:Q75">
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>$AB48=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:Q14">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="2" priority="13">
       <formula>$AG14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O57">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>$AB57=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O59:Q59">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$AB59=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42 N42:N43 Q42:Q43">
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="2" priority="11">
       <formula>$AE42=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17121,105 +17137,106 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH84:AH97">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D3" r:id="rId3" display="mailto:abirudugadda@deloitte.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="M33" r:id="rId34" display="akalkundre@deloitte.com" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="P38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C39" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C40" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C41" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C43" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C52" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C53" r:id="rId54" display="mailto:visviswanathan@deloitte.com" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C54" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C56" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C57" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C58" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C59" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C61" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C62" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C63" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C64" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C82" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C83" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C84" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C85" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C86" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C87" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C89" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C91" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C92" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C99" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C2" r:id="rId97"/>
+    <hyperlink ref="C3" r:id="rId98"/>
+    <hyperlink ref="D3" display="mailto:abirudugadda@deloitte.com" r:id="rId99"/>
+    <hyperlink ref="C4" r:id="rId100"/>
+    <hyperlink ref="C5" r:id="rId101"/>
+    <hyperlink ref="C6" r:id="rId102"/>
+    <hyperlink ref="C7" r:id="rId103"/>
+    <hyperlink ref="C8" r:id="rId104"/>
+    <hyperlink ref="C9" r:id="rId105"/>
+    <hyperlink ref="C10" r:id="rId106"/>
+    <hyperlink ref="C11" r:id="rId107"/>
+    <hyperlink ref="C12" r:id="rId108"/>
+    <hyperlink ref="C13" r:id="rId109"/>
+    <hyperlink ref="C14" r:id="rId110"/>
+    <hyperlink ref="C15" r:id="rId111"/>
+    <hyperlink ref="C16" r:id="rId112"/>
+    <hyperlink ref="C17" r:id="rId113"/>
+    <hyperlink ref="C18" r:id="rId114"/>
+    <hyperlink ref="C19" r:id="rId115"/>
+    <hyperlink ref="C20" r:id="rId116"/>
+    <hyperlink ref="C21" r:id="rId117"/>
+    <hyperlink ref="C22" r:id="rId118"/>
+    <hyperlink ref="C23" r:id="rId119"/>
+    <hyperlink ref="C24" r:id="rId120"/>
+    <hyperlink ref="C25" r:id="rId121"/>
+    <hyperlink ref="C26" r:id="rId122"/>
+    <hyperlink ref="C27" r:id="rId123"/>
+    <hyperlink ref="C28" r:id="rId124"/>
+    <hyperlink ref="C29" r:id="rId125"/>
+    <hyperlink ref="C30" r:id="rId126"/>
+    <hyperlink ref="C31" r:id="rId127"/>
+    <hyperlink ref="C32" r:id="rId128"/>
+    <hyperlink ref="C33" r:id="rId129"/>
+    <hyperlink ref="M33" display="akalkundre@deloitte.com" r:id="rId130"/>
+    <hyperlink ref="C34" r:id="rId131"/>
+    <hyperlink ref="C35" r:id="rId132"/>
+    <hyperlink ref="C36" r:id="rId133"/>
+    <hyperlink ref="C37" r:id="rId134"/>
+    <hyperlink ref="C38" r:id="rId135"/>
+    <hyperlink ref="P38" r:id="rId136"/>
+    <hyperlink ref="C39" r:id="rId137"/>
+    <hyperlink ref="C40" r:id="rId138"/>
+    <hyperlink ref="C41" r:id="rId139"/>
+    <hyperlink ref="C42" r:id="rId140"/>
+    <hyperlink ref="C43" r:id="rId141"/>
+    <hyperlink ref="C44" r:id="rId142"/>
+    <hyperlink ref="C45" r:id="rId143"/>
+    <hyperlink ref="C47" r:id="rId144"/>
+    <hyperlink ref="C48" r:id="rId145"/>
+    <hyperlink ref="C49" r:id="rId146"/>
+    <hyperlink ref="C50" r:id="rId147"/>
+    <hyperlink ref="C51" r:id="rId148"/>
+    <hyperlink ref="C52" r:id="rId149"/>
+    <hyperlink ref="C53" display="mailto:visviswanathan@deloitte.com" r:id="rId150"/>
+    <hyperlink ref="C54" r:id="rId151"/>
+    <hyperlink ref="C55" r:id="rId152"/>
+    <hyperlink ref="C56" r:id="rId153"/>
+    <hyperlink ref="C57" r:id="rId154"/>
+    <hyperlink ref="C58" r:id="rId155"/>
+    <hyperlink ref="C59" r:id="rId156"/>
+    <hyperlink ref="C61" r:id="rId157"/>
+    <hyperlink ref="C62" r:id="rId158"/>
+    <hyperlink ref="C63" r:id="rId159"/>
+    <hyperlink ref="C64" r:id="rId160"/>
+    <hyperlink ref="C66" r:id="rId161"/>
+    <hyperlink ref="C67" r:id="rId162"/>
+    <hyperlink ref="C68" r:id="rId163"/>
+    <hyperlink ref="C69" r:id="rId164"/>
+    <hyperlink ref="C71" r:id="rId165"/>
+    <hyperlink ref="C72" r:id="rId166"/>
+    <hyperlink ref="C73" r:id="rId167"/>
+    <hyperlink ref="C75" r:id="rId168"/>
+    <hyperlink ref="C76" r:id="rId169"/>
+    <hyperlink ref="C79" r:id="rId170"/>
+    <hyperlink ref="C80" r:id="rId171"/>
+    <hyperlink ref="C82" r:id="rId172"/>
+    <hyperlink ref="C83" r:id="rId173"/>
+    <hyperlink ref="C84" r:id="rId174"/>
+    <hyperlink ref="C85" r:id="rId175"/>
+    <hyperlink ref="C86" r:id="rId176"/>
+    <hyperlink ref="C87" r:id="rId177"/>
+    <hyperlink ref="C88" r:id="rId178"/>
+    <hyperlink ref="C89" r:id="rId179"/>
+    <hyperlink ref="C90" r:id="rId180"/>
+    <hyperlink ref="C91" r:id="rId181"/>
+    <hyperlink ref="C92" r:id="rId182"/>
+    <hyperlink ref="C93" r:id="rId183"/>
+    <hyperlink ref="C94" r:id="rId184"/>
+    <hyperlink ref="C95" r:id="rId185"/>
+    <hyperlink ref="C96" r:id="rId186"/>
+    <hyperlink ref="C97" r:id="rId187"/>
+    <hyperlink ref="C99" r:id="rId188"/>
+    <hyperlink ref="C100" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId94"/>
 </worksheet>
 </file>
@@ -17234,26 +17251,26 @@
     <col min="3" max="3" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>634</v>
-      </c>
-      <c r="B1" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>636</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C2" s="0" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="80" t="s">
         <v>36</v>
       </c>
@@ -17264,7 +17281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="82" t="s">
         <v>56</v>
       </c>
@@ -17275,7 +17292,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="82" t="s">
         <v>38</v>
       </c>
@@ -17286,7 +17303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="82" t="s">
         <v>106</v>
       </c>
@@ -17297,7 +17314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="82" t="s">
         <v>51</v>
       </c>
@@ -17308,7 +17325,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="82" t="s">
         <v>82</v>
       </c>
@@ -17319,7 +17336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="82" t="s">
         <v>101</v>
       </c>
@@ -17330,7 +17347,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="82" t="s">
         <v>197</v>
       </c>
@@ -17341,9 +17358,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="80" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B11" s="78">
         <v>84</v>
@@ -17354,6 +17371,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -17368,24 +17386,24 @@
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="78" t="s">
+        <v>642</v>
+      </c>
+      <c r="B2" s="78" t="s">
         <v>638</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="78" t="s">
-        <v>639</v>
-      </c>
-      <c r="B2" s="78" t="s">
-        <v>635</v>
       </c>
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="78" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>127</v>
@@ -17394,10 +17412,10 @@
         <v>45</v>
       </c>
       <c r="D3" s="78" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="78" t="s">
         <v>40</v>
       </c>
@@ -17411,7 +17429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="78" t="s">
         <v>75</v>
       </c>
@@ -17423,7 +17441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="78" t="s">
         <v>110</v>
       </c>
@@ -17435,7 +17453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="78" t="s">
         <v>58</v>
       </c>
@@ -17447,7 +17465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="78" t="s">
         <v>95</v>
       </c>
@@ -17459,7 +17477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="78" t="s">
         <v>113</v>
       </c>
@@ -17471,7 +17489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="78" t="s">
         <v>374</v>
       </c>
@@ -17483,7 +17501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="78" t="s">
         <v>123</v>
       </c>
@@ -17495,7 +17513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="78" t="s">
         <v>86</v>
       </c>
@@ -17507,7 +17525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="78" t="s">
         <v>174</v>
       </c>
@@ -17519,7 +17537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="78" t="s">
         <v>211</v>
       </c>
@@ -17531,7 +17549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="78" t="s">
         <v>219</v>
       </c>
@@ -17543,7 +17561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="78" t="s">
         <v>228</v>
       </c>
@@ -17555,9 +17573,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="78" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B17" s="78">
         <v>6</v>
@@ -17569,35 +17587,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D18" t="s">
+    <row r="18">
+      <c r="D18" s="0" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="77" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="78" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="B23" s="78" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C23" s="78"/>
       <c r="D23" s="78"/>
       <c r="E23" s="78"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="78" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B24" s="78" t="s">
         <v>83</v>
@@ -17609,10 +17627,10 @@
         <v>61</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="78" t="s">
         <v>40</v>
       </c>
@@ -17627,7 +17645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="78" t="s">
         <v>75</v>
       </c>
@@ -17640,7 +17658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="78" t="s">
         <v>110</v>
       </c>
@@ -17653,7 +17671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="78" t="s">
         <v>58</v>
       </c>
@@ -17666,7 +17684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="78" t="s">
         <v>95</v>
       </c>
@@ -17679,7 +17697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="78" t="s">
         <v>113</v>
       </c>
@@ -17694,7 +17712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="78" t="s">
         <v>374</v>
       </c>
@@ -17709,7 +17727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="78" t="s">
         <v>123</v>
       </c>
@@ -17724,7 +17742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="78" t="s">
         <v>86</v>
       </c>
@@ -17739,7 +17757,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="78" t="s">
         <v>174</v>
       </c>
@@ -17752,7 +17770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="78" t="s">
         <v>211</v>
       </c>
@@ -17765,7 +17783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="78" t="s">
         <v>219</v>
       </c>
@@ -17778,7 +17796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="78" t="s">
         <v>228</v>
       </c>
@@ -17791,9 +17809,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="78" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B38" s="78">
         <v>24</v>
@@ -17808,162 +17826,162 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="78" t="s">
+        <v>645</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="79" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
         <v>642</v>
       </c>
-      <c r="B41" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B43" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="79" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+      <c r="B50" s="0" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
         <v>639</v>
       </c>
-      <c r="B50" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>636</v>
-      </c>
-      <c r="B51" t="s">
-        <v>648</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="B51" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="C51" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="D51" t="s">
-        <v>649</v>
-      </c>
-      <c r="E51" t="s">
-        <v>650</v>
-      </c>
-      <c r="F51" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D51" s="0" t="s">
+        <v>652</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>653</v>
+      </c>
+      <c r="F51" s="0" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="80" t="s">
-        <v>651</v>
-      </c>
-      <c r="B52">
+        <v>654</v>
+      </c>
+      <c r="B52" s="0">
         <v>5</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="0">
         <v>14</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="0">
         <v>1</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="0">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="80" t="s">
-        <v>652</v>
-      </c>
-      <c r="C53">
+        <v>655</v>
+      </c>
+      <c r="C53" s="0">
         <v>8</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="0">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="80" t="s">
+        <v>656</v>
+      </c>
+      <c r="B54" s="0">
+        <v>1</v>
+      </c>
+      <c r="C54" s="0">
+        <v>29</v>
+      </c>
+      <c r="D54" s="0">
+        <v>5</v>
+      </c>
+      <c r="F54" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="80" t="s">
         <v>653</v>
       </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54">
-        <v>29</v>
-      </c>
-      <c r="D54">
-        <v>5</v>
-      </c>
-      <c r="F54">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" s="80" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56">
       <c r="A56" s="80" t="s">
-        <v>637</v>
-      </c>
-      <c r="B56">
+        <v>640</v>
+      </c>
+      <c r="B56" s="0">
         <v>6</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="0">
         <v>51</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="0">
         <v>6</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="0">
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="70" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B59" s="71"/>
       <c r="C59" s="71"/>
       <c r="D59" s="71"/>
       <c r="E59" s="71"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="70" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B60" s="70" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C60" s="70" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D60" s="70" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E60" s="70" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F60" s="77"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="323">
         <v>38</v>
       </c>
       <c r="B61" s="71" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C61" s="71">
         <v>12</v>
@@ -17975,10 +17993,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="324"/>
       <c r="B62" s="71" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C62" s="71">
         <v>9</v>
@@ -17990,10 +18008,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="325"/>
       <c r="B63" s="71" t="s">
-        <v>517</v>
+        <v>624</v>
       </c>
       <c r="C63" s="71">
         <v>27</v>
@@ -18005,29 +18023,30 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="C64" s="81">
         <f>C63/(C63+D63)</f>
-        <v>0.79411764705882348</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
+        <v>0.7941176470588235</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="C65" s="81">
         <f>C62/(C62+D62)</f>
-        <v>0.39130434782608697</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
+        <v>0.391304347826087</v>
+      </c>
+    </row>
+    <row r="66">
       <c r="C66" s="81">
         <f>C61/(C61+D61)</f>
         <v>0.34285714285714286</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="A61:A63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18040,128 +18059,129 @@
     <col min="2" max="2" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>636</v>
-      </c>
-      <c r="B3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" s="0" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="80" t="s">
         <v>149</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="80" t="s">
         <v>166</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="80" t="s">
         <v>122</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="80" t="s">
         <v>391</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="80" t="s">
         <v>406</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="80" t="s">
         <v>357</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="80" t="s">
         <v>410</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="80" t="s">
         <v>157</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="80" t="s">
-        <v>637</v>
-      </c>
-      <c r="B16">
+        <v>640</v>
+      </c>
+      <c r="B16" s="0">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18174,107 +18194,108 @@
     <col min="2" max="3" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="291" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="291" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C1" s="291" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="2" ht="29">
       <c r="A2" s="292" t="s">
         <v>198</v>
       </c>
       <c r="B2" s="293" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C2" s="294" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="292" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="295" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C3" s="294" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="4" ht="29">
       <c r="A4" s="292" t="s">
         <v>141</v>
       </c>
       <c r="B4" s="293" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C4" s="294" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="5" ht="58">
       <c r="A5" s="292" t="s">
+        <v>668</v>
+      </c>
+      <c r="B5" s="293" t="s">
+        <v>663</v>
+      </c>
+      <c r="C5" s="294" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="6" ht="29">
+      <c r="A6" s="293" t="s">
+        <v>670</v>
+      </c>
+      <c r="B6" s="293" t="s">
         <v>665</v>
       </c>
-      <c r="B5" s="293" t="s">
-        <v>660</v>
-      </c>
-      <c r="C5" s="294" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="293" t="s">
-        <v>667</v>
-      </c>
-      <c r="B6" s="293" t="s">
-        <v>662</v>
-      </c>
       <c r="C6" s="294" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="293" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="293" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C7" s="294" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="296" t="s">
         <v>174</v>
       </c>
       <c r="B8" s="297" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C8" s="296" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="296" t="s">
         <v>113</v>
       </c>
       <c r="B9" s="297" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C9" s="296" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18287,27 +18308,28 @@
     <col min="2" max="2" width="93.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="288" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B1" s="288" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="289" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="B2" s="290" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
+    <hyperlink ref="B2" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18323,65 +18345,65 @@
     <col min="5" max="5" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="39" x14ac:dyDescent="0.35">
+    <row r="1" ht="39">
       <c r="A1" s="298" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="B1" s="299" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C1" s="299" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D1" s="299" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="E1" s="300" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="247" customHeight="1" x14ac:dyDescent="0.35">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="2" ht="247" customHeight="1">
       <c r="A2" s="328" t="s">
         <v>198</v>
       </c>
       <c r="B2" s="331" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C2" s="331">
         <v>2</v>
       </c>
       <c r="D2" s="334" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="E2" s="301" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="3" ht="26.5">
       <c r="A3" s="329"/>
       <c r="B3" s="333"/>
       <c r="C3" s="333"/>
       <c r="D3" s="335"/>
       <c r="E3" s="302" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="4" ht="156.5">
       <c r="A4" s="329"/>
       <c r="B4" s="303" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C4" s="303">
         <v>2</v>
       </c>
       <c r="D4" s="304" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E4" s="302" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="5" ht="39.5">
       <c r="A5" s="329" t="s">
         <v>58</v>
       </c>
@@ -18392,26 +18414,26 @@
         <v>3</v>
       </c>
       <c r="D5" s="305" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="E5" s="302" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="6" ht="65.5">
       <c r="A6" s="330"/>
       <c r="B6" s="333"/>
       <c r="C6" s="333"/>
       <c r="D6" s="306" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E6" s="307" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="7" ht="52.5">
       <c r="A7" s="328" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B7" s="331" t="s">
         <v>96</v>
@@ -18420,35 +18442,35 @@
         <v>3</v>
       </c>
       <c r="D7" s="305" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E7" s="301" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="8" ht="65.5">
       <c r="A8" s="329"/>
       <c r="B8" s="332"/>
       <c r="C8" s="332"/>
       <c r="D8" s="308" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="E8" s="309" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="9" ht="39.5">
       <c r="A9" s="330"/>
       <c r="B9" s="333"/>
       <c r="C9" s="333"/>
       <c r="D9" s="306" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="E9" s="310"/>
     </row>
-    <row r="10" spans="1:5" ht="273" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="273" customHeight="1">
       <c r="A10" s="328" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B10" s="331" t="s">
         <v>87</v>
@@ -18457,22 +18479,22 @@
         <v>4</v>
       </c>
       <c r="D10" s="326" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E10" s="301" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="11" ht="26.5">
       <c r="A11" s="330"/>
       <c r="B11" s="333"/>
       <c r="C11" s="333"/>
       <c r="D11" s="327"/>
       <c r="E11" s="307" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="12" ht="65.5">
       <c r="A12" s="311" t="s">
         <v>110</v>
       </c>
@@ -18483,14 +18505,14 @@
         <v>2</v>
       </c>
       <c r="D12" s="304" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E12" s="312" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -18507,6 +18529,7 @@
     <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18519,36 +18542,37 @@
     <col min="2" max="2" width="62.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="275" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B1" s="276" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="71" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="71" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
+    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18562,117 +18586,118 @@
     <col min="3" max="3" width="53.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B2" t="s">
-        <v>714</v>
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>717</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="D2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>719</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>716</v>
       </c>
-      <c r="E2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>713</v>
-      </c>
-      <c r="B3" t="s">
-        <v>718</v>
+      <c r="B3" s="0" t="s">
+        <v>721</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>723</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>719</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" s="0" t="s">
         <v>720</v>
       </c>
-      <c r="E3" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>722</v>
-      </c>
-      <c r="B4" t="s">
-        <v>723</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>725</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>728</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="D4" t="s">
-        <v>716</v>
-      </c>
-      <c r="E4" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>722</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
         <v>725</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="D5" t="s">
-        <v>727</v>
-      </c>
-      <c r="E5" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>722</v>
-      </c>
-      <c r="B6" t="s">
-        <v>728</v>
+      <c r="B6" s="0" t="s">
+        <v>731</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="D6" t="s">
-        <v>730</v>
-      </c>
-      <c r="E6" t="s">
-        <v>721</v>
+        <v>732</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>724</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1000-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-1000-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-1000-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-1000-000004000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18688,63 +18713,64 @@
     <col min="5" max="5" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>713</v>
-      </c>
-      <c r="B2" t="s">
-        <v>731</v>
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" ht="101.5">
+      <c r="A2" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>734</v>
       </c>
       <c r="C2" s="277" t="s">
-        <v>732</v>
-      </c>
-      <c r="D2" t="s">
-        <v>733</v>
-      </c>
-      <c r="E2" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
         <v>735</v>
       </c>
-      <c r="B3" t="s">
-        <v>515</v>
+      <c r="D2" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>516</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="D3" t="s">
-        <v>727</v>
-      </c>
-      <c r="E3" t="s">
-        <v>734</v>
+        <v>739</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>737</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="overview" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1100-000001000000}"/>
+    <hyperlink ref="C2" location="overview" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18753,88 +18779,89 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>735</v>
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>738</v>
       </c>
       <c r="C2" s="278" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>735</v>
-      </c>
-      <c r="B3" t="s">
-        <v>516</v>
+        <v>740</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>517</v>
       </c>
       <c r="C3" s="278" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>738</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>735</v>
-      </c>
       <c r="C4" s="278" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>740</v>
+        <v>742</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>743</v>
       </c>
       <c r="C5" s="278" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>740</v>
+        <v>744</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>743</v>
       </c>
       <c r="C6" s="278" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1200-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" xr:uid="{00000000-0004-0000-1200-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" xr:uid="{00000000-0004-0000-1200-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" xr:uid="{00000000-0004-0000-1200-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" xr:uid="{00000000-0004-0000-1200-000004000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" r:id="rId2"/>
+    <hyperlink ref="C4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" r:id="rId3"/>
+    <hyperlink ref="C5" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" r:id="rId4"/>
+    <hyperlink ref="C6" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FB81B8-A234-4EA6-8FB5-B1AA8CB50C92}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>456</v>
       </c>
@@ -18851,8 +18878,8 @@
         <v>460</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -18861,15 +18888,15 @@
       <c r="C2" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -18878,15 +18905,15 @@
       <c r="C3" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -18895,74 +18922,92 @@
       <c r="C4" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>468</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>469</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>470</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>471</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>8</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>472</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="C4" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+    <hyperlink ref="B3" r:id="rId3"/>
+    <hyperlink ref="C3" r:id="rId4"/>
+    <hyperlink ref="B4" r:id="rId5"/>
+    <hyperlink ref="C4" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18976,103 +19021,104 @@
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5">
       <c r="A2" s="336" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="B2" s="173" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C2" s="277" t="s">
-        <v>744</v>
-      </c>
-      <c r="D2" t="s">
+        <v>747</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>723</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>720</v>
       </c>
-      <c r="E2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" ht="29">
       <c r="A3" s="336"/>
       <c r="B3" s="173" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="D3" t="s">
-        <v>747</v>
-      </c>
-      <c r="E3" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>748</v>
-      </c>
-      <c r="B5" t="s">
         <v>749</v>
       </c>
+      <c r="D3" s="0" t="s">
+        <v>750</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>752</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="D5" t="s">
-        <v>733</v>
-      </c>
-      <c r="E5" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>753</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>736</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>751</v>
-      </c>
-      <c r="B7" t="s">
-        <v>752</v>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>755</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="D7" t="s">
-        <v>754</v>
-      </c>
-      <c r="E7" t="s">
-        <v>717</v>
+        <v>756</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>757</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>720</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1300-000001000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-1300-000002000000}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-1300-000003000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C5" r:id="rId3"/>
+    <hyperlink ref="C7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19085,117 +19131,118 @@
     <col min="2" max="2" width="77.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="275" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="279" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B2" s="280" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="3" ht="43.5">
       <c r="A3" s="281" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B3" s="282" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="4" ht="43.5">
       <c r="A4" s="281" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B4" s="282" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="5" ht="101.5">
       <c r="A5" s="281" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B5" s="283" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6" ht="29">
       <c r="A6" s="281" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B6" s="282" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="279" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B7" s="280" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="279" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B8" s="280" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="9" ht="72.5">
       <c r="A9" s="281" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B9" s="282" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="279" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B10" s="280" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="284" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B11" s="280" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="12" ht="58">
       <c r="A12" s="285" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B12" s="282" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-1400-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" xr:uid="{00000000-0004-0000-1400-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" xr:uid="{00000000-0004-0000-1400-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-1400-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" xr:uid="{00000000-0004-0000-1400-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" xr:uid="{00000000-0004-0000-1400-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" xr:uid="{00000000-0004-0000-1400-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" xr:uid="{00000000-0004-0000-1400-000007000000}"/>
-    <hyperlink ref="B10" r:id="rId9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" xr:uid="{00000000-0004-0000-1400-000008000000}"/>
-    <hyperlink ref="B11" r:id="rId10" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" xr:uid="{00000000-0004-0000-1400-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-1400-00000A000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" r:id="rId2"/>
+    <hyperlink ref="B4" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" r:id="rId5"/>
+    <hyperlink ref="B7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" r:id="rId6"/>
+    <hyperlink ref="B8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" r:id="rId7"/>
+    <hyperlink ref="B9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" r:id="rId8"/>
+    <hyperlink ref="B10" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" r:id="rId9"/>
+    <hyperlink ref="B11" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" r:id="rId10"/>
+    <hyperlink ref="B12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19208,36 +19255,37 @@
     <col min="2" max="2" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="67" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B1" s="67" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5">
       <c r="A2" s="286" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="3" ht="43.5">
       <c r="A3" s="286" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-1500-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-1500-000001000000}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19250,63 +19298,64 @@
     <col min="2" max="2" width="48.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>672</v>
-      </c>
-      <c r="B1" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>675</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B3" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="B5" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>786</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="B7" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>788</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="B8" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>790</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="B9" t="s">
-        <v>790</v>
+        <v>792</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>793</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-1600-000000000000}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{00000000-0004-0000-1600-000001000000}"/>
-    <hyperlink ref="A7" r:id="rId3" xr:uid="{00000000-0004-0000-1600-000002000000}"/>
-    <hyperlink ref="A8" r:id="rId4" xr:uid="{00000000-0004-0000-1600-000003000000}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{00000000-0004-0000-1600-000004000000}"/>
+    <hyperlink ref="A3" r:id="rId1"/>
+    <hyperlink ref="A5" r:id="rId2"/>
+    <hyperlink ref="A7" r:id="rId3"/>
+    <hyperlink ref="A8" r:id="rId4"/>
+    <hyperlink ref="A9" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19319,45 +19368,46 @@
     <col min="2" max="2" width="42.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="287" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="B1" s="276" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="114" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="71" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="71" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" xr:uid="{00000000-0004-0000-1700-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://becurious.edcast.eu/pathways/azure-sql-this" xr:uid="{00000000-0004-0000-1700-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" location="overview" display="IICS Complated Guide" xr:uid="{00000000-0004-0000-1700-000002000000}"/>
+    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" r:id="rId1"/>
+    <hyperlink ref="B3" display="https://becurious.edcast.eu/pathways/azure-sql-this" r:id="rId2"/>
+    <hyperlink ref="B4" location="overview" display="IICS Complated Guide" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19372,399 +19422,400 @@
     <col min="5" max="5" width="57.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="C2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2" s="0">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D3" s="0">
+        <v>2</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="D4" s="0">
+        <v>3</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D7" s="0">
+        <v>2</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="D8" s="0">
+        <v>3</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>9</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="D9" s="0">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>10</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D10" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E10" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>11</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="D11" s="0">
+        <v>3</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>12</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="D12" s="0">
+        <v>4</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>13</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>479</v>
       </c>
-      <c r="D3">
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>14</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D14" s="0">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E14" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>15</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="D15" s="0">
+        <v>3</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>16</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="D16" s="0">
+        <v>4</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>17</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>478</v>
+      </c>
+      <c r="D17" s="0">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>18</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="D18" s="0">
+        <v>2</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>19</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="D19" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C4" t="s">
-        <v>481</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="E19" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>20</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" t="s">
-        <v>483</v>
-      </c>
-      <c r="D5">
+      <c r="E20" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>21</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="D21" s="0">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="E21" s="0" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>22</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>486</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>494</v>
+      </c>
+      <c r="D22" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>485</v>
-      </c>
-      <c r="C6" t="s">
-        <v>486</v>
-      </c>
-      <c r="D6">
+      <c r="E22" s="0" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>23</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="D23" s="0">
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>485</v>
-      </c>
-      <c r="C7" t="s">
-        <v>479</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>485</v>
-      </c>
-      <c r="C8" t="s">
-        <v>481</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>488</v>
-      </c>
-      <c r="C9" t="s">
-        <v>477</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>488</v>
-      </c>
-      <c r="C10" t="s">
-        <v>479</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>488</v>
-      </c>
-      <c r="C11" t="s">
-        <v>481</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>488</v>
-      </c>
-      <c r="C12" t="s">
-        <v>483</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>489</v>
-      </c>
-      <c r="C13" t="s">
-        <v>477</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>489</v>
-      </c>
-      <c r="C14" t="s">
-        <v>479</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>489</v>
-      </c>
-      <c r="C15" t="s">
-        <v>481</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>489</v>
-      </c>
-      <c r="C16" t="s">
-        <v>483</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>490</v>
-      </c>
-      <c r="C17" t="s">
-        <v>477</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>490</v>
-      </c>
-      <c r="C18" t="s">
-        <v>479</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>490</v>
-      </c>
-      <c r="C19" t="s">
-        <v>481</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>490</v>
-      </c>
-      <c r="C20" t="s">
-        <v>483</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>485</v>
-      </c>
-      <c r="C21" t="s">
-        <v>491</v>
-      </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>485</v>
-      </c>
-      <c r="C22" t="s">
-        <v>493</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-      <c r="E22" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" t="s">
-        <v>486</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>495</v>
+      <c r="E23" s="0" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19779,201 +19830,202 @@
     <col min="5" max="5" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>2</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>38</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>500</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="0" t="s">
+        <v>501</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>5</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>34</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E4" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="E4" s="0" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>80</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="0">
         <v>7</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>80</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="0">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>25</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="0">
         <v>9</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="0">
         <v>10</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>25</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" s="0">
         <v>11</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>25</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="D10" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
         <v>12</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>25</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>22</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="0" t="s">
         <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5417B356-7CA8-4073-B5EA-2ED7E0869648}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.36328125" customWidth="1"/>
@@ -19983,7 +20035,7 @@
     <col min="5" max="5" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="4" t="s">
         <v>504</v>
       </c>
@@ -20000,85 +20052,103 @@
         <v>505</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" s="0">
         <v>80</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>346</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="0">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>510</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>16</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>511</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14947C1-2082-4307-8EB3-961E6465F131}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -20089,37 +20159,37 @@
     <col min="6" max="6" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="3">
@@ -20129,34 +20199,34 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>515</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>320</v>
       </c>
       <c r="E3" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>516</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="3">
@@ -20166,17 +20236,17 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>78</v>
       </c>
-      <c r="C5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="3">
@@ -20186,76 +20256,98 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>320</v>
       </c>
       <c r="E6" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>78</v>
       </c>
-      <c r="C7" t="s">
-        <v>517</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" s="0" t="s">
+        <v>518</v>
+      </c>
+      <c r="D7" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0">
+        <v>94</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0">
+        <v>55</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>80</v>
+      </c>
+      <c r="C10" s="0" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>94</v>
-      </c>
-      <c r="C8" t="s">
-        <v>514</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D10" s="0" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>55</v>
-      </c>
-      <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" t="s">
-        <v>519</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E10" s="0" t="s">
         <v>520</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>522</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -20277,42 +20369,42 @@
     <col min="11" max="11" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" ht="58">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" ht="126" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -20337,13 +20429,13 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -20357,7 +20449,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>127</v>
@@ -20368,11 +20460,11 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -20386,7 +20478,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>127</v>
@@ -20395,15 +20487,15 @@
         <v>127</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -20426,20 +20518,20 @@
         <v>127</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="5"/>
@@ -20451,7 +20543,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -20477,12 +20569,12 @@
         <v>190</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -20499,7 +20591,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="82" customHeight="1">
       <c r="A9" s="5">
         <v>9</v>
       </c>
@@ -20525,10 +20617,10 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="11" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -20552,12 +20644,12 @@
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="246" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="246" customHeight="1">
       <c r="A11" s="5">
         <v>11</v>
       </c>
@@ -20571,7 +20663,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>45</v>
@@ -20580,15 +20672,15 @@
         <v>45</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="11" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="12" ht="58.5" customHeight="1">
       <c r="A12" s="5">
         <v>12</v>
       </c>
@@ -20612,16 +20704,16 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="5">
         <v>13</v>
       </c>
@@ -20648,7 +20740,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="5">
         <v>14</v>
       </c>
@@ -20671,15 +20763,15 @@
         <v>127</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="5">
         <v>15</v>
       </c>
@@ -20700,17 +20792,17 @@
         <v>127</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="71" customHeight="1">
       <c r="A16" s="5">
         <v>16</v>
       </c>
@@ -20723,8 +20815,8 @@
       <c r="D16" s="5">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>548</v>
+      <c r="E16" s="0" t="s">
+        <v>550</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>45</v>
@@ -20733,17 +20825,17 @@
         <v>127</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="17" ht="134" customHeight="1">
       <c r="A17" s="5">
         <v>17</v>
       </c>
@@ -20766,24 +20858,24 @@
         <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="12">
         <v>18</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>50</v>
@@ -20792,7 +20884,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>127</v>
@@ -20801,20 +20893,20 @@
         <v>127</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="5">
         <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>50</v>
@@ -20823,7 +20915,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>127</v>
@@ -20836,12 +20928,12 @@
       <c r="J19" s="6"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="5">
         <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>50</v>
@@ -20863,12 +20955,12 @@
       <c r="J20" s="6"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="5">
         <v>21</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>50</v>
@@ -20890,7 +20982,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -20913,17 +21005,17 @@
         <v>127</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -20946,7 +21038,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="60.5" customHeight="1">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20960,7 +21052,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>127</v>
@@ -20972,15 +21064,15 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="5">
         <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>50</v>
@@ -21002,12 +21094,12 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="5">
         <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>50</v>
@@ -21029,7 +21121,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="5">
         <v>28</v>
       </c>
@@ -21043,7 +21135,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>127</v>
@@ -21058,12 +21150,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="55.5" customHeight="1">
       <c r="A28" s="5">
         <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>50</v>
@@ -21084,15 +21176,15 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="8" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="29" ht="68.5" customHeight="1">
       <c r="A29" s="5">
         <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>50</v>
@@ -21113,11 +21205,12 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="8" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -21143,11 +21236,11 @@
     <col min="14" max="14" width="18.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="314" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D1" s="315"/>
       <c r="E1" s="315"/>
@@ -21158,17 +21251,17 @@
       <c r="J1" s="315"/>
       <c r="K1" s="316"/>
       <c r="L1" s="317" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M1" s="318"/>
       <c r="N1" s="318"/>
     </row>
-    <row r="2" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" ht="58">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
       <c r="D2" s="319" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E2" s="319"/>
       <c r="F2" s="319"/>
@@ -21176,75 +21269,75 @@
       <c r="H2" s="319"/>
       <c r="I2" s="319"/>
       <c r="J2" s="26" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="K2" s="27"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="43.5">
       <c r="A3" s="28" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N3" s="29" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="24" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>127</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G4" s="25">
         <v>0</v>
@@ -21253,7 +21346,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>63</v>
@@ -21265,24 +21358,24 @@
         <v>45</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N4" s="25">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="35" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C5" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E5" s="38" t="s">
         <v>63</v>
@@ -21307,15 +21400,15 @@
         <v>45</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N5" s="37">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="35" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>269</v>
@@ -21357,62 +21450,62 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="35" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N7" s="37">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="35" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E8" s="41">
         <v>0.5</v>
@@ -21431,30 +21524,30 @@
         <v>48</v>
       </c>
       <c r="K8" s="40" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N8" s="37">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" ht="29">
       <c r="A9" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C9" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>63</v>
@@ -21481,13 +21574,13 @@
         <v>45</v>
       </c>
       <c r="M9" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N9" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="24" t="s">
         <v>59</v>
       </c>
@@ -21498,7 +21591,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E10" s="41">
         <v>1</v>
@@ -21516,33 +21609,33 @@
         <v>63</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N10" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" ht="29">
       <c r="A11" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E11" s="41">
         <v>1</v>
@@ -21560,22 +21653,22 @@
         <v>63</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N11" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="24" t="s">
         <v>59</v>
       </c>
@@ -21586,7 +21679,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E12" s="49">
         <v>0.8</v>
@@ -21607,30 +21700,30 @@
         <v>253</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L12" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N12" s="43">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C13" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E13" s="41">
         <v>0.5</v>
@@ -21648,7 +21741,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K13" s="54">
         <v>9618241586</v>
@@ -21657,18 +21750,18 @@
         <v>45</v>
       </c>
       <c r="M13" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N13" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="25" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>127</v>
@@ -21707,7 +21800,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="24" t="s">
         <v>59</v>
       </c>
@@ -21745,13 +21838,13 @@
         <v>45</v>
       </c>
       <c r="M15" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N15" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="24" t="s">
         <v>59</v>
       </c>
@@ -21777,13 +21870,13 @@
         <v>210</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>127</v>
@@ -21795,18 +21888,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>63</v>
@@ -21839,18 +21932,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="64" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E18" s="41">
         <v>0.5</v>
@@ -21868,57 +21961,58 @@
         <v>46049</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M18" s="43" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="N18" s="43">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>235</v>
       </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>593</v>
-      </c>
-      <c r="E19" t="s">
-        <v>612</v>
-      </c>
-      <c r="F19" t="s">
-        <v>518</v>
-      </c>
-      <c r="G19" t="s">
-        <v>613</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="C19" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="E19" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="K19" t="s">
+      <c r="F19" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="G19" s="0" t="s">
         <v>615</v>
       </c>
+      <c r="J19" s="0" t="s">
+        <v>616</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>617</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="D2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -21933,30 +22027,30 @@
     <col min="5" max="5" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="76" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C1" s="76" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D1" s="76" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E1" s="76" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="320" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C2" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!U1:U679, "Y")</f>
@@ -21971,10 +22065,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="320"/>
       <c r="B3" s="6" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C3" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!V1:V679, "Y")</f>
@@ -21989,10 +22083,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="320"/>
       <c r="B4" s="6" t="s">
-        <v>517</v>
+        <v>624</v>
       </c>
       <c r="C4" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!AB1:AB679, "Y")</f>
@@ -22007,22 +22101,22 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>622</v>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>625</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="B7" s="6" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C7" s="68">
         <v>36</v>
@@ -22032,37 +22126,37 @@
       </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="321" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B9" s="321"/>
       <c r="C9" s="321"/>
-      <c r="D9" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D9" s="0" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="69"/>
       <c r="B10" s="69" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="70" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B11" s="322">
         <v>74</v>
       </c>
       <c r="C11" s="322"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="71" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B12" s="72">
         <v>61</v>
@@ -22071,9 +22165,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="71" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B13" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
@@ -22083,9 +22177,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="71" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B14" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "N")</f>
@@ -22093,9 +22187,9 @@
       </c>
       <c r="C14" s="71"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="74" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B15" s="75">
         <v>26</v>
@@ -22104,26 +22198,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="71" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B16" s="72">
         <f>B12-B15</f>
         <v>35</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to TeamTracker under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Data/TeamTracker.xlsx
+++ b/Data/TeamTracker.xlsx
@@ -41,7 +41,7 @@
   <externalReferences>
     <externalReference r:id="rId25"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId26"/>
     <pivotCache cacheId="1" r:id="rId27"/>
@@ -80,26 +80,35 @@
   <commentList>
     <comment ref="Y39" authorId="0" shapeId="0" xr:uid="{A76EB6EC-838A-4804-B11A-4B53BE1844C8}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y40" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="Y41" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Completed AI anthropic training</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Completed AI anthropic training_x000A_</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -117,34 +126,46 @@
   <commentList>
     <comment ref="K15" authorId="0" shapeId="0" xr:uid="{E8742F7E-8B8E-40B8-88FA-1BF58FA61E56}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Connect with GD onshore team</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Connect with GD onshore team_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K16" authorId="1" shapeId="0" xr:uid="{2B8B1264-9F08-40E1-9040-B79527887B45}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_8:30 AM to 9: 00 AM PST with onshore Deloitte conterparts Gerardo,Prathyusha .Mon,Tue,Thu,Fri_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K17" authorId="2" shapeId="0" xr:uid="{B23C388E-2E4B-496D-A7D5-EFA61D303073}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Previously these calls were scheduled. It was cancelled due to time constraints. Currently, 1 separate call with onshore Deloitte team is scheduled Weekly (on Wednesday)but Sean from GD joins this call, along with Souwmya, Daniel_x000A_</t>
+        </r>
       </text>
     </comment>
     <comment ref="K22" authorId="3" shapeId="0" xr:uid="{6A7DE910-52BF-4905-9039-3376F875BE51}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Tech Sync calls are there with onshore GD teams</t>
+        <r>
+          <rPr>
+            <rFont val="Aptos Narrow"/>
+            <sz val="11"/>
+          </rPr>
+          <t xml:space="preserve">This comment reflects a threaded comment in this cell, a feature that might be supported by newer versions of your spreadsheet program (for example later versions of Excel). Any edits will be overwritten if opened in a spreadsheet program that supports threaded comments._x000A__x000A_Comment:_x000A_Tech Sync calls are there with onshore GD teams_x000A_</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -152,7 +173,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3558" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="797">
   <si>
     <t>SrNo</t>
   </si>
@@ -370,7 +391,7 @@
     <t>Firewire Modernization 2.0</t>
   </si>
   <si>
-    <t>We are going through KT videos.
+    <t xml:space="preserve">We are going through KT videos.
 Delivery not started yet.</t>
   </si>
   <si>
@@ -605,7 +626,7 @@
     <t>In progress</t>
   </si>
   <si>
-    <t>Client compliance Training Completed ,  Started working on Project Task</t>
+    <t xml:space="preserve">Client compliance Training Completed ,  Started working on Project Task</t>
   </si>
   <si>
     <t>Anand Maurya</t>
@@ -982,7 +1003,7 @@
     <t>Alex</t>
   </si>
   <si>
-    <t>VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
+    <t xml:space="preserve">VDI Received and going through KT videos. Waiting for GD leader response.    Client compliance email not received</t>
   </si>
   <si>
     <t>Abinesh C</t>
@@ -1094,7 +1115,7 @@
     <t>JIRA</t>
   </si>
   <si>
-    <t>VDI  received</t>
+    <t xml:space="preserve">VDI  received</t>
   </si>
   <si>
     <t>Kammeta, Prathap</t>
@@ -1115,7 +1136,7 @@
     <t>Inprogress</t>
   </si>
   <si>
-    <t>VDI Setup Done, Required tools setup completed (Ready API, JMeter)
+    <t xml:space="preserve">VDI Setup Done, Required tools setup completed (Ready API, JMeter)
 Client compliance email not received</t>
   </si>
   <si>
@@ -1152,7 +1173,7 @@
     <t>Mathew Romstadt</t>
   </si>
   <si>
-    <t>DUO setup done. VDI is accessible.
+    <t xml:space="preserve">DUO setup done. VDI is accessible.
 Received Compliance training email. Completed compliance training.
 Raised AG tickets for Confluence, Github and ReadyAPI.
 VDI setup done</t>
@@ -1551,6 +1572,15 @@
     <t>psharma@deloitte.com</t>
   </si>
   <si>
+    <t>And@1234</t>
+  </si>
+  <si>
+    <t>psharmht@deloitte.com</t>
+  </si>
+  <si>
+    <t>Srmulla@12</t>
+  </si>
+  <si>
     <t>StepID</t>
   </si>
   <si>
@@ -1620,6 +1650,12 @@
     <t>Install all necessary softwares and register in git.</t>
   </si>
   <si>
+    <t>Verify Validation</t>
+  </si>
+  <si>
+    <t>Validation Progress</t>
+  </si>
+  <si>
     <t>ProgressID</t>
   </si>
   <si>
@@ -1647,6 +1683,9 @@
     <t>2026-09-09</t>
   </si>
   <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
     <t>CandidateId</t>
   </si>
   <si>
@@ -1722,26 +1761,26 @@
     <t>Has Team Member(s) in ADMX? (Y/N)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Offshore)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Onshore / GD)</t>
   </si>
   <si>
-    <t>Scrum Master
+    <t xml:space="preserve">Scrum Master
 (Release)</t>
   </si>
   <si>
-    <t>Internal Meeting Cadence 
+    <t xml:space="preserve">Internal Meeting Cadence 
 (If has Team in USA / ADMX)</t>
   </si>
   <si>
     <t>Rekha/Meenakshi</t>
   </si>
   <si>
-    <t>M,T,TH,F - 10:30 - 11:00 PM IST 
+    <t xml:space="preserve">M,T,TH,F - 10:30 - 11:00 PM IST 
 USA : Daily Connect with Michael Griffin  
 Mexico : Daily Connect with Jesus Enrique Rivera Hernandez</t>
   </si>
@@ -1873,30 +1912,29 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Team Member Available for 
-W/E 21st</t>
+      <t>Team Member Available for _x000A_W/E 21st</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> June</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
       <t xml:space="preserve"> Support</t>
     </r>
@@ -1908,7 +1946,7 @@
     <t>Track Name</t>
   </si>
   <si>
-    <t>PROD Support Applicable 
+    <t xml:space="preserve">PROD Support Applicable 
 (Y/N)</t>
   </si>
   <si>
@@ -2218,7 +2256,7 @@
     <t>Total No. of Resources</t>
   </si>
   <si>
-    <t>Additional Tools  Access requested specific to skillset</t>
+    <t xml:space="preserve">Additional Tools  Access requested specific to skillset</t>
   </si>
   <si>
     <t>Key Highlights</t>
@@ -2232,10 +2270,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Firewire: Github, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2246,10 +2284,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Both resources are going through KT recordings.</t>
     </r>
@@ -2260,10 +2298,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Access to Github, Sciforma are pending for one resource</t>
     </r>
@@ -2277,10 +2315,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>ArcPlatform: Confluence, VS2022 (.Net Framework &amp; .Net Core), GitHub, GitHub Copilot, DB Access - Non/ Prod, DataDog, Team City, Octopus, Azure DevOps, Prod VDI, ActiveBatch, CosmosDB, RedShift, SSMS</t>
     </r>
@@ -2291,10 +2329,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">One resource pending with Dev environment setup in progress and started with the KT confluence page &amp; recordings. </t>
     </r>
@@ -2305,10 +2343,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Github, Informatica, AWS Redshift</t>
     </r>
@@ -2319,10 +2357,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Currently progressing on project deliverables for OnePay Wallet</t>
     </r>
@@ -2333,10 +2371,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>DC1 (prod server), Informatica POC (Shared path for code), Azure SQL DB, Microsoft SQL Server</t>
     </r>
@@ -2347,10 +2385,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 of 3 resources are working on prod support</t>
     </r>
@@ -2364,20 +2402,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>IDE</t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>: Android Studio for Android, and XCode for iOS</t>
     </r>
@@ -2388,10 +2426,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Received macOS VDI details, but unable to access due to IP address issue (GD team is working on the resolution).</t>
     </r>
@@ -2402,20 +2440,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve">Github: </t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Copilot access if being used by client</t>
     </r>
@@ -2426,10 +2464,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Going through KT and Onboarding contents. Project delivery is yet to start. Further info on Project Delivery after today's client connect</t>
     </r>
@@ -2440,20 +2478,20 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <b/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Git GUI tool:</t>
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t xml:space="preserve"> Sourcetree or Github Desktop</t>
     </r>
@@ -2467,10 +2505,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>Git Hub, Azure Portal, ADO NP, ADO PROD, DC1 Account, CyberArk, Datadog, 9 Account, JumpBox, Teamcity, Octopus, Atlassian, Jfrog artifactory</t>
     </r>
@@ -2481,10 +2519,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 resources are Working on the Legacy Non-Prod &amp; PRD Deployments.</t>
     </r>
@@ -2495,10 +2533,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>2 resources are awaiting VDI access.</t>
     </r>
@@ -2509,10 +2547,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>VS code and JIRA</t>
     </r>
@@ -2523,10 +2561,10 @@
     </r>
     <r>
       <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
         <rFont val="Verdana"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="10.5"/>
       </rPr>
       <t>One resource is going through KT videos and started on JIRA story TAX-72949 from Sprint 141 and other resource is yet to start.</t>
     </r>
@@ -2695,15 +2733,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)
-</t>
+      <t xml:space="preserve">Complete Guide To Unit Testing in .Net Core (NUnit &amp; XUnit)_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section 1 - 4</t>
     </r>
@@ -2713,15 +2750,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code
-</t>
+      <t xml:space="preserve">How to Write BulletProof Multi-Threaded C# Code_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section Introducing Thread Locking</t>
     </r>
@@ -2731,22 +2767,16 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Learn Parallel Programming with C# and .NET
-</t>
+      <t xml:space="preserve">Learn Parallel Programming with C# and .NET_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Sections:
-- Task Programing
-- Concurrent Collection
-- [Optional] Task Coordination
-- Async Programming
-+ Task.WhenAll(), Task.WhenAny()</t>
+      <t>Only Sections:_x000A_- Task Programing_x000A_- Concurrent Collection_x000A_- [Optional] Task Coordination_x000A_- Async Programming_x000A_+ Task.WhenAll(), Task.WhenAny()</t>
     </r>
   </si>
   <si>
@@ -2754,15 +2784,14 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide
-</t>
+      <t xml:space="preserve">Asp.Net Core 8 (.NET 8) | True Ultimate Guide_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
       <t>Only Section 4 Middleware</t>
     </r>
@@ -2785,23 +2814,21 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FF000000"/>
+        <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">RabbitMQ and Messaging Concepts
-</t>
+      <t xml:space="preserve">RabbitMQ and Messaging Concepts_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Section:
-[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
+      <t>Only Section:_x000A_[Section: Microservices Async Communication w/ RabbitMQ &amp; MassTransit for Checkout Order]</t>
     </r>
   </si>
   <si>
@@ -2821,18 +2848,16 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Modern dotnet testing
-</t>
+      <t xml:space="preserve">Modern dotnet testing_x000A_</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <color rgb="FFFF0000"/>
+        <sz val="11"/>
       </rPr>
-      <t>Only Section:
-Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
+      <t>Only Section:_x000A_Integration Testing of Application - WebApplicationFactory, Service Isolation..]</t>
     </r>
   </si>
   <si>
@@ -2903,7 +2928,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3129,19 +3155,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -3152,13 +3165,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="5" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3200,7 +3213,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3212,13 +3225,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -3747,638 +3760,638 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="1" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="327">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="10" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="12" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="15" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" applyFont="1" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="3" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="18" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="18" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="14" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="16" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="2" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="8" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="25" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="11" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="24" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="5" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="13" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="17" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="20" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="17" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="12" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="11" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="14" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="22" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="22" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="22" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="15" applyFill="1" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyBorder="1" xfId="0"/>
+    <xf numFmtId="16" applyNumberFormat="1" fontId="17" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="29" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="9" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="4" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="30" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="9" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="23" applyFont="1" fillId="15" applyFill="1" borderId="4" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="26" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="0" borderId="31" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="16" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="21" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="28" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="15" applyBorder="1" xfId="1"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="11" applyFont="1" fillId="0" borderId="15" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="0" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="12" applyFill="1" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="24" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="11" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="1" applyBorder="1" xfId="1"/>
+    <xf numFmtId="15" applyNumberFormat="1" fontId="0" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="20" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" applyNumberFormat="1" fontId="20" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" applyFont="1" fillId="11" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="11" applyFont="1" fillId="0" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" applyFill="1" borderId="1" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="27" applyFont="1" fillId="12" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="4" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="1" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" applyFont="1" fillId="16" applyFill="1" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" applyFont="1" fillId="17" applyFill="1" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="39" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="34" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="40" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" applyFont="1" fillId="0" borderId="42" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="33" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="35" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="7" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="5" applyFill="1" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" applyFont="1" fillId="7" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="9" applyFill="1" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="11" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="12" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="13" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" applyFont="1" fillId="0" borderId="14" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="36" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="37" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="43" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="38" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" applyFont="1" fillId="0" borderId="41" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7392,7 +7405,7 @@
     <col min="2" max="2" width="27.26953125" customWidth="1"/>
     <col min="3" max="3" width="29.1796875" customWidth="1"/>
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
-    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" bestFit="1" width="10.08984375" customWidth="1"/>
     <col min="8" max="8" width="14.54296875" customWidth="1"/>
     <col min="9" max="9" width="13.54296875" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
@@ -7414,7 +7427,7 @@
     <col min="35" max="35" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
@@ -7521,7 +7534,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="87">
         <v>1</v>
       </c>
@@ -7596,7 +7609,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="71">
         <v>2</v>
       </c>
@@ -7668,7 +7681,7 @@
       </c>
       <c r="AH3" s="71"/>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="71">
         <v>3</v>
       </c>
@@ -7766,7 +7779,7 @@
       </c>
       <c r="AH4" s="71"/>
     </row>
-    <row r="5" spans="1:35" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" ht="43.5">
       <c r="A5" s="71">
         <v>4</v>
       </c>
@@ -7866,7 +7879,7 @@
       </c>
       <c r="AH5" s="71"/>
     </row>
-    <row r="6" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="6" ht="101.5">
       <c r="A6" s="71">
         <v>5</v>
       </c>
@@ -7966,7 +7979,7 @@
       </c>
       <c r="AH6" s="71"/>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="71">
         <v>6</v>
       </c>
@@ -7979,16 +7992,16 @@
       <c r="D7" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>50</v>
       </c>
       <c r="F7" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="0" t="s">
         <v>39</v>
       </c>
       <c r="I7" s="94" t="s">
@@ -8064,7 +8077,7 @@
       </c>
       <c r="AH7" s="71"/>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="71">
         <v>7</v>
       </c>
@@ -8156,7 +8169,7 @@
       </c>
       <c r="AH8" s="71"/>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="71">
         <v>8</v>
       </c>
@@ -8248,7 +8261,7 @@
       </c>
       <c r="AH9" s="71"/>
     </row>
-    <row r="10" spans="1:35" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" ht="87">
       <c r="A10" s="87">
         <v>9</v>
       </c>
@@ -8320,7 +8333,7 @@
       </c>
       <c r="AH10" s="107"/>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="71">
         <v>10</v>
       </c>
@@ -8339,10 +8352,10 @@
       <c r="F11" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="0" t="s">
         <v>39</v>
       </c>
       <c r="I11" s="94" t="s">
@@ -8418,7 +8431,7 @@
       </c>
       <c r="AH11" s="94"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="71">
         <v>11</v>
       </c>
@@ -8518,7 +8531,7 @@
       </c>
       <c r="AH12" s="94"/>
     </row>
-    <row r="13" spans="1:35" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" ht="101.5">
       <c r="A13" s="71">
         <v>12</v>
       </c>
@@ -8616,7 +8629,7 @@
       </c>
       <c r="AH13" s="94"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="87">
         <v>13</v>
       </c>
@@ -8702,7 +8715,7 @@
       </c>
       <c r="AH14" s="89"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="71">
         <v>14</v>
       </c>
@@ -8794,7 +8807,7 @@
       </c>
       <c r="AH15" s="94"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="71">
         <v>15</v>
       </c>
@@ -8888,7 +8901,7 @@
       </c>
       <c r="AH16" s="94"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="71">
         <v>16</v>
       </c>
@@ -8907,7 +8920,7 @@
       <c r="F17" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="112" t="s">
@@ -8931,7 +8944,7 @@
       <c r="N17" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="O17" t="s">
+      <c r="O17" s="0" t="s">
         <v>124</v>
       </c>
       <c r="P17" s="71" t="s">
@@ -8988,7 +9001,7 @@
       </c>
       <c r="AH17" s="94"/>
     </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="71">
         <v>17</v>
       </c>
@@ -9007,7 +9020,7 @@
       <c r="F18" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H18" s="71" t="s">
@@ -9082,7 +9095,7 @@
       </c>
       <c r="AH18" s="94"/>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="71">
         <v>18</v>
       </c>
@@ -9178,7 +9191,7 @@
       </c>
       <c r="AH19" s="94"/>
     </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="71">
         <v>19</v>
       </c>
@@ -9272,7 +9285,7 @@
       </c>
       <c r="AH20" s="94"/>
     </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="87">
         <v>20</v>
       </c>
@@ -9364,7 +9377,7 @@
       </c>
       <c r="AH21" s="89"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="71">
         <v>21</v>
       </c>
@@ -9460,7 +9473,7 @@
       </c>
       <c r="AH22" s="94"/>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="71">
         <v>22</v>
       </c>
@@ -9482,7 +9495,7 @@
       <c r="G23" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="0" t="s">
         <v>148</v>
       </c>
       <c r="I23" s="113" t="s">
@@ -9558,7 +9571,7 @@
       </c>
       <c r="AH23" s="94"/>
     </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="71">
         <v>23</v>
       </c>
@@ -9577,7 +9590,7 @@
       <c r="F24" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H24" s="71" t="s">
@@ -9648,7 +9661,7 @@
       </c>
       <c r="AH24" s="94"/>
     </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="71">
         <v>24</v>
       </c>
@@ -9691,7 +9704,7 @@
       <c r="N25" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="O25" t="s">
+      <c r="O25" s="0" t="s">
         <v>124</v>
       </c>
       <c r="P25" s="71" t="s">
@@ -9746,7 +9759,7 @@
       </c>
       <c r="AH25" s="94"/>
     </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="71">
         <v>25</v>
       </c>
@@ -9759,13 +9772,13 @@
       <c r="D26" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="0" t="s">
         <v>50</v>
       </c>
       <c r="F26" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="71" t="s">
@@ -9837,7 +9850,7 @@
         <v>8873884889</v>
       </c>
     </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="71">
         <v>26</v>
       </c>
@@ -9935,7 +9948,7 @@
       </c>
       <c r="AH27" s="94"/>
     </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="71">
         <v>27</v>
       </c>
@@ -10035,7 +10048,7 @@
       </c>
       <c r="AH28" s="94"/>
     </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="87">
         <v>28</v>
       </c>
@@ -10133,7 +10146,7 @@
       </c>
       <c r="AH29" s="125"/>
     </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="71">
         <v>29</v>
       </c>
@@ -10223,7 +10236,7 @@
       </c>
       <c r="AH30" s="94"/>
     </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="71">
         <v>30</v>
       </c>
@@ -10320,7 +10333,7 @@
         <v>8873884889</v>
       </c>
     </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="71">
         <v>31</v>
       </c>
@@ -10416,7 +10429,7 @@
       </c>
       <c r="AH32" s="134"/>
     </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="71">
         <v>32</v>
       </c>
@@ -10512,7 +10525,7 @@
       </c>
       <c r="AH33" s="111"/>
     </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="71">
         <v>33</v>
       </c>
@@ -10608,7 +10621,7 @@
       </c>
       <c r="AH34" s="94"/>
     </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="71">
         <v>34</v>
       </c>
@@ -10651,7 +10664,7 @@
       <c r="N35" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="O35" t="s">
+      <c r="O35" s="0" t="s">
         <v>124</v>
       </c>
       <c r="P35" s="71" t="s">
@@ -10702,7 +10715,7 @@
       </c>
       <c r="AH35" s="94"/>
     </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="87">
         <v>35</v>
       </c>
@@ -10794,7 +10807,7 @@
       </c>
       <c r="AH36" s="89"/>
     </row>
-    <row r="37" spans="1:34" ht="87" x14ac:dyDescent="0.35">
+    <row r="37" ht="87">
       <c r="A37" s="71">
         <v>36</v>
       </c>
@@ -10891,7 +10904,7 @@
         <v>8873884889</v>
       </c>
     </row>
-    <row r="38" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="71">
         <v>37</v>
       </c>
@@ -10987,7 +11000,7 @@
       </c>
       <c r="AH38" s="94"/>
     </row>
-    <row r="39" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="71">
         <v>38</v>
       </c>
@@ -11030,7 +11043,7 @@
       <c r="N39" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="O39" t="s">
+      <c r="O39" s="0" t="s">
         <v>124</v>
       </c>
       <c r="P39" s="71" t="s">
@@ -11079,7 +11092,7 @@
       </c>
       <c r="AH39" s="71"/>
     </row>
-    <row r="40" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="71">
         <v>39</v>
       </c>
@@ -11175,7 +11188,7 @@
       </c>
       <c r="AH40" s="71"/>
     </row>
-    <row r="41" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="87">
         <v>40</v>
       </c>
@@ -11259,7 +11272,7 @@
       </c>
       <c r="AH41" s="87"/>
     </row>
-    <row r="42" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="71">
         <v>41</v>
       </c>
@@ -11357,7 +11370,7 @@
       </c>
       <c r="AH42" s="71"/>
     </row>
-    <row r="43" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="117">
         <v>42</v>
       </c>
@@ -11453,7 +11466,7 @@
       </c>
       <c r="AH43" s="117"/>
     </row>
-    <row r="44" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="87">
         <v>43</v>
       </c>
@@ -11547,7 +11560,7 @@
       </c>
       <c r="AH44" s="87"/>
     </row>
-    <row r="45" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="117">
         <v>44</v>
       </c>
@@ -11643,7 +11656,7 @@
       </c>
       <c r="AH45" s="117"/>
     </row>
-    <row r="46" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="71">
         <v>45</v>
       </c>
@@ -11741,7 +11754,7 @@
       </c>
       <c r="AH46" s="71"/>
     </row>
-    <row r="47" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="87">
         <v>46</v>
       </c>
@@ -11829,7 +11842,7 @@
       </c>
       <c r="AH47" s="87"/>
     </row>
-    <row r="48" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="87">
         <v>47</v>
       </c>
@@ -11915,7 +11928,7 @@
       </c>
       <c r="AH48" s="87"/>
     </row>
-    <row r="49" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="71">
         <v>48</v>
       </c>
@@ -12011,7 +12024,7 @@
       </c>
       <c r="AH49" s="71"/>
     </row>
-    <row r="50" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="71">
         <v>49</v>
       </c>
@@ -12109,7 +12122,7 @@
       </c>
       <c r="AH50" s="71"/>
     </row>
-    <row r="51" spans="1:34" ht="29" x14ac:dyDescent="0.35">
+    <row r="51" ht="29">
       <c r="A51" s="100">
         <v>50</v>
       </c>
@@ -12205,7 +12218,7 @@
       </c>
       <c r="AH51" s="100"/>
     </row>
-    <row r="52" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="71">
         <v>51</v>
       </c>
@@ -12301,7 +12314,7 @@
       </c>
       <c r="AH52" s="71"/>
     </row>
-    <row r="53" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="71">
         <v>52</v>
       </c>
@@ -12397,7 +12410,7 @@
       </c>
       <c r="AH53" s="71"/>
     </row>
-    <row r="54" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="87">
         <v>53</v>
       </c>
@@ -12491,7 +12504,7 @@
       </c>
       <c r="AH54" s="87"/>
     </row>
-    <row r="55" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="87">
         <v>54</v>
       </c>
@@ -12575,7 +12588,7 @@
       </c>
       <c r="AH55" s="87"/>
     </row>
-    <row r="56" spans="1:34" ht="58" x14ac:dyDescent="0.35">
+    <row r="56" ht="58">
       <c r="A56" s="71">
         <v>55</v>
       </c>
@@ -12669,7 +12682,7 @@
       </c>
       <c r="AH56" s="71"/>
     </row>
-    <row r="57" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="71">
         <v>56</v>
       </c>
@@ -12763,7 +12776,7 @@
       </c>
       <c r="AH57" s="71"/>
     </row>
-    <row r="58" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="87">
         <v>57</v>
       </c>
@@ -12857,7 +12870,7 @@
       </c>
       <c r="AH58" s="87"/>
     </row>
-    <row r="59" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="71">
         <v>58</v>
       </c>
@@ -12949,7 +12962,7 @@
       </c>
       <c r="AH59" s="71"/>
     </row>
-    <row r="60" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="71">
         <v>59</v>
       </c>
@@ -12992,7 +13005,7 @@
       <c r="N60" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="O60" t="s">
+      <c r="O60" s="0" t="s">
         <v>124</v>
       </c>
       <c r="P60" s="71" t="s">
@@ -13045,7 +13058,7 @@
       </c>
       <c r="AH60" s="71"/>
     </row>
-    <row r="61" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="87">
         <v>60</v>
       </c>
@@ -13117,7 +13130,7 @@
       </c>
       <c r="AH61" s="87"/>
     </row>
-    <row r="62" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="71">
         <v>61</v>
       </c>
@@ -13213,7 +13226,7 @@
       </c>
       <c r="AH62" s="71"/>
     </row>
-    <row r="63" spans="1:34" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" ht="29">
       <c r="A63" s="71">
         <v>62</v>
       </c>
@@ -13311,7 +13324,7 @@
       </c>
       <c r="AH63" s="71"/>
     </row>
-    <row r="64" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="71">
         <v>63</v>
       </c>
@@ -13409,7 +13422,7 @@
       </c>
       <c r="AH64" s="71"/>
     </row>
-    <row r="65" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="87">
         <v>64</v>
       </c>
@@ -13493,7 +13506,7 @@
       </c>
       <c r="AH65" s="87"/>
     </row>
-    <row r="66" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="117">
         <v>65</v>
       </c>
@@ -13542,7 +13555,7 @@
       <c r="P66" s="155" t="s">
         <v>304</v>
       </c>
-      <c r="Q66" t="s">
+      <c r="Q66" s="0" t="s">
         <v>305</v>
       </c>
       <c r="R66" s="117" t="s">
@@ -13589,7 +13602,7 @@
       </c>
       <c r="AH66" s="117"/>
     </row>
-    <row r="67" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="87">
         <v>66</v>
       </c>
@@ -13669,7 +13682,7 @@
       </c>
       <c r="AH67" s="87"/>
     </row>
-    <row r="68" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="71">
         <v>67</v>
       </c>
@@ -13765,7 +13778,7 @@
       </c>
       <c r="AH68" s="71"/>
     </row>
-    <row r="69" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="71">
         <v>68</v>
       </c>
@@ -13857,7 +13870,7 @@
       </c>
       <c r="AH69" s="71"/>
     </row>
-    <row r="70" spans="1:34" ht="87" x14ac:dyDescent="0.35">
+    <row r="70" ht="87">
       <c r="A70" s="71">
         <v>69</v>
       </c>
@@ -13957,7 +13970,7 @@
       </c>
       <c r="AH70" s="71"/>
     </row>
-    <row r="71" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="71">
         <v>70</v>
       </c>
@@ -14053,7 +14066,7 @@
       </c>
       <c r="AH71" s="71"/>
     </row>
-    <row r="72" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="117">
         <v>71</v>
       </c>
@@ -14153,7 +14166,7 @@
       </c>
       <c r="AH72" s="117"/>
     </row>
-    <row r="73" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="71">
         <v>72</v>
       </c>
@@ -14172,7 +14185,7 @@
       <c r="F73" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G73" s="0" t="s">
         <v>100</v>
       </c>
       <c r="H73" s="71" t="s">
@@ -14253,7 +14266,7 @@
       </c>
       <c r="AH73" s="71"/>
     </row>
-    <row r="74" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="71">
         <v>73</v>
       </c>
@@ -14275,7 +14288,7 @@
       <c r="G74" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="0" t="s">
         <v>52</v>
       </c>
       <c r="I74" s="94" t="s">
@@ -14353,7 +14366,7 @@
       </c>
       <c r="AH74" s="71"/>
     </row>
-    <row r="75" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="71">
         <v>74</v>
       </c>
@@ -14449,7 +14462,7 @@
       </c>
       <c r="AH75" s="71"/>
     </row>
-    <row r="76" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="71">
         <v>75</v>
       </c>
@@ -14545,7 +14558,7 @@
       </c>
       <c r="AH76" s="71"/>
     </row>
-    <row r="77" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="71">
         <v>76</v>
       </c>
@@ -14633,7 +14646,7 @@
       </c>
       <c r="AH77" s="71"/>
     </row>
-    <row r="78" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="87">
         <v>77</v>
       </c>
@@ -14711,7 +14724,7 @@
       </c>
       <c r="AH78" s="87"/>
     </row>
-    <row r="79" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="87">
         <v>78</v>
       </c>
@@ -14811,7 +14824,7 @@
       </c>
       <c r="AH79" s="87"/>
     </row>
-    <row r="80" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="71">
         <v>79</v>
       </c>
@@ -14907,7 +14920,7 @@
       </c>
       <c r="AH80" s="71"/>
     </row>
-    <row r="81" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="71">
         <v>80</v>
       </c>
@@ -15005,7 +15018,7 @@
       </c>
       <c r="AH81" s="71"/>
     </row>
-    <row r="82" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="71">
         <v>81</v>
       </c>
@@ -15101,7 +15114,7 @@
       </c>
       <c r="AH82" s="71"/>
     </row>
-    <row r="83" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83" s="71">
         <v>82</v>
       </c>
@@ -15129,7 +15142,7 @@
       <c r="I83" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="J83" t="s">
+      <c r="J83" s="0" t="s">
         <v>68</v>
       </c>
       <c r="K83" s="215">
@@ -15197,7 +15210,7 @@
       </c>
       <c r="AH83" s="71"/>
     </row>
-    <row r="84" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84" s="218">
         <v>83</v>
       </c>
@@ -15295,7 +15308,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="85" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85" s="225">
         <v>84</v>
       </c>
@@ -15397,7 +15410,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="86" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86" s="225">
         <v>85</v>
       </c>
@@ -15501,7 +15514,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="87" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87" s="225">
         <v>86</v>
       </c>
@@ -15601,7 +15614,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="88" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88" s="225">
         <v>87</v>
       </c>
@@ -15693,7 +15706,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="89" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89" s="126">
         <v>88</v>
       </c>
@@ -15793,7 +15806,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="90" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90" s="244">
         <v>89</v>
       </c>
@@ -15895,7 +15908,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="91" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91" s="244">
         <v>90</v>
       </c>
@@ -15997,7 +16010,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="92" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92" s="244">
         <v>91</v>
       </c>
@@ -16085,7 +16098,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="93" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93" s="244">
         <v>92</v>
       </c>
@@ -16171,7 +16184,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="94" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94" s="244">
         <v>93</v>
       </c>
@@ -16265,7 +16278,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="95" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95" s="244">
         <v>94</v>
       </c>
@@ -16357,7 +16370,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="96" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="96">
       <c r="A96" s="251">
         <v>95</v>
       </c>
@@ -16457,7 +16470,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="97" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="97">
       <c r="A97" s="258">
         <v>96</v>
       </c>
@@ -16555,7 +16568,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="98" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="98">
       <c r="A98" s="71">
         <v>97</v>
       </c>
@@ -16653,7 +16666,7 @@
       </c>
       <c r="AH98" s="71"/>
     </row>
-    <row r="99" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="99">
       <c r="A99" s="71">
         <v>98</v>
       </c>
@@ -16749,7 +16762,7 @@
       </c>
       <c r="AH99" s="71"/>
     </row>
-    <row r="100" spans="1:34" ht="15" x14ac:dyDescent="0.4">
+    <row r="100" ht="15">
       <c r="A100" s="71">
         <v>99</v>
       </c>
@@ -16833,246 +16846,246 @@
         <v>430</v>
       </c>
     </row>
-    <row r="101" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101" s="71">
         <v>100</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="0" t="s">
         <v>431</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="K101" t="s">
+      <c r="K101" s="0" t="s">
         <v>434</v>
       </c>
-      <c r="L101" t="s">
+      <c r="L101" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="M101" t="s">
+      <c r="M101" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="N101" t="s">
+      <c r="N101" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="O101" t="s">
+      <c r="O101" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="P101" t="s">
+      <c r="P101" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="Q101" t="s">
+      <c r="Q101" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="U101" t="s">
-        <v>45</v>
-      </c>
-      <c r="V101" t="s">
-        <v>45</v>
-      </c>
-      <c r="W101" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB101" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE101" t="s">
+      <c r="U101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="V101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="W101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB101" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="AE101" s="0" t="s">
         <v>437</v>
       </c>
       <c r="AG101" s="156">
         <v>8873884889</v>
       </c>
     </row>
-    <row r="102" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" s="0">
         <v>101</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="0" t="s">
         <v>438</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C102" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G102" t="s">
+      <c r="G102" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="I102" t="s">
+      <c r="I102" s="0" t="s">
         <v>433</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="L102" t="s">
-        <v>45</v>
-      </c>
-      <c r="M102" t="s">
+      <c r="L102" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M102" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="N102" t="s">
+      <c r="N102" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="O102" t="s">
+      <c r="O102" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="P102" t="s">
+      <c r="P102" s="0" t="s">
         <v>43</v>
       </c>
-      <c r="Q102" t="s">
+      <c r="Q102" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="U102" t="s">
+      <c r="U102" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="V102" t="s">
+      <c r="V102" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="W102" t="s">
+      <c r="W102" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="AB102" t="s">
+      <c r="AB102" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="AE102" t="s">
+      <c r="AE102" s="0" t="s">
         <v>442</v>
       </c>
       <c r="AG102" s="156"/>
     </row>
-    <row r="103" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" s="0">
         <v>102</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="0" t="s">
         <v>443</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C103" s="0" t="s">
         <v>444</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="G103" t="s">
+      <c r="G103" s="0" t="s">
         <v>196</v>
       </c>
-      <c r="I103" t="s">
+      <c r="I103" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="K103" t="s">
+      <c r="K103" s="0" t="s">
         <v>445</v>
       </c>
-      <c r="L103" t="s">
-        <v>45</v>
-      </c>
-      <c r="M103" t="s">
+      <c r="L103" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="M103" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="N103" t="s">
+      <c r="N103" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="O103" t="s">
+      <c r="O103" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="P103" t="s">
+      <c r="P103" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="Q103" t="s">
+      <c r="Q103" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="U103" t="s">
+      <c r="U103" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="V103" t="s">
+      <c r="V103" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="W103" t="s">
+      <c r="W103" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="AB103" t="s">
+      <c r="AB103" s="0" t="s">
         <v>126</v>
       </c>
-      <c r="AE103" t="s">
+      <c r="AE103" s="0" t="s">
         <v>46</v>
       </c>
       <c r="AG103" s="156"/>
     </row>
-    <row r="104" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="AG104" s="156"/>
     </row>
-    <row r="105" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="AG105" s="156"/>
     </row>
-    <row r="106" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="AG106" s="156"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B99">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C92 C94:C98">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C100">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C93">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C99">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16 P16:Q16">
-    <cfRule type="expression" dxfId="9" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>$AH16=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N35 Q35 O40:Q40">
-    <cfRule type="expression" dxfId="8" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>$AF35=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N48:P48 N49 N51 Q51 N54:Q54 N56:Q56 N65:Q65 O71 O75:Q75">
-    <cfRule type="expression" dxfId="7" priority="10">
+    <cfRule type="expression" dxfId="2" priority="10">
       <formula>$AB48=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N14:Q14">
-    <cfRule type="expression" dxfId="6" priority="13">
+    <cfRule type="expression" dxfId="2" priority="13">
       <formula>$AG14=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O57">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>$AB57=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O59:Q59">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="2" priority="7">
       <formula>$AB59=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P42 N42:N43 Q42:Q43">
-    <cfRule type="expression" dxfId="3" priority="11">
+    <cfRule type="expression" dxfId="2" priority="11">
       <formula>$AE42=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17082,105 +17095,106 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH84:AH97">
-    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D3" r:id="rId3" display="mailto:abirudugadda@deloitte.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C11" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C12" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="C13" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C15" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C16" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C18" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C19" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C21" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C22" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C24" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C25" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C26" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C28" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C29" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C30" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C31" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C32" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C33" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="M33" r:id="rId34" display="akalkundre@deloitte.com" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C34" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C35" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C36" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C37" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C38" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="P38" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C39" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C40" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C41" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C42" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="C43" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C44" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="C45" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C47" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="C48" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C49" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C50" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C51" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="C52" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C53" r:id="rId54" display="mailto:visviswanathan@deloitte.com" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C54" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C55" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C56" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C57" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="C58" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C59" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C61" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C62" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="C63" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C64" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="C67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="C69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C71" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C72" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C73" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="C76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="C79" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="C80" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="C82" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="C83" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="C84" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="C85" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="C86" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="C87" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="C88" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="C89" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="C90" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="C91" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="C92" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="C93" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="C94" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="C95" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="C96" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="C97" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="C99" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="C100" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="C2" r:id="rId97"/>
+    <hyperlink ref="C3" r:id="rId98"/>
+    <hyperlink ref="D3" display="mailto:abirudugadda@deloitte.com" r:id="rId99"/>
+    <hyperlink ref="C4" r:id="rId100"/>
+    <hyperlink ref="C5" r:id="rId101"/>
+    <hyperlink ref="C6" r:id="rId102"/>
+    <hyperlink ref="C7" r:id="rId103"/>
+    <hyperlink ref="C8" r:id="rId104"/>
+    <hyperlink ref="C9" r:id="rId105"/>
+    <hyperlink ref="C10" r:id="rId106"/>
+    <hyperlink ref="C11" r:id="rId107"/>
+    <hyperlink ref="C12" r:id="rId108"/>
+    <hyperlink ref="C13" r:id="rId109"/>
+    <hyperlink ref="C14" r:id="rId110"/>
+    <hyperlink ref="C15" r:id="rId111"/>
+    <hyperlink ref="C16" r:id="rId112"/>
+    <hyperlink ref="C17" r:id="rId113"/>
+    <hyperlink ref="C18" r:id="rId114"/>
+    <hyperlink ref="C19" r:id="rId115"/>
+    <hyperlink ref="C20" r:id="rId116"/>
+    <hyperlink ref="C21" r:id="rId117"/>
+    <hyperlink ref="C22" r:id="rId118"/>
+    <hyperlink ref="C23" r:id="rId119"/>
+    <hyperlink ref="C24" r:id="rId120"/>
+    <hyperlink ref="C25" r:id="rId121"/>
+    <hyperlink ref="C26" r:id="rId122"/>
+    <hyperlink ref="C27" r:id="rId123"/>
+    <hyperlink ref="C28" r:id="rId124"/>
+    <hyperlink ref="C29" r:id="rId125"/>
+    <hyperlink ref="C30" r:id="rId126"/>
+    <hyperlink ref="C31" r:id="rId127"/>
+    <hyperlink ref="C32" r:id="rId128"/>
+    <hyperlink ref="C33" r:id="rId129"/>
+    <hyperlink ref="M33" display="akalkundre@deloitte.com" r:id="rId130"/>
+    <hyperlink ref="C34" r:id="rId131"/>
+    <hyperlink ref="C35" r:id="rId132"/>
+    <hyperlink ref="C36" r:id="rId133"/>
+    <hyperlink ref="C37" r:id="rId134"/>
+    <hyperlink ref="C38" r:id="rId135"/>
+    <hyperlink ref="P38" r:id="rId136"/>
+    <hyperlink ref="C39" r:id="rId137"/>
+    <hyperlink ref="C40" r:id="rId138"/>
+    <hyperlink ref="C41" r:id="rId139"/>
+    <hyperlink ref="C42" r:id="rId140"/>
+    <hyperlink ref="C43" r:id="rId141"/>
+    <hyperlink ref="C44" r:id="rId142"/>
+    <hyperlink ref="C45" r:id="rId143"/>
+    <hyperlink ref="C47" r:id="rId144"/>
+    <hyperlink ref="C48" r:id="rId145"/>
+    <hyperlink ref="C49" r:id="rId146"/>
+    <hyperlink ref="C50" r:id="rId147"/>
+    <hyperlink ref="C51" r:id="rId148"/>
+    <hyperlink ref="C52" r:id="rId149"/>
+    <hyperlink ref="C53" display="mailto:visviswanathan@deloitte.com" r:id="rId150"/>
+    <hyperlink ref="C54" r:id="rId151"/>
+    <hyperlink ref="C55" r:id="rId152"/>
+    <hyperlink ref="C56" r:id="rId153"/>
+    <hyperlink ref="C57" r:id="rId154"/>
+    <hyperlink ref="C58" r:id="rId155"/>
+    <hyperlink ref="C59" r:id="rId156"/>
+    <hyperlink ref="C61" r:id="rId157"/>
+    <hyperlink ref="C62" r:id="rId158"/>
+    <hyperlink ref="C63" r:id="rId159"/>
+    <hyperlink ref="C64" r:id="rId160"/>
+    <hyperlink ref="C66" r:id="rId161"/>
+    <hyperlink ref="C67" r:id="rId162"/>
+    <hyperlink ref="C68" r:id="rId163"/>
+    <hyperlink ref="C69" r:id="rId164"/>
+    <hyperlink ref="C71" r:id="rId165"/>
+    <hyperlink ref="C72" r:id="rId166"/>
+    <hyperlink ref="C73" r:id="rId167"/>
+    <hyperlink ref="C75" r:id="rId168"/>
+    <hyperlink ref="C76" r:id="rId169"/>
+    <hyperlink ref="C79" r:id="rId170"/>
+    <hyperlink ref="C80" r:id="rId171"/>
+    <hyperlink ref="C82" r:id="rId172"/>
+    <hyperlink ref="C83" r:id="rId173"/>
+    <hyperlink ref="C84" r:id="rId174"/>
+    <hyperlink ref="C85" r:id="rId175"/>
+    <hyperlink ref="C86" r:id="rId176"/>
+    <hyperlink ref="C87" r:id="rId177"/>
+    <hyperlink ref="C88" r:id="rId178"/>
+    <hyperlink ref="C89" r:id="rId179"/>
+    <hyperlink ref="C90" r:id="rId180"/>
+    <hyperlink ref="C91" r:id="rId181"/>
+    <hyperlink ref="C92" r:id="rId182"/>
+    <hyperlink ref="C93" r:id="rId183"/>
+    <hyperlink ref="C94" r:id="rId184"/>
+    <hyperlink ref="C95" r:id="rId185"/>
+    <hyperlink ref="C96" r:id="rId186"/>
+    <hyperlink ref="C97" r:id="rId187"/>
+    <hyperlink ref="C99" r:id="rId188"/>
+    <hyperlink ref="C100" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId94"/>
 </worksheet>
 </file>
@@ -17195,26 +17209,26 @@
     <col min="3" max="3" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>628</v>
-      </c>
-      <c r="B1" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>630</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="C2" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C2" s="0" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="80" t="s">
         <v>36</v>
       </c>
@@ -17225,7 +17239,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="82" t="s">
         <v>56</v>
       </c>
@@ -17236,7 +17250,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="82" t="s">
         <v>38</v>
       </c>
@@ -17247,7 +17261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="82" t="s">
         <v>105</v>
       </c>
@@ -17258,7 +17272,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="82" t="s">
         <v>51</v>
       </c>
@@ -17269,7 +17283,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="82" t="s">
         <v>82</v>
       </c>
@@ -17280,7 +17294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="82" t="s">
         <v>100</v>
       </c>
@@ -17291,7 +17305,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="82" t="s">
         <v>196</v>
       </c>
@@ -17302,9 +17316,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="80" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B11" s="78">
         <v>84</v>
@@ -17315,6 +17329,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -17329,24 +17344,24 @@
     <col min="4" max="4" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="78" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B2" s="78" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C2" s="78"/>
       <c r="D2" s="78"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="78" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>126</v>
@@ -17355,10 +17370,10 @@
         <v>45</v>
       </c>
       <c r="D3" s="78" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="78" t="s">
         <v>40</v>
       </c>
@@ -17372,7 +17387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="78" t="s">
         <v>75</v>
       </c>
@@ -17384,7 +17399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="78" t="s">
         <v>109</v>
       </c>
@@ -17396,7 +17411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="78" t="s">
         <v>58</v>
       </c>
@@ -17408,7 +17423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="78" t="s">
         <v>95</v>
       </c>
@@ -17420,7 +17435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="78" t="s">
         <v>112</v>
       </c>
@@ -17432,7 +17447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="78" t="s">
         <v>370</v>
       </c>
@@ -17444,7 +17459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="78" t="s">
         <v>122</v>
       </c>
@@ -17456,7 +17471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="78" t="s">
         <v>86</v>
       </c>
@@ -17468,7 +17483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="78" t="s">
         <v>173</v>
       </c>
@@ -17480,7 +17495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="78" t="s">
         <v>210</v>
       </c>
@@ -17492,7 +17507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="78" t="s">
         <v>218</v>
       </c>
@@ -17504,7 +17519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="78" t="s">
         <v>227</v>
       </c>
@@ -17516,9 +17531,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="78" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B17" s="78">
         <v>6</v>
@@ -17530,35 +17545,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D18" t="s">
+    <row r="18">
+      <c r="D18" s="0" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19">
+      <c r="A19" s="0" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="77" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="78" t="s">
+        <v>639</v>
+      </c>
+      <c r="B23" s="78" t="s">
         <v>635</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="78" t="s">
-        <v>633</v>
-      </c>
-      <c r="B23" s="78" t="s">
-        <v>629</v>
       </c>
       <c r="C23" s="78"/>
       <c r="D23" s="78"/>
       <c r="E23" s="78"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="78" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="B24" s="78" t="s">
         <v>83</v>
@@ -17570,10 +17585,10 @@
         <v>61</v>
       </c>
       <c r="E24" s="78" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="78" t="s">
         <v>40</v>
       </c>
@@ -17588,7 +17603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="78" t="s">
         <v>75</v>
       </c>
@@ -17601,7 +17616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="78" t="s">
         <v>109</v>
       </c>
@@ -17614,7 +17629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="78" t="s">
         <v>58</v>
       </c>
@@ -17627,7 +17642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="78" t="s">
         <v>95</v>
       </c>
@@ -17640,7 +17655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="78" t="s">
         <v>112</v>
       </c>
@@ -17655,7 +17670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="78" t="s">
         <v>370</v>
       </c>
@@ -17670,7 +17685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="78" t="s">
         <v>122</v>
       </c>
@@ -17685,7 +17700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="78" t="s">
         <v>86</v>
       </c>
@@ -17700,7 +17715,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="78" t="s">
         <v>173</v>
       </c>
@@ -17713,7 +17728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="78" t="s">
         <v>210</v>
       </c>
@@ -17726,7 +17741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="78" t="s">
         <v>218</v>
       </c>
@@ -17739,7 +17754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="78" t="s">
         <v>227</v>
       </c>
@@ -17752,9 +17767,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="78" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="B38" s="78">
         <v>24</v>
@@ -17769,162 +17784,162 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="78" t="s">
+        <v>642</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="79" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="s">
+        <v>639</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="s">
         <v>636</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B51" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="0" t="s">
+        <v>649</v>
+      </c>
+      <c r="E51" s="0" t="s">
+        <v>650</v>
+      </c>
+      <c r="F51" s="0" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B43" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="79" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>633</v>
-      </c>
-      <c r="B50" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>630</v>
-      </c>
-      <c r="B51" t="s">
-        <v>642</v>
-      </c>
-      <c r="C51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D51" t="s">
-        <v>643</v>
-      </c>
-      <c r="E51" t="s">
-        <v>644</v>
-      </c>
-      <c r="F51" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="80" t="s">
-        <v>645</v>
-      </c>
-      <c r="B52">
+        <v>651</v>
+      </c>
+      <c r="B52" s="0">
         <v>5</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="0">
         <v>14</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="0">
         <v>1</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="0">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="80" t="s">
-        <v>646</v>
-      </c>
-      <c r="C53">
+        <v>652</v>
+      </c>
+      <c r="C53" s="0">
         <v>8</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="0">
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="80" t="s">
-        <v>647</v>
-      </c>
-      <c r="B54">
+        <v>653</v>
+      </c>
+      <c r="B54" s="0">
         <v>1</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="0">
         <v>29</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="0">
         <v>5</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="0">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="80" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="80" t="s">
-        <v>631</v>
-      </c>
-      <c r="B56">
+        <v>637</v>
+      </c>
+      <c r="B56" s="0">
         <v>6</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="0">
         <v>51</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="0">
         <v>6</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="0">
         <v>63</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="70" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B59" s="71"/>
       <c r="C59" s="71"/>
       <c r="D59" s="71"/>
       <c r="E59" s="71"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="70" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B60" s="70" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C60" s="70" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D60" s="70" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E60" s="70" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="F60" s="77"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="313">
         <v>38</v>
       </c>
       <c r="B61" s="71" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C61" s="71">
         <v>12</v>
@@ -17936,10 +17951,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="314"/>
       <c r="B62" s="71" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C62" s="71">
         <v>9</v>
@@ -17951,10 +17966,10 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="315"/>
       <c r="B63" s="71" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C63" s="71">
         <v>27</v>
@@ -17966,29 +17981,30 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="C64" s="81">
         <f>C63/(C63+D63)</f>
-        <v>0.79411764705882348</v>
-      </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.35">
+        <v>0.7941176470588235</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="C65" s="81">
         <f>C62/(C62+D62)</f>
-        <v>0.39130434782608697</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.35">
+        <v>0.391304347826087</v>
+      </c>
+    </row>
+    <row r="66">
       <c r="C66" s="81">
         <f>C61/(C61+D61)</f>
         <v>0.34285714285714286</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="A61:A63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18001,128 +18017,129 @@
     <col min="2" max="2" width="16.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>630</v>
-      </c>
-      <c r="B3" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B1" s="0" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>636</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="80" t="s">
         <v>134</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="80" t="s">
         <v>148</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="80" t="s">
         <v>121</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="80" t="s">
         <v>387</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="80" t="s">
         <v>401</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="80" t="s">
         <v>355</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="80" t="s">
         <v>405</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="80" t="s">
         <v>156</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="80" t="s">
-        <v>631</v>
-      </c>
-      <c r="B16">
+        <v>637</v>
+      </c>
+      <c r="B16" s="0">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18135,107 +18152,108 @@
     <col min="2" max="3" width="26.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="281" t="s">
         <v>12</v>
       </c>
       <c r="B1" s="281" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="C1" s="281" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="2" ht="29">
       <c r="A2" s="282" t="s">
         <v>197</v>
       </c>
       <c r="B2" s="283" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C2" s="284" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="282" t="s">
         <v>109</v>
       </c>
       <c r="B3" s="285" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C3" s="284" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="4" ht="29">
       <c r="A4" s="282" t="s">
         <v>140</v>
       </c>
       <c r="B4" s="283" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C4" s="284" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" ht="58">
       <c r="A5" s="282" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B5" s="283" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C5" s="284" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" ht="29">
       <c r="A6" s="283" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="B6" s="283" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C6" s="284" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="283" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="283" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C7" s="284" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="286" t="s">
         <v>173</v>
       </c>
       <c r="B8" s="287" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C8" s="286" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="286" t="s">
         <v>112</v>
       </c>
       <c r="B9" s="287" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C9" s="286" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18248,27 +18266,28 @@
     <col min="2" max="2" width="93.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="278" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B1" s="278" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="279" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="B2" s="280" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
+    <hyperlink ref="B2" display="https://greendot365.sharepoint.com/sites/VendorComplianceTraining/Shared Documents/Forms/AllItems.aspx" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18284,65 +18303,65 @@
     <col min="5" max="5" width="31.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="39" x14ac:dyDescent="0.35">
+    <row r="1" ht="39">
       <c r="A1" s="288" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="B1" s="289" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C1" s="289" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D1" s="289" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="E1" s="290" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="247" customHeight="1" x14ac:dyDescent="0.35">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="2" ht="247" customHeight="1">
       <c r="A2" s="318" t="s">
         <v>197</v>
       </c>
       <c r="B2" s="321" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C2" s="321">
         <v>2</v>
       </c>
       <c r="D2" s="324" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="E2" s="291" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="3" ht="26.5">
       <c r="A3" s="319"/>
       <c r="B3" s="323"/>
       <c r="C3" s="323"/>
       <c r="D3" s="325"/>
       <c r="E3" s="292" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="156.5" x14ac:dyDescent="0.35">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="4" ht="156.5">
       <c r="A4" s="319"/>
       <c r="B4" s="293" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C4" s="293">
         <v>2</v>
       </c>
       <c r="D4" s="294" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="E4" s="292" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="5" ht="39.5">
       <c r="A5" s="319" t="s">
         <v>58</v>
       </c>
@@ -18353,26 +18372,26 @@
         <v>3</v>
       </c>
       <c r="D5" s="295" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="E5" s="292" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="6" ht="65.5">
       <c r="A6" s="320"/>
       <c r="B6" s="323"/>
       <c r="C6" s="323"/>
       <c r="D6" s="296" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="E6" s="297" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="52.5" x14ac:dyDescent="0.35">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="7" ht="52.5">
       <c r="A7" s="318" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="B7" s="321" t="s">
         <v>96</v>
@@ -18381,35 +18400,35 @@
         <v>3</v>
       </c>
       <c r="D7" s="295" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="E7" s="291" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="8" ht="65.5">
       <c r="A8" s="319"/>
       <c r="B8" s="322"/>
       <c r="C8" s="322"/>
       <c r="D8" s="298" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="E8" s="299" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="39.5" x14ac:dyDescent="0.35">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="9" ht="39.5">
       <c r="A9" s="320"/>
       <c r="B9" s="323"/>
       <c r="C9" s="323"/>
       <c r="D9" s="296" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="E9" s="300"/>
     </row>
-    <row r="10" spans="1:5" ht="273" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="273" customHeight="1">
       <c r="A10" s="318" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B10" s="321" t="s">
         <v>87</v>
@@ -18418,22 +18437,22 @@
         <v>4</v>
       </c>
       <c r="D10" s="316" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="E10" s="291" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="26.5" x14ac:dyDescent="0.35">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="11" ht="26.5">
       <c r="A11" s="320"/>
       <c r="B11" s="323"/>
       <c r="C11" s="323"/>
       <c r="D11" s="317"/>
       <c r="E11" s="297" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="65.5" x14ac:dyDescent="0.35">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="12" ht="65.5">
       <c r="A12" s="301" t="s">
         <v>109</v>
       </c>
@@ -18444,14 +18463,14 @@
         <v>2</v>
       </c>
       <c r="D12" s="294" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E12" s="302" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
@@ -18468,6 +18487,7 @@
     <mergeCell ref="C10:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18480,36 +18500,37 @@
     <col min="2" max="2" width="62.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="265" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B1" s="266" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="71" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="71" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0F00-000001000000}"/>
+    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/green-dot-devops-profile-training" r:id="rId1"/>
+    <hyperlink ref="B3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18523,117 +18544,118 @@
     <col min="3" max="3" width="53.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B2" t="s">
-        <v>708</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>714</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D2" t="s">
-        <v>710</v>
-      </c>
-      <c r="E2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>707</v>
-      </c>
-      <c r="B3" t="s">
-        <v>712</v>
+        <v>715</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>718</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>713</v>
-      </c>
-      <c r="D3" t="s">
-        <v>714</v>
-      </c>
-      <c r="E3" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>723</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>716</v>
       </c>
-      <c r="B4" t="s">
+      <c r="E4" s="0" t="s">
         <v>717</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="D4" t="s">
-        <v>710</v>
-      </c>
-      <c r="E4" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>716</v>
-      </c>
-      <c r="B5" t="s">
-        <v>719</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>722</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>725</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" t="s">
+        <v>726</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>727</v>
+      </c>
+      <c r="E5" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="E5" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>716</v>
-      </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
         <v>722</v>
       </c>
+      <c r="B6" s="0" t="s">
+        <v>728</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="D6" t="s">
-        <v>724</v>
-      </c>
-      <c r="E6" t="s">
-        <v>715</v>
+        <v>729</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>730</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>721</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1000-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-1000-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-1000-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{00000000-0004-0000-1000-000004000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18649,63 +18671,64 @@
     <col min="5" max="5" width="18.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B2" t="s">
-        <v>725</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="2" ht="101.5">
+      <c r="A2" s="0" t="s">
+        <v>713</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>731</v>
       </c>
       <c r="C2" s="267" t="s">
-        <v>726</v>
-      </c>
-      <c r="D2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="E2" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>729</v>
-      </c>
-      <c r="B3" t="s">
-        <v>507</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="D3" t="s">
-        <v>721</v>
-      </c>
-      <c r="E3" t="s">
-        <v>728</v>
+      <c r="E3" s="0" t="s">
+        <v>734</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="overview" xr:uid="{00000000-0004-0000-1100-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1100-000001000000}"/>
+    <hyperlink ref="C2" location="overview" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18714,88 +18737,89 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>729</v>
+        <v>712</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="s">
+        <v>735</v>
       </c>
       <c r="C2" s="268" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>729</v>
-      </c>
-      <c r="B3" t="s">
-        <v>508</v>
+        <v>737</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="s">
+        <v>735</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>514</v>
       </c>
       <c r="C3" s="268" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>729</v>
+        <v>738</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>735</v>
       </c>
       <c r="C4" s="268" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>734</v>
+        <v>739</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>740</v>
       </c>
       <c r="C5" s="268" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>734</v>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>740</v>
       </c>
       <c r="C6" s="268" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1200-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" xr:uid="{00000000-0004-0000-1200-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" xr:uid="{00000000-0004-0000-1200-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" xr:uid="{00000000-0004-0000-1200-000003000000}"/>
-    <hyperlink ref="C6" r:id="rId5" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" xr:uid="{00000000-0004-0000-1200-000004000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dlbefktukbqc&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334584233%7cunknow" r:id="rId2"/>
+    <hyperlink ref="C4" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.youtube.com%2fwatch%3fv%3dhnvr2k5d2nw&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921%7c0%7c0%7c639038967334607937%7cunknow" r:id="rId3"/>
+    <hyperlink ref="C5" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2frovo%2fguides%2fend-user-guide%2fhow-to-use-rovo&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c47579708de528e1455%7c36da45f1dd2c4d1faf135abe46b99921" r:id="rId4"/>
+    <hyperlink ref="C6" location="autom…" tooltip="https://nam10.safelinks.protection.outlook.com/?url=https%3a%2f%2fwww.atlassian.com%2fsoftware%2fconfluence%2fresources%2fguides%2fbest-practices%2fconfluence-rovo%23automation-and-ai-in-confluence&amp;data=05%7c02%7ckmullangi%40deloitte.com%7c53f0e13896974c4" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FB81B8-A234-4EA6-8FB5-B1AA8CB50C92}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.6328125" customWidth="1"/>
     <col min="3" max="3" width="13.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>446</v>
       </c>
@@ -18812,8 +18836,8 @@
         <v>450</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -18822,15 +18846,15 @@
       <c r="C2" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -18839,15 +18863,15 @@
       <c r="C3" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -18856,91 +18880,143 @@
       <c r="C4" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>458</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>459</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="0" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>460</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="0" t="s">
         <v>451</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>453</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>464</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>461</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="C3" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="B4" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="C4" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+    <hyperlink ref="B3" r:id="rId3"/>
+    <hyperlink ref="C3" r:id="rId4"/>
+    <hyperlink ref="B4" r:id="rId5"/>
+    <hyperlink ref="C4" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -18954,103 +19030,104 @@
     <col min="3" max="3" width="33.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="C1" s="77" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="D1" s="77" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="E1" s="77" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5">
       <c r="A2" s="326" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
       <c r="B2" s="171" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="C2" s="267" t="s">
-        <v>738</v>
-      </c>
-      <c r="D2" t="s">
-        <v>714</v>
-      </c>
-      <c r="E2" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>744</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>720</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="3" ht="29">
       <c r="A3" s="326"/>
       <c r="B3" s="171" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="D3" t="s">
-        <v>741</v>
-      </c>
-      <c r="E3" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>742</v>
-      </c>
-      <c r="B5" t="s">
-        <v>743</v>
+        <v>746</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>747</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>749</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="D5" t="s">
-        <v>727</v>
-      </c>
-      <c r="E5" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+        <v>750</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>745</v>
-      </c>
-      <c r="B7" t="s">
-        <v>746</v>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>751</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>752</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="D7" t="s">
-        <v>748</v>
-      </c>
-      <c r="E7" t="s">
-        <v>711</v>
+        <v>753</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>754</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>717</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="A2:A3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-1300-000000000000}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-1300-000001000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-1300-000002000000}"/>
-    <hyperlink ref="C7" r:id="rId4" xr:uid="{00000000-0004-0000-1300-000003000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C5" r:id="rId3"/>
+    <hyperlink ref="C7" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19063,117 +19140,118 @@
     <col min="2" max="2" width="77.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="265" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B1" s="77" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="269" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="B2" s="270" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="3" ht="43.5">
       <c r="A3" s="271" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="B3" s="272" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="4" ht="43.5">
       <c r="A4" s="271" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="B4" s="272" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="5" ht="101.5">
       <c r="A5" s="271" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
       <c r="B5" s="273" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="6" ht="29">
       <c r="A6" s="271" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="B6" s="272" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="269" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="B7" s="270" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="269" t="s">
-        <v>761</v>
+        <v>767</v>
       </c>
       <c r="B8" s="270" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="9" ht="72.5">
       <c r="A9" s="271" t="s">
-        <v>763</v>
+        <v>769</v>
       </c>
       <c r="B9" s="272" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="269" t="s">
-        <v>765</v>
+        <v>771</v>
       </c>
       <c r="B10" s="270" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="274" t="s">
-        <v>767</v>
+        <v>773</v>
       </c>
       <c r="B11" s="270" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="12" ht="58">
       <c r="A12" s="275" t="s">
-        <v>769</v>
+        <v>775</v>
       </c>
       <c r="B12" s="272" t="s">
-        <v>770</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-1400-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" xr:uid="{00000000-0004-0000-1400-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" xr:uid="{00000000-0004-0000-1400-000002000000}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-1400-000003000000}"/>
-    <hyperlink ref="B6" r:id="rId5" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" xr:uid="{00000000-0004-0000-1400-000004000000}"/>
-    <hyperlink ref="B7" r:id="rId6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" xr:uid="{00000000-0004-0000-1400-000005000000}"/>
-    <hyperlink ref="B8" r:id="rId7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" xr:uid="{00000000-0004-0000-1400-000006000000}"/>
-    <hyperlink ref="B9" r:id="rId8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" xr:uid="{00000000-0004-0000-1400-000007000000}"/>
-    <hyperlink ref="B10" r:id="rId9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" xr:uid="{00000000-0004-0000-1400-000008000000}"/>
-    <hyperlink ref="B11" r:id="rId10" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" xr:uid="{00000000-0004-0000-1400-000009000000}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-1400-00000A000000}"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="B3" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110221459" r:id="rId2"/>
+    <hyperlink ref="B4" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100834837" r:id="rId3"/>
+    <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/110314377" r:id="rId5"/>
+    <hyperlink ref="B7" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/108778855" r:id="rId6"/>
+    <hyperlink ref="B8" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100527044" r:id="rId7"/>
+    <hyperlink ref="B9" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/100764263" r:id="rId8"/>
+    <hyperlink ref="B10" tooltip="https://becurious.edcast.eu/pathways/green-dot-dot-net-profile-training/cards/101256005" r:id="rId9"/>
+    <hyperlink ref="B11" display="https://secure-web.cisco.com/1tvyNBxX3ndiQ5w6U35qtGmNindmwLdjQ9DVBuD5KL_1y2XN6on5qJVqSpbgS8xDmmnv0dmmZz0mhBoPa2E_zcjKTj25VXZ_-eRZKm39pQw6zg2QwuQMJdhhTTvKC90CEqT6dHXTF7HRXQgeFrcpS7uxvGh-NrlFnbjtI-38q9A_zOHEKPkoBtGsVjehAbYc83dzt1xNM5hW9YnnwpxRmypm4oj-5xJip156IgbnCA6Y1RZkv7gnsqgZwpYE1b3-CHke-AhKhfzQtwKiLCDW-EYEam7oJ8PUj80pjFq2_ZvoaIvQXxCCNUsXkjIBcvcVto5BCDCFQ2irHwPb9RXNbTNct5BFz0tuw_1OvjhUmhMeyJBr7mxT4k7wfHcq197LeZZGn-8BCyEevjUoOo2pmOiOCmm0Y_oYuAUFmdmrVEB2nZSeOTZsSMUbPTBA9Yrs94BKdUDzIf9kplTnJxh0CM3Q41pMlod_uyXkG_aLLzl2-q-XpUukXH-TgaFEncXM1/https%3A%2F%2Fbecurious.edcast.eu%2Finsights%2FECL-62a9fb5a-bfa5-48c8-b554-9a827d075124" r:id="rId10"/>
+    <hyperlink ref="B12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19186,36 +19264,37 @@
     <col min="2" max="2" width="37.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="67" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B1" s="67" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="2" ht="43.5">
       <c r="A2" s="276" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="3" ht="43.5">
       <c r="A3" s="276" t="s">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>774</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-1500-000000000000}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-1500-000001000000}"/>
+    <hyperlink ref="A2" r:id="rId1"/>
+    <hyperlink ref="A3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19228,63 +19307,64 @@
     <col min="2" max="2" width="48.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="77" t="s">
-        <v>666</v>
-      </c>
-      <c r="B1" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="B3" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>781</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="B5" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>783</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="B7" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>785</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="B8" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="B9" t="s">
-        <v>784</v>
+        <v>789</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>790</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-1600-000000000000}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{00000000-0004-0000-1600-000001000000}"/>
-    <hyperlink ref="A7" r:id="rId3" xr:uid="{00000000-0004-0000-1600-000002000000}"/>
-    <hyperlink ref="A8" r:id="rId4" xr:uid="{00000000-0004-0000-1600-000003000000}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{00000000-0004-0000-1600-000004000000}"/>
+    <hyperlink ref="A3" r:id="rId1"/>
+    <hyperlink ref="A5" r:id="rId2"/>
+    <hyperlink ref="A7" r:id="rId3"/>
+    <hyperlink ref="A8" r:id="rId4"/>
+    <hyperlink ref="A9" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19297,51 +19377,52 @@
     <col min="2" max="2" width="42.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="277" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="B1" s="266" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="112" t="s">
-        <v>785</v>
+        <v>791</v>
       </c>
       <c r="B2" s="101" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="71" t="s">
-        <v>787</v>
+        <v>793</v>
       </c>
       <c r="B3" s="101" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="71" t="s">
-        <v>789</v>
+        <v>795</v>
       </c>
       <c r="B4" s="101" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" xr:uid="{00000000-0004-0000-1700-000000000000}"/>
-    <hyperlink ref="B3" r:id="rId2" display="https://becurious.edcast.eu/pathways/azure-sql-this" xr:uid="{00000000-0004-0000-1700-000001000000}"/>
-    <hyperlink ref="B4" r:id="rId3" location="overview" display="IICS Complated Guide" xr:uid="{00000000-0004-0000-1700-000002000000}"/>
+    <hyperlink ref="B2" display="https://becurious.edcast.eu/pathways/amazon-redshift-training-pathway" r:id="rId1"/>
+    <hyperlink ref="B3" display="https://becurious.edcast.eu/pathways/azure-sql-this" r:id="rId2"/>
+    <hyperlink ref="B4" location="overview" display="IICS Complated Guide" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A39430F7-7ECF-4A8C-8A31-042445403756}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="18.54296875" customWidth="1"/>
@@ -19350,388 +19431,423 @@
     <col min="5" max="5" width="57.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="C2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D2">
+      <c r="C2" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="D2" s="0">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="E2" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="C3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D3">
+      <c r="C3" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D3" s="0">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D4" s="0">
+        <v>3</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="D5" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D6" s="0">
+        <v>1</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D7" s="0">
+        <v>2</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D8" s="0">
+        <v>3</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>9</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="D9" s="0">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>10</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D10" s="0">
+        <v>2</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>11</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D11" s="0">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="E11" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>12</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="D12" s="0">
+        <v>4</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>13</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>14</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="D14" s="0">
+        <v>2</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>15</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D15" s="0">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E15" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>16</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="D16" s="0">
+        <v>4</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>17</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="D17" s="0">
+        <v>1</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>18</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C18" s="0" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="D18" s="0">
+        <v>2</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>19</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D19" s="0">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>20</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="D20" s="0">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" t="s">
-        <v>474</v>
-      </c>
-      <c r="D5">
+      <c r="E20" s="0" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>21</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="D21" s="0">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="E21" s="0" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>22</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="D22" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>476</v>
-      </c>
-      <c r="C6" t="s">
-        <v>477</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="E22" s="0" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="D23" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>476</v>
-      </c>
-      <c r="C7" t="s">
-        <v>470</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>476</v>
-      </c>
-      <c r="C8" t="s">
-        <v>472</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" t="s">
-        <v>468</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>479</v>
-      </c>
-      <c r="C10" t="s">
-        <v>470</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>479</v>
-      </c>
-      <c r="C11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>479</v>
-      </c>
-      <c r="C12" t="s">
-        <v>474</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>480</v>
-      </c>
-      <c r="C13" t="s">
-        <v>468</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>480</v>
-      </c>
-      <c r="C14" t="s">
-        <v>470</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>480</v>
-      </c>
-      <c r="C15" t="s">
-        <v>472</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>480</v>
-      </c>
-      <c r="C16" t="s">
-        <v>474</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
-      </c>
-      <c r="E16" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>481</v>
-      </c>
-      <c r="C17" t="s">
-        <v>468</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>481</v>
-      </c>
-      <c r="C18" t="s">
-        <v>470</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>481</v>
-      </c>
-      <c r="C19" t="s">
-        <v>472</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>481</v>
-      </c>
-      <c r="C20" t="s">
-        <v>474</v>
-      </c>
-      <c r="D20">
-        <v>4</v>
-      </c>
-      <c r="E20" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>476</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E23" s="0" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-      <c r="E21" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>476</v>
-      </c>
-      <c r="C22" t="s">
-        <v>484</v>
-      </c>
-      <c r="D22">
+      <c r="C24" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="D24" s="0">
         <v>5</v>
       </c>
-      <c r="E22" t="s">
-        <v>485</v>
+      <c r="E24" s="0" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89F9B618-8BC8-49DD-B7A7-74400FF462D0}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -19740,229 +19856,332 @@
     <col min="5" max="5" width="16.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="4" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>38</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>490</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="E2" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>490</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="D3" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="E3" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>34</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E4" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="E4" s="0" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>80</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E5" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="E5" s="0" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>80</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0">
         <v>6</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E6" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="E6" s="0" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>25</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0">
         <v>5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="0" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>1</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0">
         <v>1</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="0" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>25</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="0" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" s="0">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0">
         <v>25</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0">
         <v>21</v>
       </c>
-      <c r="D10" t="s">
-        <v>493</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" s="0">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0">
         <v>25</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0">
         <v>22</v>
       </c>
-      <c r="D11" t="s">
-        <v>493</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" s="0">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0">
         <v>25</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0">
         <v>23</v>
       </c>
-      <c r="D12" t="s">
-        <v>493</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E12" s="0" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" s="0">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0">
         <v>80</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0">
         <v>7</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E13" t="s">
-        <v>494</v>
+      <c r="E13" s="0" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>80</v>
+      </c>
+      <c r="C14" s="0">
+        <v>22</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0">
+        <v>12</v>
+      </c>
+      <c r="C15" s="0">
+        <v>9</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0">
+        <v>12</v>
+      </c>
+      <c r="C16" s="0">
+        <v>10</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0">
+        <v>12</v>
+      </c>
+      <c r="C17" s="0">
+        <v>12</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0">
+        <v>12</v>
+      </c>
+      <c r="C18" s="0">
+        <v>11</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0">
+        <v>12</v>
+      </c>
+      <c r="C19" s="0">
+        <v>23</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -19978,9 +20197,9 @@
     <col min="5" max="5" width="15.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="4" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -19992,105 +20211,106 @@
         <v>449</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>80</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="0" t="s">
         <v>344</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E2" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
+      <c r="D2" s="0" t="s">
+        <v>503</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
         <v>35</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="E3" s="0" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="E4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="E4" s="0" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="E5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="E5" s="0" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
         <v>16</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="E6" t="s">
-        <v>502</v>
+      <c r="E6" s="0" t="s">
+        <v>508</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14947C1-2082-4307-8EB3-961E6465F131}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="1"/>
@@ -20101,37 +20321,37 @@
     <col min="6" max="6" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E2" s="3">
@@ -20141,34 +20361,34 @@
         <v>46249</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" s="0">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="C3" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>318</v>
       </c>
       <c r="E3" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>508</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C4" s="0" t="s">
+        <v>514</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="3">
@@ -20178,17 +20398,17 @@
         <v>46255</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="0">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0">
         <v>78</v>
       </c>
-      <c r="C5" t="s">
-        <v>506</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C5" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>61</v>
       </c>
       <c r="E5" s="3">
@@ -20198,96 +20418,115 @@
         <v>46268</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" s="0">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0">
         <v>87</v>
       </c>
-      <c r="C6" t="s">
-        <v>507</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C6" s="0" t="s">
+        <v>513</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>318</v>
       </c>
       <c r="E6" s="3">
         <v>46325</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="0">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0">
         <v>78</v>
       </c>
-      <c r="C7" t="s">
-        <v>509</v>
-      </c>
-      <c r="D7" t="s">
-        <v>493</v>
-      </c>
-      <c r="E7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="C7" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0">
         <v>94</v>
       </c>
-      <c r="C8" t="s">
-        <v>506</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="C8" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="0">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0">
         <v>55</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="E9" t="s">
-        <v>511</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E9" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>80</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>517</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>22</v>
+      </c>
+      <c r="C11" s="0" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>509</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>511</v>
-      </c>
-      <c r="F10" t="s">
-        <v>513</v>
-      </c>
+      <c r="D11" s="0" t="s">
+        <v>498</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="F11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -20309,42 +20548,42 @@
     <col min="11" max="11" width="21.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" ht="58">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F1" s="23" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G1" s="23" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="H1" s="23" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="I1" s="23" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="J1" s="23" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="K1" s="23" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="126" customHeight="1" x14ac:dyDescent="0.35">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="2" ht="126" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -20369,13 +20608,13 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -20389,7 +20628,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>126</v>
@@ -20400,11 +20639,11 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="K3" s="8"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -20418,7 +20657,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>126</v>
@@ -20427,15 +20666,15 @@
         <v>126</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="8"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -20458,20 +20697,20 @@
         <v>126</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="5"/>
@@ -20483,7 +20722,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="8"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -20509,12 +20748,12 @@
         <v>189</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="8"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="5">
         <v>8</v>
       </c>
@@ -20531,7 +20770,7 @@
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
     </row>
-    <row r="9" spans="1:11" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="82" customHeight="1">
       <c r="A9" s="5">
         <v>9</v>
       </c>
@@ -20557,10 +20796,10 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="11" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="5">
         <v>10</v>
       </c>
@@ -20584,12 +20823,12 @@
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="246" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="246" customHeight="1">
       <c r="A11" s="5">
         <v>11</v>
       </c>
@@ -20603,7 +20842,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>45</v>
@@ -20612,15 +20851,15 @@
         <v>45</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
       <c r="K11" s="11" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="12" ht="58.5" customHeight="1">
       <c r="A12" s="5">
         <v>12</v>
       </c>
@@ -20644,16 +20883,16 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" s="5">
         <v>13</v>
       </c>
@@ -20680,7 +20919,7 @@
       <c r="J13" s="6"/>
       <c r="K13" s="8"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="5">
         <v>14</v>
       </c>
@@ -20703,15 +20942,15 @@
         <v>126</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="5">
         <v>15</v>
       </c>
@@ -20732,17 +20971,17 @@
         <v>126</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="71" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="71" customHeight="1">
       <c r="A16" s="5">
         <v>16</v>
       </c>
@@ -20755,8 +20994,8 @@
       <c r="D16" s="5">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
-        <v>541</v>
+      <c r="E16" s="0" t="s">
+        <v>547</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>45</v>
@@ -20765,17 +21004,17 @@
         <v>126</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="8" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="17" ht="134" customHeight="1">
       <c r="A17" s="5">
         <v>17</v>
       </c>
@@ -20798,24 +21037,24 @@
         <v>45</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="12">
         <v>18</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C18" s="14" t="s">
         <v>50</v>
@@ -20824,7 +21063,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>126</v>
@@ -20833,20 +21072,20 @@
         <v>126</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="J18" s="13"/>
       <c r="K18" s="15"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="5">
         <v>19</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>50</v>
@@ -20855,7 +21094,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>126</v>
@@ -20868,12 +21107,12 @@
       <c r="J19" s="6"/>
       <c r="K19" s="8"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="5">
         <v>20</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C20" s="18" t="s">
         <v>50</v>
@@ -20895,12 +21134,12 @@
       <c r="J20" s="6"/>
       <c r="K20" s="8"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="5">
         <v>21</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C21" s="18" t="s">
         <v>50</v>
@@ -20922,7 +21161,7 @@
       <c r="J21" s="6"/>
       <c r="K21" s="8"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="5">
         <v>22</v>
       </c>
@@ -20945,17 +21184,17 @@
         <v>126</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="5">
         <v>23</v>
       </c>
@@ -20978,7 +21217,7 @@
       <c r="J23" s="6"/>
       <c r="K23" s="8"/>
     </row>
-    <row r="24" spans="1:11" ht="60.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" ht="60.5" customHeight="1">
       <c r="A24" s="16">
         <v>24</v>
       </c>
@@ -20992,7 +21231,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>126</v>
@@ -21004,15 +21243,15 @@
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="8" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" s="5">
         <v>25</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>50</v>
@@ -21034,12 +21273,12 @@
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="5">
         <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>50</v>
@@ -21061,7 +21300,7 @@
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="5">
         <v>28</v>
       </c>
@@ -21075,7 +21314,7 @@
         <v>2</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>126</v>
@@ -21090,12 +21329,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="55.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" ht="55.5" customHeight="1">
       <c r="A28" s="5">
         <v>29</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>50</v>
@@ -21116,15 +21355,15 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
       <c r="K28" s="8" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="68.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="29" ht="68.5" customHeight="1">
       <c r="A29" s="5">
         <v>30</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>50</v>
@@ -21145,11 +21384,12 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="8" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -21175,11 +21415,11 @@
     <col min="14" max="14" width="18.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="304" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="D1" s="305"/>
       <c r="E1" s="305"/>
@@ -21190,17 +21430,17 @@
       <c r="J1" s="305"/>
       <c r="K1" s="306"/>
       <c r="L1" s="307" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="M1" s="308"/>
       <c r="N1" s="308"/>
     </row>
-    <row r="2" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" ht="58">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="25"/>
       <c r="D2" s="309" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="E2" s="309"/>
       <c r="F2" s="309"/>
@@ -21208,75 +21448,75 @@
       <c r="H2" s="309"/>
       <c r="I2" s="309"/>
       <c r="J2" s="26" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="K2" s="27"/>
       <c r="L2" s="25"/>
       <c r="M2" s="25"/>
       <c r="N2" s="25"/>
     </row>
-    <row r="3" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" ht="43.5">
       <c r="A3" s="28" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="G3" s="29" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="H3" s="29" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="I3" s="29" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="J3" s="29" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="K3" s="30" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="L3" s="29" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="N3" s="29" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="24" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C4" s="25" t="s">
         <v>126</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E4" s="32" t="s">
         <v>63</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="G4" s="25">
         <v>0</v>
@@ -21285,7 +21525,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>63</v>
@@ -21297,24 +21537,24 @@
         <v>45</v>
       </c>
       <c r="M4" s="25" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N4" s="25">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="35" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C5" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E5" s="38" t="s">
         <v>63</v>
@@ -21339,15 +21579,15 @@
         <v>45</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N5" s="37">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="35" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B6" s="36" t="s">
         <v>268</v>
@@ -21389,62 +21629,62 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="35" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="G7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="I7" s="37" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="J7" s="39" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="K7" s="39" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="L7" s="37" t="s">
         <v>45</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N7" s="37">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="35" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>45</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E8" s="41">
         <v>0.5</v>
@@ -21463,30 +21703,30 @@
         <v>48</v>
       </c>
       <c r="K8" s="40" t="s">
+        <v>595</v>
+      </c>
+      <c r="L8" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="25" t="s">
         <v>589</v>
-      </c>
-      <c r="L8" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>583</v>
       </c>
       <c r="N8" s="37">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" ht="29">
       <c r="A9" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="C9" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E9" s="41" t="s">
         <v>63</v>
@@ -21513,13 +21753,13 @@
         <v>45</v>
       </c>
       <c r="M9" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N9" s="43">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="24" t="s">
         <v>59</v>
       </c>
@@ -21530,7 +21770,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="47" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E10" s="41">
         <v>1</v>
@@ -21548,33 +21788,33 @@
         <v>63</v>
       </c>
       <c r="J10" s="44" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="K10" s="45" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M10" s="47" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N10" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" ht="29">
       <c r="A11" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="47" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E11" s="41">
         <v>1</v>
@@ -21592,22 +21832,22 @@
         <v>63</v>
       </c>
       <c r="J11" s="44" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="K11" s="45" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L11" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N11" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="24" t="s">
         <v>59</v>
       </c>
@@ -21618,7 +21858,7 @@
         <v>45</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E12" s="49">
         <v>0.8</v>
@@ -21639,30 +21879,30 @@
         <v>252</v>
       </c>
       <c r="K12" s="52" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="L12" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M12" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N12" s="43">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="42" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="C13" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E13" s="41">
         <v>0.5</v>
@@ -21680,7 +21920,7 @@
         <v>63</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="K13" s="54">
         <v>9618241586</v>
@@ -21689,18 +21929,18 @@
         <v>45</v>
       </c>
       <c r="M13" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N13" s="43">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="25" t="s">
         <v>59</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>126</v>
@@ -21739,7 +21979,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="24" t="s">
         <v>59</v>
       </c>
@@ -21777,13 +22017,13 @@
         <v>45</v>
       </c>
       <c r="M15" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N15" s="43">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="24" t="s">
         <v>59</v>
       </c>
@@ -21809,13 +22049,13 @@
         <v>210</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="J16" s="44" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K16" s="45" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="L16" s="43" t="s">
         <v>126</v>
@@ -21827,18 +22067,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17">
       <c r="A17" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="C17" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="E17" s="41" t="s">
         <v>63</v>
@@ -21871,18 +22111,18 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="64" t="s">
         <v>59</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="43" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="E18" s="41">
         <v>0.5</v>
@@ -21900,57 +22140,58 @@
         <v>46049</v>
       </c>
       <c r="J18" s="44" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="K18" s="45" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="L18" s="43" t="s">
         <v>45</v>
       </c>
       <c r="M18" s="43" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="N18" s="43">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="19">
+      <c r="A19" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>586</v>
-      </c>
-      <c r="E19" t="s">
-        <v>605</v>
-      </c>
-      <c r="F19" t="s">
-        <v>510</v>
-      </c>
-      <c r="G19" t="s">
-        <v>606</v>
-      </c>
-      <c r="J19" t="s">
-        <v>607</v>
-      </c>
-      <c r="K19" t="s">
-        <v>608</v>
+      <c r="C19" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>611</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>516</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>612</v>
+      </c>
+      <c r="J19" s="0" t="s">
+        <v>613</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>614</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="C1:K1"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="D2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -21965,30 +22206,30 @@
     <col min="5" max="5" width="17.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="76" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C1" s="76" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D1" s="76" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E1" s="76" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="310" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C2" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!U1:U679, "Y")</f>
@@ -22003,10 +22244,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="310"/>
       <c r="B3" s="6" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C3" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!V1:V679, "Y")</f>
@@ -22021,10 +22262,10 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="310"/>
       <c r="B4" s="6" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="C4" s="65" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y", [1]Team!AB1:AB679, "Y")</f>
@@ -22039,22 +22280,22 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>616</v>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>622</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="67" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D6" s="67" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="B7" s="6" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C7" s="68">
         <v>36</v>
@@ -22064,37 +22305,37 @@
       </c>
       <c r="E7" s="6"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="311" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="B9" s="311"/>
       <c r="C9" s="311"/>
-      <c r="D9" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D9" s="0" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="69"/>
       <c r="B10" s="69" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="69" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="70" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="B11" s="312">
         <v>74</v>
       </c>
       <c r="C11" s="312"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="71" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="B12" s="72">
         <v>61</v>
@@ -22103,9 +22344,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="71" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B13" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "Y")</f>
@@ -22115,9 +22356,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="71" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="B14" s="73" t="e">
         <f>COUNTIFS([1]Team!L1:L679, "N")</f>
@@ -22125,9 +22366,9 @@
       </c>
       <c r="C14" s="71"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="74" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="B15" s="75">
         <v>26</v>
@@ -22136,26 +22377,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="71" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B16" s="72">
         <f>B12-B15</f>
         <v>35</v>
       </c>
       <c r="C16" s="71" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="B11:C11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to TeamTracker under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
